--- a/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
+++ b/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="768">
   <si>
     <t>set</t>
   </si>
@@ -111,1669 +111,1534 @@
     <t>u</t>
   </si>
   <si>
-    <t>UPSBIOCHR</t>
-  </si>
-  <si>
-    <t>UPSBIOOTH</t>
-  </si>
-  <si>
-    <t>REGRS</t>
-  </si>
-  <si>
-    <t>DEGRS</t>
-  </si>
-  <si>
-    <t>RESHR</t>
-  </si>
-  <si>
-    <t>DESHR</t>
-  </si>
-  <si>
-    <t>RECRP</t>
-  </si>
-  <si>
-    <t>DECRP</t>
-  </si>
-  <si>
-    <t>REPET</t>
-  </si>
-  <si>
-    <t>DEPET</t>
-  </si>
-  <si>
-    <t>REWET</t>
-  </si>
-  <si>
-    <t>DEWET</t>
-  </si>
-  <si>
-    <t>LNDPET</t>
-  </si>
-  <si>
-    <t>TRAEVSCHG001</t>
-  </si>
-  <si>
-    <t>TRAEVSCHG002</t>
-  </si>
-  <si>
-    <t>TRAEVSCHG003</t>
-  </si>
-  <si>
-    <t>INDOTHELCHTH</t>
-  </si>
-  <si>
-    <t>INDOTHDSLHTH</t>
-  </si>
-  <si>
-    <t>INDOTHNGSHTH</t>
-  </si>
-  <si>
-    <t>INDOTHBIOHTH</t>
-  </si>
-  <si>
-    <t>INDOTHCOAHTH</t>
-  </si>
-  <si>
-    <t>INDOTHHDGHTH</t>
-  </si>
-  <si>
-    <t>INDOTHGSLMDR</t>
-  </si>
-  <si>
-    <t>INDOTHDSLMDR</t>
-  </si>
-  <si>
-    <t>INDOTHELCMDR</t>
-  </si>
-  <si>
-    <t>INDOTHPLT</t>
-  </si>
-  <si>
-    <t>INDMTRELCHTH</t>
-  </si>
-  <si>
-    <t>INDMTRDSLHTH</t>
-  </si>
-  <si>
-    <t>INDMTRNGSHTH</t>
-  </si>
-  <si>
-    <t>INDMTRBIOHTH</t>
-  </si>
-  <si>
-    <t>INDMTRCOAHTH</t>
-  </si>
-  <si>
-    <t>INDMTRHDGHTH</t>
-  </si>
-  <si>
-    <t>INDMTRGSLMDR</t>
-  </si>
-  <si>
-    <t>INDMTRDSLMDR</t>
-  </si>
-  <si>
-    <t>INDMTRELCMDR</t>
-  </si>
-  <si>
-    <t>INDMTRPLT</t>
-  </si>
-  <si>
-    <t>INDCHMPLT</t>
-  </si>
-  <si>
-    <t>INDCHMELCHTH</t>
-  </si>
-  <si>
-    <t>INDCHMKERHTH</t>
-  </si>
-  <si>
-    <t>INDCHMNGSHTH</t>
-  </si>
-  <si>
-    <t>INDCHMBIOHTH</t>
-  </si>
-  <si>
-    <t>INDCHMCOAHTH</t>
-  </si>
-  <si>
-    <t>INDCHMHDGHTH</t>
-  </si>
-  <si>
-    <t>INDFBTELCHTH</t>
-  </si>
-  <si>
-    <t>INDFBTPLT</t>
-  </si>
-  <si>
-    <t>INDFBTHFOHTH</t>
-  </si>
-  <si>
-    <t>INDFBTNGSHTH</t>
-  </si>
-  <si>
-    <t>INDFBTBIOHTH</t>
-  </si>
-  <si>
-    <t>INDFBTCOAHTH</t>
-  </si>
-  <si>
-    <t>INDFBTHDGHTH</t>
-  </si>
-  <si>
-    <t>DEMINDHDG</t>
-  </si>
-  <si>
-    <t>INDIRSPLT</t>
-  </si>
-  <si>
-    <t>AGRGSLFSH</t>
-  </si>
-  <si>
-    <t>DEMINDWST</t>
+    <t>DUMREWET</t>
+  </si>
+  <si>
+    <t>DUMDEWET</t>
+  </si>
+  <si>
+    <t>ACCPWRWAT</t>
+  </si>
+  <si>
+    <t>ACCMINWAT</t>
+  </si>
+  <si>
+    <t>ACCAGRWAT1</t>
+  </si>
+  <si>
+    <t>ACCAGRWAT0</t>
+  </si>
+  <si>
+    <t>LNDWET</t>
+  </si>
+  <si>
+    <t>STOBATIN</t>
+  </si>
+  <si>
+    <t>STOBATOUT</t>
+  </si>
+  <si>
+    <t>LVSOTHCF</t>
+  </si>
+  <si>
+    <t>LVSOTHCU</t>
+  </si>
+  <si>
+    <t>LNDCANLR</t>
+  </si>
+  <si>
+    <t>LNDCANLI</t>
+  </si>
+  <si>
+    <t>LNDCANHR</t>
+  </si>
+  <si>
+    <t>LNDCANHI</t>
+  </si>
+  <si>
+    <t>DEMAGRCOA</t>
+  </si>
+  <si>
+    <t>DEMAGRLPG</t>
+  </si>
+  <si>
+    <t>DEMAGRELC</t>
+  </si>
+  <si>
+    <t>AGRELCCUR</t>
+  </si>
+  <si>
+    <t>AGRHEATCOA</t>
+  </si>
+  <si>
+    <t>AGRHEATLPG</t>
+  </si>
+  <si>
+    <t>AGRHEATELC</t>
+  </si>
+  <si>
+    <t>AGRMOTLPG</t>
+  </si>
+  <si>
+    <t>AGRMOTELC</t>
+  </si>
+  <si>
+    <t>PROPROCBIOF</t>
+  </si>
+  <si>
+    <t>BLENDBIOF</t>
+  </si>
+  <si>
+    <t>DEMTRABIO</t>
+  </si>
+  <si>
+    <t>BLENDJETKER</t>
+  </si>
+  <si>
+    <t>INDMINHPHBIOCCS</t>
+  </si>
+  <si>
+    <t>INDMINHPHCOACCS</t>
+  </si>
+  <si>
+    <t>INDASHHPHBIOCCS</t>
+  </si>
+  <si>
+    <t>INDASHHPHCOACCS</t>
+  </si>
+  <si>
+    <t>INDOTHHPHBIOCCS</t>
+  </si>
+  <si>
+    <t>INDOTHHPHCOACCS</t>
+  </si>
+  <si>
+    <t>INDKILNBIOCCS</t>
+  </si>
+  <si>
+    <t>INDKILNCOACCS</t>
+  </si>
+  <si>
+    <t>INDOTHLPHELC</t>
+  </si>
+  <si>
+    <t>INDPLANTCCSASH</t>
+  </si>
+  <si>
+    <t>BSTOPPWRWAT</t>
+  </si>
+  <si>
+    <t>BSTOPPUBWAT</t>
+  </si>
+  <si>
+    <t>BSTOPOTHWAT</t>
+  </si>
+  <si>
+    <t>BSTOPMINWAT</t>
+  </si>
+  <si>
+    <t>BSTOPRESWAT</t>
+  </si>
+  <si>
+    <t>BSTOPGOVWAT</t>
+  </si>
+  <si>
+    <t>BSTOPAGRWAT</t>
+  </si>
+  <si>
+    <t>BSTOPWSTCO2</t>
+  </si>
+  <si>
+    <t>DEMTOURELC</t>
+  </si>
+  <si>
+    <t>TOURELCHET</t>
+  </si>
+  <si>
+    <t>TOURELCCUR</t>
+  </si>
+  <si>
+    <t>DEMTOURLPG</t>
+  </si>
+  <si>
+    <t>TOURLPGHET</t>
+  </si>
+  <si>
+    <t>DEMTOURBIO</t>
+  </si>
+  <si>
+    <t>TOURBIOHET</t>
+  </si>
+  <si>
+    <t>DEMTOURCOA</t>
+  </si>
+  <si>
+    <t>TOURCOAHET</t>
+  </si>
+  <si>
+    <t>DEMTOURDSL</t>
+  </si>
+  <si>
+    <t>TOURDSLHET</t>
+  </si>
+  <si>
+    <t>DUMLUC</t>
+  </si>
+  <si>
+    <t>DEMPWRCBM</t>
+  </si>
+  <si>
+    <t>IMPJETKER</t>
+  </si>
+  <si>
+    <t>MINCBM</t>
+  </si>
+  <si>
+    <t>PWRCBM001</t>
+  </si>
+  <si>
+    <t>LNDCRPOTH</t>
+  </si>
+  <si>
+    <t>INDPLANTOTH</t>
+  </si>
+  <si>
+    <t>INDOTHLPHDSL</t>
+  </si>
+  <si>
+    <t>INDOTHLPHLPG</t>
+  </si>
+  <si>
+    <t>INDOTHLPHHFO</t>
+  </si>
+  <si>
+    <t>INDOTHLPHCOA</t>
+  </si>
+  <si>
+    <t>INDOTHLPHBIO</t>
+  </si>
+  <si>
+    <t>INDOTHHPHDSL</t>
+  </si>
+  <si>
+    <t>INDOTHHPHLPG</t>
+  </si>
+  <si>
+    <t>INDOTHHPHHFO</t>
+  </si>
+  <si>
+    <t>INDOTHHPHCOA</t>
+  </si>
+  <si>
+    <t>INDOTHHPHBIO</t>
+  </si>
+  <si>
+    <t>INDMINMOTDSL</t>
+  </si>
+  <si>
+    <t>INDMINMOTELE</t>
+  </si>
+  <si>
+    <t>INDMINUNIT</t>
+  </si>
+  <si>
+    <t>INDMINHPHLPG</t>
+  </si>
+  <si>
+    <t>INDMINHPHHFO</t>
+  </si>
+  <si>
+    <t>INDMINHPHDSL</t>
+  </si>
+  <si>
+    <t>INDMINHPHCOA</t>
+  </si>
+  <si>
+    <t>INDMINHPHBIO</t>
+  </si>
+  <si>
+    <t>INDKILNBIO</t>
+  </si>
+  <si>
+    <t>INDASHHPHBIO</t>
+  </si>
+  <si>
+    <t>INDASHHPHLPG</t>
+  </si>
+  <si>
+    <t>INDASHHPHHFO</t>
+  </si>
+  <si>
+    <t>INDASHHPHDSL</t>
+  </si>
+  <si>
+    <t>INDASHHPHCOA</t>
+  </si>
+  <si>
+    <t>INDPLANTASH</t>
+  </si>
+  <si>
+    <t>INDKILNDSL</t>
+  </si>
+  <si>
+    <t>INDKILNLPG</t>
+  </si>
+  <si>
+    <t>INDKILNHFO</t>
+  </si>
+  <si>
+    <t>INDKILNCOA</t>
+  </si>
+  <si>
+    <t>INDPLANTCEM</t>
+  </si>
+  <si>
+    <t>TRAELCRAILP</t>
+  </si>
+  <si>
+    <t>TRADSLRAILP</t>
+  </si>
+  <si>
+    <t>DEMMINWAT</t>
+  </si>
+  <si>
+    <t>DEMRESWAT</t>
+  </si>
+  <si>
+    <t>DEMOTHWAT</t>
+  </si>
+  <si>
+    <t>DEMPWRWAT</t>
+  </si>
+  <si>
+    <t>DEMGOVWAT</t>
+  </si>
+  <si>
+    <t>DEMAGRWAT</t>
+  </si>
+  <si>
+    <t>WATSURMIN</t>
+  </si>
+  <si>
+    <t>WATGWTMIN</t>
+  </si>
+  <si>
+    <t>IMPWAT</t>
+  </si>
+  <si>
+    <t>PWRCOA003</t>
+  </si>
+  <si>
+    <t>WSTLFLGEN</t>
+  </si>
+  <si>
+    <t>WSTINCGEN</t>
+  </si>
+  <si>
+    <t>LVSCTLCF</t>
+  </si>
+  <si>
+    <t>LVSGOACF</t>
+  </si>
+  <si>
+    <t>LVSSHPCF</t>
+  </si>
+  <si>
+    <t>DEMPWRSOL</t>
+  </si>
+  <si>
+    <t>DEMPWRWND</t>
+  </si>
+  <si>
+    <t>DEMPWRGEO</t>
+  </si>
+  <si>
+    <t>MINSOL</t>
+  </si>
+  <si>
+    <t>MINWND</t>
+  </si>
+  <si>
+    <t>MINGEO</t>
+  </si>
+  <si>
+    <t>PWRCOA_CCS</t>
+  </si>
+  <si>
+    <t>PWRBIO_CCS</t>
+  </si>
+  <si>
+    <t>LWTADA</t>
+  </si>
+  <si>
+    <t>LWTCAR</t>
+  </si>
+  <si>
+    <t>LWTLAG</t>
+  </si>
+  <si>
+    <t>LWTLAT</t>
+  </si>
+  <si>
+    <t>LWTSPT</t>
+  </si>
+  <si>
+    <t>LWTSWR</t>
+  </si>
+  <si>
+    <t>LWTGEN</t>
+  </si>
+  <si>
+    <t>TRADSLMCYNEW</t>
+  </si>
+  <si>
+    <t>MINNGS</t>
+  </si>
+  <si>
+    <t>MINCOA</t>
+  </si>
+  <si>
+    <t>PWRNGS001</t>
+  </si>
+  <si>
+    <t>PWRCOA001</t>
+  </si>
+  <si>
+    <t>PWRSOL001</t>
+  </si>
+  <si>
+    <t>PWRTRN</t>
+  </si>
+  <si>
+    <t>PWRNGS002</t>
+  </si>
+  <si>
+    <t>MINBIO</t>
+  </si>
+  <si>
+    <t>PWRBIO001</t>
+  </si>
+  <si>
+    <t>COMELCCUR</t>
+  </si>
+  <si>
+    <t>RESELCCUR</t>
+  </si>
+  <si>
+    <t>PWRWND001</t>
+  </si>
+  <si>
+    <t>PWRWND001S</t>
+  </si>
+  <si>
+    <t>PWRGEO</t>
+  </si>
+  <si>
+    <t>PWROHC002</t>
+  </si>
+  <si>
+    <t>PWROHC003</t>
+  </si>
+  <si>
+    <t>MINURN</t>
+  </si>
+  <si>
+    <t>PWRNUC</t>
+  </si>
+  <si>
+    <t>IMPBIO</t>
+  </si>
+  <si>
+    <t>IMPLPG</t>
+  </si>
+  <si>
+    <t>IMPHFO</t>
+  </si>
+  <si>
+    <t>IMPNGS</t>
+  </si>
+  <si>
+    <t>IMPURN</t>
+  </si>
+  <si>
+    <t>PWRTRNIMP</t>
+  </si>
+  <si>
+    <t>PWRTRNEXP</t>
+  </si>
+  <si>
+    <t>MINLND</t>
+  </si>
+  <si>
+    <t>LNDFOR</t>
+  </si>
+  <si>
+    <t>LNDBLT</t>
+  </si>
+  <si>
+    <t>LNDWAT</t>
+  </si>
+  <si>
+    <t>LNDOTH</t>
+  </si>
+  <si>
+    <t>PWRCSP002</t>
+  </si>
+  <si>
+    <t>PWRCSP001</t>
+  </si>
+  <si>
+    <t>PWRSOL001S</t>
+  </si>
+  <si>
+    <t>BACKSTOP001</t>
+  </si>
+  <si>
+    <t>BSTOPCOMELC</t>
+  </si>
+  <si>
+    <t>BSTOPRESELC</t>
+  </si>
+  <si>
+    <t>MINPRC</t>
+  </si>
+  <si>
+    <t>WATSURAGR</t>
+  </si>
+  <si>
+    <t>WATGWTAGR</t>
+  </si>
+  <si>
+    <t>WATSURPUB</t>
+  </si>
+  <si>
+    <t>WATGWTPUB</t>
+  </si>
+  <si>
+    <t>LNDMAIHR</t>
+  </si>
+  <si>
+    <t>LNDMAILR</t>
+  </si>
+  <si>
+    <t>LNDMAIHI</t>
+  </si>
+  <si>
+    <t>LNDMAILI</t>
+  </si>
+  <si>
+    <t>LNDPULHR</t>
+  </si>
+  <si>
+    <t>LNDPULLR</t>
+  </si>
+  <si>
+    <t>LNDPULHI</t>
+  </si>
+  <si>
+    <t>LNDPULLI</t>
+  </si>
+  <si>
+    <t>LNDSORHR</t>
+  </si>
+  <si>
+    <t>LNDSORLR</t>
+  </si>
+  <si>
+    <t>LNDSORHI</t>
+  </si>
+  <si>
+    <t>LNDSORLI</t>
+  </si>
+  <si>
+    <t>LNDMTPHR</t>
+  </si>
+  <si>
+    <t>LNDMTPLR</t>
+  </si>
+  <si>
+    <t>LNDMTPHI</t>
+  </si>
+  <si>
+    <t>LNDMTPLI</t>
+  </si>
+  <si>
+    <t>LNDGROHR</t>
+  </si>
+  <si>
+    <t>LNDGROLR</t>
+  </si>
+  <si>
+    <t>LNDGROHI</t>
+  </si>
+  <si>
+    <t>LNDGROLI</t>
+  </si>
+  <si>
+    <t>LNDWHEHR</t>
+  </si>
+  <si>
+    <t>LNDWHELR</t>
+  </si>
+  <si>
+    <t>LNDWHEHI</t>
+  </si>
+  <si>
+    <t>LNDWHELI</t>
+  </si>
+  <si>
+    <t>LNDSUNHR</t>
+  </si>
+  <si>
+    <t>LNDSUNLR</t>
+  </si>
+  <si>
+    <t>LNDSUNHI</t>
+  </si>
+  <si>
+    <t>LNDSUNLI</t>
+  </si>
+  <si>
+    <t>LNDOTCHR</t>
+  </si>
+  <si>
+    <t>LNDOTCLR</t>
+  </si>
+  <si>
+    <t>LNDOTCHI</t>
+  </si>
+  <si>
+    <t>LNDOTCLI</t>
+  </si>
+  <si>
+    <t>IMPMAI</t>
+  </si>
+  <si>
+    <t>IMPPUL</t>
+  </si>
+  <si>
+    <t>IMPSOR</t>
+  </si>
+  <si>
+    <t>IMPMTP</t>
+  </si>
+  <si>
+    <t>IMPGRO</t>
+  </si>
+  <si>
+    <t>IMPWHE</t>
+  </si>
+  <si>
+    <t>IMPSUN</t>
+  </si>
+  <si>
+    <t>IMPOTC</t>
+  </si>
+  <si>
+    <t>WATSURPWR</t>
+  </si>
+  <si>
+    <t>WATGWTPWR</t>
+  </si>
+  <si>
+    <t>IMPDSL</t>
+  </si>
+  <si>
+    <t>PWRDSL</t>
+  </si>
+  <si>
+    <t>RESELCCKN</t>
+  </si>
+  <si>
+    <t>RESBIOCKN</t>
+  </si>
+  <si>
+    <t>TRAELCMCYCUR</t>
+  </si>
+  <si>
+    <t>TRAELCCARCUR</t>
+  </si>
+  <si>
+    <t>TRAELCBUSCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLCARCUR</t>
+  </si>
+  <si>
+    <t>TRADSLBUSCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLMCYCUR</t>
+  </si>
+  <si>
+    <t>RESELCEFF</t>
+  </si>
+  <si>
+    <t>RESELCBST</t>
+  </si>
+  <si>
+    <t>COMELCEFF</t>
+  </si>
+  <si>
+    <t>COMELCBST</t>
+  </si>
+  <si>
+    <t>COMDSLHET</t>
+  </si>
+  <si>
+    <t>COMBIOHET</t>
+  </si>
+  <si>
+    <t>COMELCHET</t>
+  </si>
+  <si>
+    <t>RESBIOHEL</t>
+  </si>
+  <si>
+    <t>RESELCHEL</t>
+  </si>
+  <si>
+    <t>BSTOPMCY</t>
+  </si>
+  <si>
+    <t>BSTOPCAR</t>
+  </si>
+  <si>
+    <t>BSTOPBUS</t>
+  </si>
+  <si>
+    <t>BSTOPCOMHET</t>
+  </si>
+  <si>
+    <t>BSTOPRESHEL</t>
+  </si>
+  <si>
+    <t>BSTOPRESCKN</t>
+  </si>
+  <si>
+    <t>COMCOAHET</t>
+  </si>
+  <si>
+    <t>EXPMAI</t>
+  </si>
+  <si>
+    <t>EXPSOR</t>
+  </si>
+  <si>
+    <t>EXPMTP</t>
+  </si>
+  <si>
+    <t>EXPWHE</t>
+  </si>
+  <si>
+    <t>EXPSUN</t>
+  </si>
+  <si>
+    <t>LNDCRP</t>
+  </si>
+  <si>
+    <t>EXPOTC</t>
+  </si>
+  <si>
+    <t>EXPCOA</t>
+  </si>
+  <si>
+    <t>LNDGRS</t>
+  </si>
+  <si>
+    <t>LNDPSTCU</t>
+  </si>
+  <si>
+    <t>LNDPSTCF</t>
+  </si>
+  <si>
+    <t>LVSCTLCU</t>
+  </si>
+  <si>
+    <t>LVSGOACU</t>
+  </si>
+  <si>
+    <t>LVSSHPCU</t>
+  </si>
+  <si>
+    <t>DEMINDELC</t>
   </si>
   <si>
     <t>DEMINDCOA</t>
   </si>
   <si>
-    <t>DEMINDNGS</t>
+    <t>DEMINDBIO</t>
+  </si>
+  <si>
+    <t>DEMRESELC</t>
+  </si>
+  <si>
+    <t>DEMRESBIO</t>
+  </si>
+  <si>
+    <t>DEMCOMCOA</t>
+  </si>
+  <si>
+    <t>DEMCOMBIO</t>
+  </si>
+  <si>
+    <t>DEMCOMELC</t>
+  </si>
+  <si>
+    <t>DEMPWRCOA</t>
+  </si>
+  <si>
+    <t>DEMPWRNGS</t>
+  </si>
+  <si>
+    <t>DEMPWRBIO</t>
+  </si>
+  <si>
+    <t>DEMPWRHFO</t>
+  </si>
+  <si>
+    <t>DEMPWRURN</t>
+  </si>
+  <si>
+    <t>DEMPWRDSL</t>
+  </si>
+  <si>
+    <t>DEMTRAELC</t>
+  </si>
+  <si>
+    <t>DEMTRAGSL</t>
+  </si>
+  <si>
+    <t>DEMTRADSL</t>
   </si>
   <si>
     <t>DEMINDHFO</t>
   </si>
   <si>
+    <t>DEMINDDSL</t>
+  </si>
+  <si>
+    <t>DEMINDLPG</t>
+  </si>
+  <si>
+    <t>DEMCOMDSL</t>
+  </si>
+  <si>
+    <t>DEMRESLPG</t>
+  </si>
+  <si>
+    <t>DEMRESKER</t>
+  </si>
+  <si>
+    <t>RESDSLHEL</t>
+  </si>
+  <si>
+    <t>RESLPGHEL</t>
+  </si>
+  <si>
+    <t>RESLPGCKN</t>
+  </si>
+  <si>
+    <t>RESELCLGT</t>
+  </si>
+  <si>
+    <t>RESKERLGT</t>
+  </si>
+  <si>
+    <t>RESBIOLGT</t>
+  </si>
+  <si>
+    <t>RESELCCOL</t>
+  </si>
+  <si>
+    <t>DEMTRAJETKER</t>
+  </si>
+  <si>
+    <t>TRAJFLAVI</t>
+  </si>
+  <si>
+    <t>RESELCWHT</t>
+  </si>
+  <si>
+    <t>RESDSLWHT</t>
+  </si>
+  <si>
+    <t>RESBIOWHT</t>
+  </si>
+  <si>
+    <t>RESLPGWHT</t>
+  </si>
+  <si>
+    <t>RESKERWHT</t>
+  </si>
+  <si>
+    <t>COMLPGHET</t>
+  </si>
+  <si>
+    <t>IMPKER</t>
+  </si>
+  <si>
+    <t>TRADSLCARCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLCARNEW</t>
+  </si>
+  <si>
+    <t>TRADSLCARNEW</t>
+  </si>
+  <si>
+    <t>TRADSHCARNEW</t>
+  </si>
+  <si>
+    <t>TRAELCCARNEW</t>
+  </si>
+  <si>
+    <t>TRAGSLMCYNEW</t>
+  </si>
+  <si>
+    <t>TRAELCMCYNEW</t>
+  </si>
+  <si>
+    <t>TRADSLBUSNEW</t>
+  </si>
+  <si>
+    <t>TRADSHBUSNEW</t>
+  </si>
+  <si>
+    <t>TRAELCBUSNEW</t>
+  </si>
+  <si>
+    <t>IMPGSL</t>
+  </si>
+  <si>
+    <t>RESKERCKN</t>
+  </si>
+  <si>
+    <t>DEMRESDSL</t>
+  </si>
+  <si>
+    <t>TRAGSLMNBCUR</t>
+  </si>
+  <si>
+    <t>TRADSLMNBCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLMNBNEW</t>
+  </si>
+  <si>
+    <t>TRADSLMNBNEW</t>
+  </si>
+  <si>
+    <t>TRADSHMNBNEW</t>
+  </si>
+  <si>
+    <t>TRAELCMNBCUR</t>
+  </si>
+  <si>
+    <t>TRAELCMNBNEW</t>
+  </si>
+  <si>
+    <t>TRAGSLLTRCUR</t>
+  </si>
+  <si>
+    <t>TRADSLLTRCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLLTRNEW</t>
+  </si>
+  <si>
+    <t>TRADSLLTRNEW</t>
+  </si>
+  <si>
+    <t>TRADSHLTRNEW</t>
+  </si>
+  <si>
+    <t>TRAELCLTRCUR</t>
+  </si>
+  <si>
+    <t>TRAELCLTRNEW</t>
+  </si>
+  <si>
+    <t>TRADSLMTRCUR</t>
+  </si>
+  <si>
+    <t>TRADSLMTRNEW</t>
+  </si>
+  <si>
+    <t>TRAELCMTRCUR</t>
+  </si>
+  <si>
+    <t>TRAELCMTRNEW</t>
+  </si>
+  <si>
+    <t>TRADSLHTRCUR</t>
+  </si>
+  <si>
+    <t>TRADSLHTRNEW</t>
+  </si>
+  <si>
+    <t>TRAELCHTRCUR</t>
+  </si>
+  <si>
+    <t>TRAELCHTRNEW</t>
+  </si>
+  <si>
+    <t>DEMCOMLPG</t>
+  </si>
+  <si>
+    <t>DEMRESSOL</t>
+  </si>
+  <si>
+    <t>BSTOPRESWHT</t>
+  </si>
+  <si>
+    <t>BSTOPRESLGT</t>
+  </si>
+  <si>
+    <t>RESLPGLGT</t>
+  </si>
+  <si>
+    <t>DUMDEFOR</t>
+  </si>
+  <si>
+    <t>DUMREFOR</t>
+  </si>
+  <si>
+    <t>WSTGEN</t>
+  </si>
+  <si>
+    <t>WSTOPB</t>
+  </si>
+  <si>
+    <t>WSTDMP</t>
+  </si>
+  <si>
+    <t>WSTCOL</t>
+  </si>
+  <si>
+    <t>WSTUNS</t>
+  </si>
+  <si>
+    <t>WSTORG</t>
+  </si>
+  <si>
+    <t>WSTSEP</t>
+  </si>
+  <si>
+    <t>WSTDGS</t>
+  </si>
+  <si>
+    <t>WSTCMP</t>
+  </si>
+  <si>
+    <t>WSTMTR</t>
+  </si>
+  <si>
+    <t>WSTPAR</t>
+  </si>
+  <si>
+    <t>WSTPLR</t>
+  </si>
+  <si>
+    <t>WSTGLR</t>
+  </si>
+  <si>
+    <t>WSTHZD</t>
+  </si>
+  <si>
+    <t>WSTINCRES</t>
+  </si>
+  <si>
+    <t>WSTLFLRES</t>
+  </si>
+  <si>
+    <t>DEMPWRLFG</t>
+  </si>
+  <si>
+    <t>PWRLFG001</t>
+  </si>
+  <si>
+    <t>PWRCOA002</t>
+  </si>
+  <si>
+    <t>MINBGS</t>
+  </si>
+  <si>
+    <t>DEMRESBGS</t>
+  </si>
+  <si>
+    <t>RESBGSCKN</t>
+  </si>
+  <si>
+    <t>RESBGSHEL</t>
+  </si>
+  <si>
+    <t>RESBGSWHT</t>
+  </si>
+  <si>
+    <t>TRADSLRAILF</t>
+  </si>
+  <si>
+    <t>TRAELCRAILF</t>
+  </si>
+  <si>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>PWRWAT0</t>
+  </si>
+  <si>
+    <t>MINWAT0</t>
+  </si>
+  <si>
+    <t>AGRWAT1</t>
+  </si>
+  <si>
+    <t>AGRWAT0</t>
+  </si>
+  <si>
+    <t>LWET</t>
+  </si>
+  <si>
+    <t>LVSOTH</t>
+  </si>
+  <si>
+    <t>CRPCAN</t>
+  </si>
+  <si>
+    <t>AGRELCOTH</t>
+  </si>
+  <si>
+    <t>AGRHEAT</t>
+  </si>
+  <si>
+    <t>AGRMOT</t>
+  </si>
+  <si>
+    <t>AGRLPG</t>
+  </si>
+  <si>
+    <t>AGRCOA</t>
+  </si>
+  <si>
+    <t>AGRELC</t>
+  </si>
+  <si>
+    <t>TRABIOF</t>
+  </si>
+  <si>
+    <t>TRABIO</t>
+  </si>
+  <si>
+    <t>TRAJFL</t>
+  </si>
+  <si>
+    <t>TOURELCOTH</t>
+  </si>
+  <si>
+    <t>TOURHET</t>
+  </si>
+  <si>
+    <t>TOURELC</t>
+  </si>
+  <si>
+    <t>TOURCOA</t>
+  </si>
+  <si>
+    <t>TOURBIO</t>
+  </si>
+  <si>
+    <t>TOURDSL</t>
+  </si>
+  <si>
+    <t>TOURLPG</t>
+  </si>
+  <si>
+    <t>PWRCBM</t>
+  </si>
+  <si>
+    <t>JETKER</t>
+  </si>
+  <si>
+    <t>CBM</t>
+  </si>
+  <si>
+    <t>INDOTHLPH</t>
+  </si>
+  <si>
+    <t>INDOTHHPH</t>
+  </si>
+  <si>
+    <t>INDOTH</t>
+  </si>
+  <si>
+    <t>INDMINMOT</t>
+  </si>
+  <si>
+    <t>CLK</t>
+  </si>
+  <si>
+    <t>INDHPHASH</t>
+  </si>
+  <si>
+    <t>INDHPHMIN</t>
+  </si>
+  <si>
+    <t>INDASH</t>
+  </si>
+  <si>
     <t>INDCEM</t>
   </si>
   <si>
-    <t>LNDCRPFAL</t>
-  </si>
-  <si>
-    <t>AGRFER</t>
-  </si>
-  <si>
-    <t>DEMAGRGSL</t>
-  </si>
-  <si>
-    <t>AGRDSLMCH</t>
-  </si>
-  <si>
-    <t>AGRGSLMCH</t>
-  </si>
-  <si>
-    <t>AGRELCMCH</t>
-  </si>
-  <si>
-    <t>TRAGSLCARHYBCUR</t>
-  </si>
-  <si>
-    <t>TRADSLPRL</t>
-  </si>
-  <si>
-    <t>TRAELCPRL</t>
-  </si>
-  <si>
-    <t>TRADSLFRL</t>
-  </si>
-  <si>
-    <t>TRAELCFRL</t>
-  </si>
-  <si>
-    <t>TRAGSLNAV</t>
-  </si>
-  <si>
-    <t>TRAKERAVI</t>
-  </si>
-  <si>
-    <t>LVSCTLIMP</t>
-  </si>
-  <si>
-    <t>LVSSHPIMP</t>
-  </si>
-  <si>
-    <t>LVSGOAIMP</t>
-  </si>
-  <si>
-    <t>RESELCCURR</t>
-  </si>
-  <si>
-    <t>RESELCCKNR</t>
-  </si>
-  <si>
-    <t>RESLPGCKNR</t>
-  </si>
-  <si>
-    <t>RESCHACKNR</t>
-  </si>
-  <si>
-    <t>RESBIOCKNIMPR</t>
-  </si>
-  <si>
-    <t>RESBIOCKNR</t>
-  </si>
-  <si>
-    <t>RESELCWTHR</t>
-  </si>
-  <si>
-    <t>RESBIOWTHR</t>
-  </si>
-  <si>
-    <t>RESLPGWTHR</t>
-  </si>
-  <si>
-    <t>RESCHAWTHR</t>
-  </si>
-  <si>
-    <t>RESKERLGTR</t>
-  </si>
-  <si>
-    <t>RESELCLGTR</t>
-  </si>
-  <si>
-    <t>EXPSOY</t>
-  </si>
-  <si>
-    <t>EXPSOR</t>
-  </si>
-  <si>
-    <t>EXPSES</t>
-  </si>
-  <si>
-    <t>EXPRIC</t>
-  </si>
-  <si>
-    <t>EXPVEG</t>
-  </si>
-  <si>
-    <t>IMPRIC</t>
-  </si>
-  <si>
-    <t>IMPSES</t>
-  </si>
-  <si>
-    <t>IMPSOR</t>
-  </si>
-  <si>
-    <t>IMPSOY</t>
-  </si>
-  <si>
-    <t>IMPVEG</t>
-  </si>
-  <si>
-    <t>LNDSORHR</t>
-  </si>
-  <si>
-    <t>LNDSORHI</t>
-  </si>
-  <si>
-    <t>LNDSORLR</t>
-  </si>
-  <si>
-    <t>LNDSORLI</t>
-  </si>
-  <si>
-    <t>LNDSESHR</t>
-  </si>
-  <si>
-    <t>LNDSESHI</t>
-  </si>
-  <si>
-    <t>LNDSESLR</t>
-  </si>
-  <si>
-    <t>LNDSESLI</t>
-  </si>
-  <si>
-    <t>LNDRICHR</t>
-  </si>
-  <si>
-    <t>LNDRICHI</t>
-  </si>
-  <si>
-    <t>LNDRICLR</t>
-  </si>
-  <si>
-    <t>LNDRICLI</t>
-  </si>
-  <si>
-    <t>LNDSOYHR</t>
-  </si>
-  <si>
-    <t>LNDSOYHI</t>
-  </si>
-  <si>
-    <t>LNDSOYLR</t>
-  </si>
-  <si>
-    <t>LNDSOYLI</t>
-  </si>
-  <si>
-    <t>LNDVEGHR</t>
-  </si>
-  <si>
-    <t>LNDVEGHI</t>
-  </si>
-  <si>
-    <t>LNDVEGLR</t>
-  </si>
-  <si>
-    <t>LNDVEGLI</t>
-  </si>
-  <si>
-    <t>GH2COAL</t>
-  </si>
-  <si>
-    <t>GH2NGS</t>
-  </si>
-  <si>
-    <t>BH2NGS</t>
-  </si>
-  <si>
-    <t>GH2ELC</t>
-  </si>
-  <si>
-    <t>PLANTIS</t>
-  </si>
-  <si>
-    <t>INDIRSHFOHTH</t>
-  </si>
-  <si>
-    <t>INDIRSNGSHTHCCS</t>
-  </si>
-  <si>
-    <t>INDIRSHDGDRI</t>
-  </si>
-  <si>
-    <t>INDIRSNGSDRI</t>
-  </si>
-  <si>
-    <t>INDIRSELCEAF</t>
-  </si>
-  <si>
-    <t>INDIRSBIOHTH</t>
-  </si>
-  <si>
-    <t>INDIRSBIOHTHCCS</t>
-  </si>
-  <si>
-    <t>INDIRSCOAHTH</t>
-  </si>
-  <si>
-    <t>INDIRSCOAHTHCCS</t>
-  </si>
-  <si>
-    <t>INDIRSHDGHTH</t>
-  </si>
-  <si>
-    <t>INDIRSNGSHTH</t>
-  </si>
-  <si>
-    <t>PLANTNMM</t>
-  </si>
-  <si>
-    <t>INDWSTKLN</t>
-  </si>
-  <si>
-    <t>INDHFOKLN</t>
-  </si>
-  <si>
-    <t>INDNGSKLNCCS</t>
-  </si>
-  <si>
-    <t>INDNGSKLN</t>
-  </si>
-  <si>
-    <t>INDBIOKLNCCS</t>
-  </si>
-  <si>
-    <t>INDBIOKLN</t>
-  </si>
-  <si>
-    <t>INDCOAKLNCCS</t>
-  </si>
-  <si>
-    <t>INDKLNCOA</t>
-  </si>
-  <si>
-    <t>PWRBATIN</t>
-  </si>
-  <si>
-    <t>PWRBATOUT</t>
-  </si>
-  <si>
-    <t>PWRTRNIMP</t>
-  </si>
-  <si>
-    <t>DEMPWRDSL</t>
-  </si>
-  <si>
-    <t>PWRDSL</t>
-  </si>
-  <si>
-    <t>LWTADA</t>
-  </si>
-  <si>
-    <t>LWTCAR</t>
-  </si>
-  <si>
-    <t>LWTLAG</t>
-  </si>
-  <si>
-    <t>LWTLAT</t>
-  </si>
-  <si>
-    <t>LWTSPT</t>
-  </si>
-  <si>
-    <t>LWTSWR</t>
-  </si>
-  <si>
-    <t>LWTGEN</t>
-  </si>
-  <si>
-    <t>RESELCBSTU</t>
-  </si>
-  <si>
-    <t>COMELCBST</t>
-  </si>
-  <si>
-    <t>RESELCCFFU</t>
-  </si>
-  <si>
-    <t>COMELCCFF</t>
-  </si>
-  <si>
-    <t>TRAELCHTRCUR</t>
-  </si>
-  <si>
-    <t>TRAELCMTRCUR</t>
-  </si>
-  <si>
-    <t>TRAELCLTRCUR</t>
-  </si>
-  <si>
-    <t>TRAELCBUSCUR</t>
-  </si>
-  <si>
-    <t>TRALPGBUSNEW</t>
-  </si>
-  <si>
-    <t>TRAELCMNBCUR</t>
-  </si>
-  <si>
-    <t>TRALPGMNBNEW</t>
-  </si>
-  <si>
-    <t>TRADSLMCYNEW</t>
-  </si>
-  <si>
-    <t>TRAELCMCYCUR</t>
-  </si>
-  <si>
-    <t>TRAELCCARCUR</t>
-  </si>
-  <si>
-    <t>TRALPGCARNEW</t>
-  </si>
-  <si>
-    <t>DEMTRALPG</t>
-  </si>
-  <si>
-    <t>IMPLFO</t>
-  </si>
-  <si>
-    <t>MINWND</t>
-  </si>
-  <si>
-    <t>MINCOA</t>
-  </si>
-  <si>
-    <t>MINNGS</t>
-  </si>
-  <si>
-    <t>PWROHC003</t>
-  </si>
-  <si>
-    <t>DEMPWRWND</t>
-  </si>
-  <si>
-    <t>PWRWND002</t>
-  </si>
-  <si>
-    <t>PWRWND001</t>
-  </si>
-  <si>
-    <t>PWRNGS002</t>
-  </si>
-  <si>
-    <t>PWRNGS001</t>
-  </si>
-  <si>
-    <t>DEMPWRNGS</t>
-  </si>
-  <si>
-    <t>PWROHC002</t>
-  </si>
-  <si>
-    <t>DEMPWRHFO</t>
-  </si>
-  <si>
-    <t>PWRCOA001</t>
-  </si>
-  <si>
-    <t>DEMPWRCOA</t>
-  </si>
-  <si>
-    <t>TRAELCLTRNEW</t>
-  </si>
-  <si>
-    <t>PWRLFG001</t>
-  </si>
-  <si>
-    <t>DEMPWRLFG</t>
-  </si>
-  <si>
-    <t>WSTLFL</t>
-  </si>
-  <si>
-    <t>WSTINC</t>
-  </si>
-  <si>
-    <t>WSTHZD</t>
+    <t>TRARAILP</t>
+  </si>
+  <si>
+    <t>WSTWAT</t>
+  </si>
+  <si>
+    <t>RESWAT</t>
+  </si>
+  <si>
+    <t>OTHWAT</t>
+  </si>
+  <si>
+    <t>GOVWAT</t>
+  </si>
+  <si>
+    <t>MINWAT1</t>
+  </si>
+  <si>
+    <t>INDDSL</t>
+  </si>
+  <si>
+    <t>PWRSOL</t>
+  </si>
+  <si>
+    <t>PWRWND</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>WND</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
+    <t>LWTCOL</t>
+  </si>
+  <si>
+    <t>LWT</t>
+  </si>
+  <si>
+    <t>NGS</t>
+  </si>
+  <si>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>ELC001</t>
+  </si>
+  <si>
+    <t>ELC002</t>
+  </si>
+  <si>
+    <t>BIO</t>
+  </si>
+  <si>
+    <t>COMELCOTH</t>
+  </si>
+  <si>
+    <t>RESELCOTH</t>
+  </si>
+  <si>
+    <t>HFO</t>
+  </si>
+  <si>
+    <t>URN</t>
+  </si>
+  <si>
+    <t>LND</t>
+  </si>
+  <si>
+    <t>CRPMAI</t>
+  </si>
+  <si>
+    <t>CRPSOR</t>
+  </si>
+  <si>
+    <t>CRPMTP</t>
+  </si>
+  <si>
+    <t>CRPPUL</t>
+  </si>
+  <si>
+    <t>LFOR</t>
+  </si>
+  <si>
+    <t>LBLT</t>
+  </si>
+  <si>
+    <t>LWAT</t>
+  </si>
+  <si>
+    <t>LOTH</t>
+  </si>
+  <si>
+    <t>WATPRC</t>
+  </si>
+  <si>
+    <t>AGRWAT2</t>
+  </si>
+  <si>
+    <t>WATEVT</t>
+  </si>
+  <si>
+    <t>WATGWT</t>
+  </si>
+  <si>
+    <t>WATSUR</t>
+  </si>
+  <si>
+    <t>CRPGRO</t>
+  </si>
+  <si>
+    <t>CRPWHE</t>
+  </si>
+  <si>
+    <t>PUBWAT</t>
+  </si>
+  <si>
+    <t>CRPSUN</t>
+  </si>
+  <si>
+    <t>CRPOTC</t>
+  </si>
+  <si>
+    <t>PWRWAT1</t>
+  </si>
+  <si>
+    <t>DSL</t>
+  </si>
+  <si>
+    <t>RESCKN</t>
+  </si>
+  <si>
+    <t>TRAMCY</t>
+  </si>
+  <si>
+    <t>TRACAR</t>
+  </si>
+  <si>
+    <t>TRABUS</t>
+  </si>
+  <si>
+    <t>COMHET</t>
+  </si>
+  <si>
+    <t>RESHEL</t>
+  </si>
+  <si>
+    <t>CRPLND</t>
+  </si>
+  <si>
+    <t>LGRS</t>
+  </si>
+  <si>
+    <t>PSTCU</t>
+  </si>
+  <si>
+    <t>PSTCF</t>
+  </si>
+  <si>
+    <t>LVSCTL</t>
+  </si>
+  <si>
+    <t>LVSSHP</t>
+  </si>
+  <si>
+    <t>LVSGOA</t>
+  </si>
+  <si>
+    <t>INDELC</t>
+  </si>
+  <si>
+    <t>INDCOA</t>
+  </si>
+  <si>
+    <t>INDBIO</t>
+  </si>
+  <si>
+    <t>RESELC</t>
+  </si>
+  <si>
+    <t>RESBIO</t>
+  </si>
+  <si>
+    <t>COMELC</t>
+  </si>
+  <si>
+    <t>COMCOA</t>
+  </si>
+  <si>
+    <t>COMBIO</t>
+  </si>
+  <si>
+    <t>PWRNGS</t>
+  </si>
+  <si>
+    <t>PWRCOA</t>
+  </si>
+  <si>
+    <t>PWRBIO</t>
+  </si>
+  <si>
+    <t>PWRHFO</t>
+  </si>
+  <si>
+    <t>PWRURN</t>
+  </si>
+  <si>
+    <t>TRAELC001</t>
+  </si>
+  <si>
+    <t>TRAGSL</t>
+  </si>
+  <si>
+    <t>GSL</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>KER</t>
+  </si>
+  <si>
+    <t>INDHFO</t>
+  </si>
+  <si>
+    <t>INDMIN</t>
+  </si>
+  <si>
+    <t>INDLPG</t>
+  </si>
+  <si>
+    <t>COMDSL</t>
+  </si>
+  <si>
+    <t>RESLPG</t>
+  </si>
+  <si>
+    <t>RESKER</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>RESLGT</t>
+  </si>
+  <si>
+    <t>RESCOL</t>
+  </si>
+  <si>
+    <t>TRAAVI</t>
+  </si>
+  <si>
+    <t>TRAJETKER</t>
+  </si>
+  <si>
+    <t>RESDSL</t>
+  </si>
+  <si>
+    <t>RESWHT</t>
+  </si>
+  <si>
+    <t>RESSOL</t>
+  </si>
+  <si>
+    <t>COMLPG</t>
+  </si>
+  <si>
+    <t>TRAMNB</t>
+  </si>
+  <si>
+    <t>TRALTR</t>
+  </si>
+  <si>
+    <t>TRAMTR</t>
+  </si>
+  <si>
+    <t>TRAHTR</t>
+  </si>
+  <si>
+    <t>DUMLND</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>WSTCLT</t>
+  </si>
+  <si>
+    <t>WSTRES</t>
+  </si>
+  <si>
+    <t>WSTMET</t>
+  </si>
+  <si>
+    <t>WSTPPR</t>
+  </si>
+  <si>
+    <t>WSTPLA</t>
   </si>
   <si>
     <t>WSTGLS</t>
   </si>
   <si>
-    <t>WSTPLR</t>
-  </si>
-  <si>
-    <t>WSTPAR</t>
-  </si>
-  <si>
-    <t>WSTMTR</t>
-  </si>
-  <si>
-    <t>WSTCMP</t>
-  </si>
-  <si>
-    <t>WSTDGS</t>
-  </si>
-  <si>
-    <t>WSTSEP</t>
-  </si>
-  <si>
-    <t>WSTORG</t>
-  </si>
-  <si>
-    <t>WSTUNS</t>
-  </si>
-  <si>
-    <t>WSTCOL</t>
-  </si>
-  <si>
-    <t>WSTDMP</t>
-  </si>
-  <si>
-    <t>WSTOPB</t>
-  </si>
-  <si>
-    <t>WSTGEN</t>
-  </si>
-  <si>
-    <t>LNDWET</t>
-  </si>
-  <si>
-    <t>DEFOR</t>
-  </si>
-  <si>
-    <t>REFOR</t>
-  </si>
-  <si>
-    <t>DUMLUC</t>
-  </si>
-  <si>
-    <t>MINHYD</t>
-  </si>
-  <si>
-    <t>PWRHYD001</t>
-  </si>
-  <si>
-    <t>PWRTRN</t>
-  </si>
-  <si>
-    <t>DEMINDELC</t>
-  </si>
-  <si>
-    <t>DEMRESELC</t>
-  </si>
-  <si>
-    <t>DEMCOMELC</t>
-  </si>
-  <si>
-    <t>PWRHYD002</t>
-  </si>
-  <si>
-    <t>PWRHYD003</t>
-  </si>
-  <si>
-    <t>PWRHYD004</t>
-  </si>
-  <si>
-    <t>IMPHFO</t>
-  </si>
-  <si>
-    <t>UPSREF001</t>
-  </si>
-  <si>
-    <t>UPSREF002</t>
-  </si>
-  <si>
-    <t>MINSOL</t>
-  </si>
-  <si>
-    <t>PWRSOL001</t>
-  </si>
-  <si>
-    <t>PWRSOL002</t>
-  </si>
-  <si>
-    <t>MINGEO</t>
-  </si>
-  <si>
-    <t>PWRGEO001</t>
-  </si>
-  <si>
-    <t>MINBIO</t>
-  </si>
-  <si>
-    <t>PWRBIO001</t>
-  </si>
-  <si>
-    <t>PWRTRNEXP</t>
-  </si>
-  <si>
-    <t>PWRCSP001</t>
-  </si>
-  <si>
-    <t>RSCLND</t>
-  </si>
-  <si>
-    <t>LNDPLAHR</t>
-  </si>
-  <si>
-    <t>LNDPLAHI</t>
-  </si>
-  <si>
-    <t>LNDPLALR</t>
-  </si>
-  <si>
-    <t>LNDPLALI</t>
-  </si>
-  <si>
-    <t>LNDMAIHR</t>
-  </si>
-  <si>
-    <t>LNDMAIHI</t>
-  </si>
-  <si>
-    <t>LNDMAILR</t>
-  </si>
-  <si>
-    <t>LNDMAILI</t>
-  </si>
-  <si>
-    <t>LNDCASHR</t>
-  </si>
-  <si>
-    <t>LNDCASHI</t>
-  </si>
-  <si>
-    <t>LNDCASLR</t>
-  </si>
-  <si>
-    <t>LNDCASLI</t>
-  </si>
-  <si>
-    <t>LNDBEAHR</t>
-  </si>
-  <si>
-    <t>LNDBEAHI</t>
-  </si>
-  <si>
-    <t>LNDBEALR</t>
-  </si>
-  <si>
-    <t>LNDBEALI</t>
-  </si>
-  <si>
-    <t>LNDCOFHR</t>
-  </si>
-  <si>
-    <t>LNDCOFHI</t>
-  </si>
-  <si>
-    <t>LNDCOFLR</t>
-  </si>
-  <si>
-    <t>LNDCOFLI</t>
-  </si>
-  <si>
-    <t>LNDGROHR</t>
-  </si>
-  <si>
-    <t>LNDGROHI</t>
-  </si>
-  <si>
-    <t>LNDGROLR</t>
-  </si>
-  <si>
-    <t>LNDGROLI</t>
-  </si>
-  <si>
-    <t>LNDSUNHR</t>
-  </si>
-  <si>
-    <t>LNDSUNHI</t>
-  </si>
-  <si>
-    <t>LNDSUNLR</t>
-  </si>
-  <si>
-    <t>LNDSUNLI</t>
-  </si>
-  <si>
-    <t>LNDOTCHR</t>
-  </si>
-  <si>
-    <t>LNDOTCHI</t>
-  </si>
-  <si>
-    <t>LNDOTCLR</t>
-  </si>
-  <si>
-    <t>LNDOTCLI</t>
-  </si>
-  <si>
-    <t>LNDPTSHR</t>
-  </si>
-  <si>
-    <t>LNDPTSHI</t>
-  </si>
-  <si>
-    <t>LNDPTSLR</t>
-  </si>
-  <si>
-    <t>LNDPTSLI</t>
-  </si>
-  <si>
-    <t>LNDFOR</t>
-  </si>
-  <si>
-    <t>LNDBLT</t>
-  </si>
-  <si>
-    <t>LNDWAT</t>
-  </si>
-  <si>
-    <t>OTHLND</t>
-  </si>
-  <si>
-    <t>IMPPLA</t>
-  </si>
-  <si>
-    <t>IMPMAI</t>
-  </si>
-  <si>
-    <t>IMPCAS</t>
-  </si>
-  <si>
-    <t>IMPBEA</t>
-  </si>
-  <si>
-    <t>IMPCOF</t>
-  </si>
-  <si>
-    <t>IMPSUN</t>
-  </si>
-  <si>
-    <t>IMPOTC</t>
-  </si>
-  <si>
-    <t>MINPRC</t>
-  </si>
-  <si>
-    <t>DEMAGRSURWAT</t>
-  </si>
-  <si>
-    <t>DEMAGRGWTWAT</t>
-  </si>
-  <si>
-    <t>DEMPUBSURWAT</t>
-  </si>
-  <si>
-    <t>DEMPUBGWTWAT</t>
-  </si>
-  <si>
-    <t>DEMPWRSURWAT</t>
-  </si>
-  <si>
-    <t>DEMPWRGWTWAT</t>
-  </si>
-  <si>
-    <t>IMPDSL</t>
-  </si>
-  <si>
-    <t>DEMAGRDSL</t>
-  </si>
-  <si>
-    <t>RESELCCKNU</t>
-  </si>
-  <si>
-    <t>COMELCHEL</t>
-  </si>
-  <si>
-    <t>LNDCRP</t>
-  </si>
-  <si>
-    <t>EXPPLA</t>
-  </si>
-  <si>
-    <t>EXPMAI</t>
-  </si>
-  <si>
-    <t>EXPCAS</t>
-  </si>
-  <si>
-    <t>EXPBEA</t>
-  </si>
-  <si>
-    <t>EXPCOF</t>
-  </si>
-  <si>
-    <t>EXPGRO</t>
-  </si>
-  <si>
-    <t>EXPPTS</t>
-  </si>
-  <si>
-    <t>EXPSUN</t>
-  </si>
-  <si>
-    <t>EXPOTC</t>
-  </si>
-  <si>
-    <t>LNDGRA</t>
-  </si>
-  <si>
-    <t>PST001</t>
-  </si>
-  <si>
-    <t>PST002</t>
-  </si>
-  <si>
-    <t>LVSCTLCUR</t>
-  </si>
-  <si>
-    <t>LVSSHPCUR</t>
-  </si>
-  <si>
-    <t>LVSGOACUR</t>
-  </si>
-  <si>
-    <t>LNDSHR</t>
-  </si>
-  <si>
-    <t>DEMPWRBIO</t>
-  </si>
-  <si>
-    <t>DEMPWRHYD</t>
-  </si>
-  <si>
-    <t>DEMPWRSOL</t>
-  </si>
-  <si>
-    <t>DEMPWRGEO</t>
-  </si>
-  <si>
-    <t>COMELCCUR</t>
-  </si>
-  <si>
-    <t>RESELCCURU</t>
-  </si>
-  <si>
-    <t>DEMINDDSL</t>
-  </si>
-  <si>
-    <t>DEMINDGSL</t>
-  </si>
-  <si>
-    <t>DEMINDKER</t>
-  </si>
-  <si>
-    <t>DEMCOMLPG</t>
-  </si>
-  <si>
-    <t>DEMRESLPG</t>
-  </si>
-  <si>
-    <t>DEMRESKER</t>
-  </si>
-  <si>
-    <t>COMLPGHEL</t>
-  </si>
-  <si>
-    <t>RESLPGCKNU</t>
-  </si>
-  <si>
-    <t>RESKERLGTU</t>
-  </si>
-  <si>
-    <t>RESELCLGTU</t>
-  </si>
-  <si>
-    <t>DEMRESCHA</t>
-  </si>
-  <si>
-    <t>RESELCCOLU</t>
-  </si>
-  <si>
-    <t>DEMCOMCHA</t>
-  </si>
-  <si>
-    <t>RESCHACKNU</t>
-  </si>
-  <si>
-    <t>IMPGSL</t>
-  </si>
-  <si>
-    <t>IMPLPG</t>
-  </si>
-  <si>
-    <t>IMPKER</t>
-  </si>
-  <si>
-    <t>MINCHA</t>
-  </si>
-  <si>
-    <t>RESBIOSPHR</t>
-  </si>
-  <si>
-    <t>RESELCWTHU</t>
-  </si>
-  <si>
-    <t>RESBIOWTHU</t>
-  </si>
-  <si>
-    <t>RESLPGWTHU</t>
-  </si>
-  <si>
-    <t>RESCHAWTHU</t>
-  </si>
-  <si>
-    <t>XRESCKNU</t>
-  </si>
-  <si>
-    <t>XRESELCOTH</t>
-  </si>
-  <si>
-    <t>XRESLGTU</t>
-  </si>
-  <si>
-    <t>XRESCOLU</t>
-  </si>
-  <si>
-    <t>XRESSPHR</t>
-  </si>
-  <si>
-    <t>XRESWTHU</t>
-  </si>
-  <si>
-    <t>XCOMHEL</t>
-  </si>
-  <si>
-    <t>XCOMELCOTH</t>
-  </si>
-  <si>
-    <t>RESBIOCKNU</t>
-  </si>
-  <si>
-    <t>RESBGSCKNR</t>
-  </si>
-  <si>
-    <t>COMBIOHEL</t>
-  </si>
-  <si>
-    <t>COMCHAHEL</t>
-  </si>
-  <si>
-    <t>COMBGSHEL</t>
-  </si>
-  <si>
-    <t>DEMRESBIO</t>
-  </si>
-  <si>
-    <t>DEMRESBGS</t>
-  </si>
-  <si>
-    <t>DEMCOMBIO</t>
-  </si>
-  <si>
-    <t>DEMCOMBGS</t>
-  </si>
-  <si>
-    <t>DEMINDCHA</t>
-  </si>
-  <si>
-    <t>RESBIOCKNIMPU</t>
-  </si>
-  <si>
-    <t>DEMINDBIO</t>
-  </si>
-  <si>
-    <t>DEMTRAELC</t>
-  </si>
-  <si>
-    <t>TRAELCCARNEW</t>
-  </si>
-  <si>
-    <t>DEMTRADSL</t>
-  </si>
-  <si>
-    <t>TRADSLCARCUR</t>
-  </si>
-  <si>
-    <t>DEMTRAGSL</t>
-  </si>
-  <si>
-    <t>TRAGSLCARCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLCARNEW</t>
-  </si>
-  <si>
-    <t>TRADSLCARNEW</t>
-  </si>
-  <si>
-    <t>TRAGSLCARHYBNEW</t>
-  </si>
-  <si>
-    <t>TRADSLBUSCUR</t>
-  </si>
-  <si>
-    <t>TRADSLBUSNEW</t>
-  </si>
-  <si>
-    <t>TRAELCBUSNEW</t>
-  </si>
-  <si>
-    <t>TRADSHBUSNEW</t>
-  </si>
-  <si>
-    <t>TRADSLMNBCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLMNBCUR</t>
-  </si>
-  <si>
-    <t>TRADSLMNBNEW</t>
-  </si>
-  <si>
-    <t>TRAGSLMNBNEW</t>
-  </si>
-  <si>
-    <t>TRADSHMNBNEW</t>
-  </si>
-  <si>
-    <t>TRAELCMNBNEW</t>
-  </si>
-  <si>
-    <t>TRAGSLMCYCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLMCYNEW</t>
-  </si>
-  <si>
-    <t>TRAELCMCYNEW</t>
-  </si>
-  <si>
-    <t>TRAGSLLTRCUR</t>
-  </si>
-  <si>
-    <t>TRADSLLTRCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLLTRNEW</t>
-  </si>
-  <si>
-    <t>TRADSLLTRNEW</t>
-  </si>
-  <si>
-    <t>TRADSHLTRNEW</t>
-  </si>
-  <si>
-    <t>TRADSLMTRCUR</t>
-  </si>
-  <si>
-    <t>TRADSLMTRNEW</t>
-  </si>
-  <si>
-    <t>TRAELCMTRNEW</t>
-  </si>
-  <si>
-    <t>TRADSLHTRCUR</t>
-  </si>
-  <si>
-    <t>TRADSLHTRNEW</t>
-  </si>
-  <si>
-    <t>TRAELCHTRNEW</t>
-  </si>
-  <si>
-    <t>DEMTRAKER</t>
-  </si>
-  <si>
-    <t>DEMAGRELC</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>PETLND</t>
-  </si>
-  <si>
-    <t>INDOTHHTH</t>
-  </si>
-  <si>
-    <t>INDOTHMDR</t>
-  </si>
-  <si>
-    <t>OTH</t>
-  </si>
-  <si>
-    <t>INDMTRHTH</t>
-  </si>
-  <si>
-    <t>INDMTRMDR</t>
-  </si>
-  <si>
-    <t>MTR</t>
-  </si>
-  <si>
-    <t>INDCHMHTH</t>
-  </si>
-  <si>
-    <t>CHM</t>
-  </si>
-  <si>
-    <t>FBT</t>
-  </si>
-  <si>
-    <t>INDFBTHTH</t>
-  </si>
-  <si>
-    <t>INDHDG</t>
-  </si>
-  <si>
-    <t>FSH</t>
-  </si>
-  <si>
-    <t>INDWST</t>
-  </si>
-  <si>
-    <t>INDCOA</t>
-  </si>
-  <si>
-    <t>INDNGS</t>
-  </si>
-  <si>
-    <t>INDHFO</t>
-  </si>
-  <si>
-    <t>CEM</t>
-  </si>
-  <si>
-    <t>FER</t>
-  </si>
-  <si>
-    <t>AGRMCH</t>
-  </si>
-  <si>
-    <t>TRAPRL</t>
-  </si>
-  <si>
-    <t>TRAFRL</t>
-  </si>
-  <si>
-    <t>TRANAV</t>
-  </si>
-  <si>
-    <t>TRAAVI</t>
-  </si>
-  <si>
-    <t>RESELCOTHR</t>
-  </si>
-  <si>
-    <t>RESLGTR</t>
-  </si>
-  <si>
-    <t>RESCKNR</t>
-  </si>
-  <si>
-    <t>RESWTHR</t>
-  </si>
-  <si>
-    <t>CRPSOY</t>
-  </si>
-  <si>
-    <t>CRPSOR</t>
-  </si>
-  <si>
-    <t>CRPSES</t>
-  </si>
-  <si>
-    <t>CRPVEG</t>
-  </si>
-  <si>
-    <t>CRPRIC</t>
-  </si>
-  <si>
-    <t>HDG</t>
-  </si>
-  <si>
-    <t>INDIRSHTH</t>
-  </si>
-  <si>
-    <t>INDSCR</t>
-  </si>
-  <si>
-    <t>INDSTL</t>
-  </si>
-  <si>
-    <t>STL</t>
-  </si>
-  <si>
-    <t>NMM</t>
-  </si>
-  <si>
-    <t>CLK</t>
-  </si>
-  <si>
-    <t>CSP</t>
-  </si>
-  <si>
-    <t>LWTCOL</t>
-  </si>
-  <si>
-    <t>LWT</t>
-  </si>
-  <si>
-    <t>TRALPG</t>
-  </si>
-  <si>
-    <t>PWRWND</t>
-  </si>
-  <si>
-    <t>PWRLFO</t>
-  </si>
-  <si>
-    <t>WND</t>
-  </si>
-  <si>
-    <t>LFO</t>
+    <t>WSTHAZ</t>
+  </si>
+  <si>
+    <t>WSTHET</t>
+  </si>
+  <si>
+    <t>LFG</t>
   </si>
   <si>
     <t>PWRLFG</t>
   </si>
   <si>
-    <t>LFG</t>
-  </si>
-  <si>
-    <t>WSTHET</t>
-  </si>
-  <si>
-    <t>WSTHAZ</t>
-  </si>
-  <si>
-    <t>WSTPLA</t>
-  </si>
-  <si>
-    <t>WSTPPR</t>
-  </si>
-  <si>
-    <t>WSTMET</t>
-  </si>
-  <si>
-    <t>WSTRES</t>
-  </si>
-  <si>
-    <t>WSTCLT</t>
-  </si>
-  <si>
-    <t>WETLND</t>
-  </si>
-  <si>
-    <t>DUM</t>
-  </si>
-  <si>
-    <t>DUM2</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>ELC001</t>
-  </si>
-  <si>
-    <t>ELC002</t>
-  </si>
-  <si>
-    <t>ELC003</t>
-  </si>
-  <si>
-    <t>INDELC</t>
-  </si>
-  <si>
-    <t>RESELC</t>
-  </si>
-  <si>
-    <t>COMELC</t>
-  </si>
-  <si>
-    <t>HFO</t>
-  </si>
-  <si>
-    <t>OIL</t>
-  </si>
-  <si>
-    <t>COA</t>
-  </si>
-  <si>
-    <t>NGS</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>GEO</t>
-  </si>
-  <si>
-    <t>BIO</t>
-  </si>
-  <si>
-    <t>LND</t>
-  </si>
-  <si>
-    <t>CRPPLA</t>
-  </si>
-  <si>
-    <t>CRPMAI</t>
-  </si>
-  <si>
-    <t>CRPCAS</t>
-  </si>
-  <si>
-    <t>CRPBEA</t>
-  </si>
-  <si>
-    <t>CRPCOF</t>
-  </si>
-  <si>
-    <t>CRPGRO</t>
-  </si>
-  <si>
-    <t>CRPPTS</t>
-  </si>
-  <si>
-    <t>CRPSUN</t>
-  </si>
-  <si>
-    <t>CRPOTC</t>
-  </si>
-  <si>
-    <t>LFOR</t>
-  </si>
-  <si>
-    <t>LBLT</t>
-  </si>
-  <si>
-    <t>LWAT</t>
-  </si>
-  <si>
-    <t>LOTH</t>
-  </si>
-  <si>
-    <t>WTRPRC</t>
-  </si>
-  <si>
-    <t>AGRWAT</t>
-  </si>
-  <si>
-    <t>WTREVT</t>
-  </si>
-  <si>
-    <t>WTRGWT</t>
-  </si>
-  <si>
-    <t>WTRSUR</t>
-  </si>
-  <si>
-    <t>PUBWAT</t>
-  </si>
-  <si>
-    <t>PWRWAT</t>
-  </si>
-  <si>
-    <t>DSL</t>
-  </si>
-  <si>
-    <t>AGRDSL</t>
-  </si>
-  <si>
-    <t>RESCKNU</t>
-  </si>
-  <si>
-    <t>COMHEL</t>
-  </si>
-  <si>
-    <t>CRPLND</t>
-  </si>
-  <si>
-    <t>GRALND</t>
-  </si>
-  <si>
-    <t>SHRLND</t>
-  </si>
-  <si>
-    <t>PSTCU</t>
-  </si>
-  <si>
-    <t>PSTCF</t>
-  </si>
-  <si>
-    <t>CTL</t>
-  </si>
-  <si>
-    <t>SHP</t>
-  </si>
-  <si>
-    <t>GOA</t>
-  </si>
-  <si>
-    <t>PWRCOA</t>
-  </si>
-  <si>
-    <t>INDBIO</t>
-  </si>
-  <si>
-    <t>PWRBIO</t>
-  </si>
-  <si>
-    <t>PWRHYD</t>
-  </si>
-  <si>
-    <t>PWRHFO</t>
-  </si>
-  <si>
-    <t>PWRNGS</t>
-  </si>
-  <si>
-    <t>PWRSOL</t>
-  </si>
-  <si>
-    <t>PWRGEO</t>
-  </si>
-  <si>
-    <t>PWROIL</t>
-  </si>
-  <si>
-    <t>COMHEH</t>
-  </si>
-  <si>
-    <t>PWRCSP</t>
-  </si>
-  <si>
-    <t>COMELCOTH</t>
-  </si>
-  <si>
-    <t>RESELCOTHU</t>
-  </si>
-  <si>
-    <t>GSL</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>KER</t>
-  </si>
-  <si>
-    <t>INDDSL</t>
-  </si>
-  <si>
-    <t>INDGSL</t>
-  </si>
-  <si>
-    <t>INDKER</t>
-  </si>
-  <si>
-    <t>COMDSL</t>
-  </si>
-  <si>
-    <t>COMLPG</t>
-  </si>
-  <si>
-    <t>RESLPG</t>
-  </si>
-  <si>
-    <t>RESKER</t>
-  </si>
-  <si>
-    <t>AGRGSL</t>
-  </si>
-  <si>
-    <t>RESLGTU</t>
-  </si>
-  <si>
-    <t>RESCOLU</t>
-  </si>
-  <si>
-    <t>CHA</t>
-  </si>
-  <si>
-    <t>RESCHA</t>
-  </si>
-  <si>
-    <t>COMCHA</t>
-  </si>
-  <si>
-    <t>RESSPHR</t>
-  </si>
-  <si>
-    <t>RESWTHU</t>
-  </si>
-  <si>
-    <t>COMCOA</t>
-  </si>
-  <si>
     <t>BGS</t>
   </si>
   <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>RIH</t>
-  </si>
-  <si>
     <t>RESBGS</t>
   </si>
   <si>
-    <t>RESBIO</t>
-  </si>
-  <si>
-    <t>INDCHA</t>
-  </si>
-  <si>
-    <t>COMBIO</t>
-  </si>
-  <si>
-    <t>COMBGS</t>
-  </si>
-  <si>
-    <t>TRAELC</t>
-  </si>
-  <si>
-    <t>TRACAR</t>
-  </si>
-  <si>
-    <t>TRAGSL</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>TRABUS</t>
-  </si>
-  <si>
-    <t>TRAMNB</t>
-  </si>
-  <si>
-    <t>TRAMCY</t>
-  </si>
-  <si>
-    <t>TRALTR</t>
-  </si>
-  <si>
-    <t>TRAMTR</t>
-  </si>
-  <si>
-    <t>TRAHTR</t>
-  </si>
-  <si>
-    <t>TRAKER</t>
-  </si>
-  <si>
-    <t>AGRELC</t>
+    <t>TRARAILF</t>
+  </si>
+  <si>
+    <t>TRAELC002</t>
   </si>
   <si>
     <t>CO2</t>
@@ -1782,12 +1647,36 @@
     <t>CH4</t>
   </si>
   <si>
-    <t>N2O</t>
+    <t>N20</t>
   </si>
   <si>
     <t>CO2eq</t>
   </si>
   <si>
+    <t>LVSCO2eq</t>
+  </si>
+  <si>
+    <t>WSTCH4</t>
+  </si>
+  <si>
+    <t>EXTIAP</t>
+  </si>
+  <si>
+    <t>EXTSNT</t>
+  </si>
+  <si>
+    <t>EXTCGS</t>
+  </si>
+  <si>
+    <t>EXTACC</t>
+  </si>
+  <si>
+    <t>EXTLAP</t>
+  </si>
+  <si>
+    <t>EXTWST</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -1803,7 +1692,19 @@
     <t>4</t>
   </si>
   <si>
-    <t>STGBAT</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>STOBAT</t>
   </si>
   <si>
     <t>FORBAL</t>
@@ -1824,43 +1725,34 @@
     <t>ORGWST</t>
   </si>
   <si>
-    <t>RESELCCKGBALU</t>
-  </si>
-  <si>
-    <t>RESELCCURBALU</t>
-  </si>
-  <si>
-    <t>RESELCEFFBALU</t>
-  </si>
-  <si>
-    <t>RESELCBSTBALU</t>
-  </si>
-  <si>
-    <t>COMELCCURBAL</t>
-  </si>
-  <si>
-    <t>COMELCHELBAL</t>
+    <t>COMELCBSTBAL</t>
   </si>
   <si>
     <t>COMELCEFFBAL</t>
   </si>
   <si>
-    <t>COMELCBSTBAL</t>
-  </si>
-  <si>
-    <t>INDELCCURBAL</t>
-  </si>
-  <si>
-    <t>INDELCHEHBAL</t>
-  </si>
-  <si>
-    <t>INDELCHELBAL</t>
-  </si>
-  <si>
-    <t>INDELCEFFBAL</t>
-  </si>
-  <si>
-    <t>INDELCBSTBAL</t>
+    <t>RESELCBSTBAL</t>
+  </si>
+  <si>
+    <t>RESELCEFFBAL</t>
+  </si>
+  <si>
+    <t>RESELCCOLBAL</t>
+  </si>
+  <si>
+    <t>RESELCHELBAL</t>
+  </si>
+  <si>
+    <t>RESELCLGTBAL</t>
+  </si>
+  <si>
+    <t>RESELCWHTBAL</t>
+  </si>
+  <si>
+    <t>RESELCCKNBAL</t>
+  </si>
+  <si>
+    <t>RESELCCURBAL</t>
   </si>
   <si>
     <t>TOTLWT</t>
@@ -1869,40 +1761,115 @@
     <t>COLLWT</t>
   </si>
   <si>
+    <t>PWRREN</t>
+  </si>
+  <si>
+    <t>TRAMCYCAP</t>
+  </si>
+  <si>
+    <t>TRACARCAP</t>
+  </si>
+  <si>
+    <t>TRAMNBCAP</t>
+  </si>
+  <si>
+    <t>TRABUSCAP</t>
+  </si>
+  <si>
+    <t>TRARAILFCAP</t>
+  </si>
+  <si>
+    <t>TRALTRCAP</t>
+  </si>
+  <si>
     <t>RESMAR</t>
   </si>
   <si>
-    <t>RESELCCKGBALR</t>
-  </si>
-  <si>
-    <t>RESELCCURBALR</t>
-  </si>
-  <si>
-    <t>RESCKNCLNU</t>
-  </si>
-  <si>
-    <t>RESCKNCLNR</t>
-  </si>
-  <si>
-    <t>RESWTHCLU</t>
-  </si>
-  <si>
-    <t>RESWTHCLR</t>
-  </si>
-  <si>
-    <t>NEWCAPCAR</t>
-  </si>
-  <si>
-    <t>FALLND</t>
-  </si>
-  <si>
-    <t>EVCHRG001</t>
-  </si>
-  <si>
-    <t>EVCHRG002</t>
-  </si>
-  <si>
-    <t>EVCHRG003</t>
+    <t>DEMAGRWATSHARE</t>
+  </si>
+  <si>
+    <t>DEMPWRWATSHARE</t>
+  </si>
+  <si>
+    <t>DEMMINWATSHARE</t>
+  </si>
+  <si>
+    <t>IRRIGSHARE</t>
+  </si>
+  <si>
+    <t>WETBAL</t>
+  </si>
+  <si>
+    <t>REWETBAL</t>
+  </si>
+  <si>
+    <t>TOTLND</t>
+  </si>
+  <si>
+    <t>CRPOTHBAL</t>
+  </si>
+  <si>
+    <t>DEFORBAL</t>
+  </si>
+  <si>
+    <t>LNDGRSBAL</t>
+  </si>
+  <si>
+    <t>2TRACAREVCAP</t>
+  </si>
+  <si>
+    <t>2TRAMCYEVCAP</t>
+  </si>
+  <si>
+    <t>2TRAMNBEVCAP</t>
+  </si>
+  <si>
+    <t>2TRABUSEVCAP</t>
+  </si>
+  <si>
+    <t>2TRALTREVCAP</t>
+  </si>
+  <si>
+    <t>2TRAMTREVCAP</t>
+  </si>
+  <si>
+    <t>2TRAHTREVCAP</t>
+  </si>
+  <si>
+    <t>RECWST</t>
+  </si>
+  <si>
+    <t>RESTRICTWAT</t>
+  </si>
+  <si>
+    <t>TRADSLHTRCURCAP</t>
+  </si>
+  <si>
+    <t>TRADSLHTRNEWCAP</t>
+  </si>
+  <si>
+    <t>TRAELCHTRCURCAP</t>
+  </si>
+  <si>
+    <t>TRAELCHTRNEWCAP</t>
+  </si>
+  <si>
+    <t>TRADSLMTRCURCAP</t>
+  </si>
+  <si>
+    <t>TRADSLMTRNEWCAP</t>
+  </si>
+  <si>
+    <t>TRAELCMTRCURCAP</t>
+  </si>
+  <si>
+    <t>TRAELCMTRNEWCAP</t>
+  </si>
+  <si>
+    <t>TRABUSACTCAP</t>
+  </si>
+  <si>
+    <t>INDOTHLPHELCSHARE</t>
   </si>
   <si>
     <t>category</t>
@@ -2684,7 +2651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O391"/>
+  <dimension ref="A1:O360"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2786,19 +2753,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C3">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2813,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -2825,562 +2792,616 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="B4">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
       <c r="E4" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="F4" t="s">
-        <v>586</v>
+        <v>541</v>
       </c>
       <c r="G4" t="s">
-        <v>590</v>
+        <v>553</v>
       </c>
       <c r="H4" t="s">
-        <v>591</v>
+        <v>554</v>
       </c>
       <c r="I4" t="s">
-        <v>590</v>
+        <v>553</v>
       </c>
       <c r="J4" t="s">
-        <v>590</v>
+        <v>553</v>
       </c>
       <c r="K4" t="s">
-        <v>590</v>
+        <v>553</v>
       </c>
       <c r="L4" t="s">
-        <v>595</v>
+        <v>562</v>
       </c>
       <c r="M4" t="s">
-        <v>595</v>
+        <v>562</v>
       </c>
       <c r="O4" t="s">
-        <v>596</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>420</v>
+        <v>389</v>
       </c>
       <c r="E5" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="F5" t="s">
-        <v>587</v>
+        <v>542</v>
       </c>
       <c r="I5" t="s">
-        <v>592</v>
+        <v>555</v>
       </c>
       <c r="K5" t="s">
-        <v>592</v>
+        <v>555</v>
       </c>
       <c r="O5" t="s">
-        <v>597</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="E6" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="F6" t="s">
-        <v>588</v>
+        <v>543</v>
       </c>
       <c r="K6" t="s">
-        <v>593</v>
+        <v>556</v>
       </c>
       <c r="O6" t="s">
-        <v>598</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="B7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>422</v>
+        <v>391</v>
       </c>
       <c r="E7" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="F7" t="s">
-        <v>589</v>
+        <v>544</v>
       </c>
       <c r="K7" t="s">
-        <v>594</v>
+        <v>557</v>
       </c>
       <c r="O7" t="s">
-        <v>599</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>423</v>
+        <v>392</v>
       </c>
       <c r="E8" t="s">
-        <v>431</v>
+        <v>400</v>
+      </c>
+      <c r="F8" t="s">
+        <v>545</v>
+      </c>
+      <c r="K8" t="s">
+        <v>558</v>
       </c>
       <c r="O8" t="s">
-        <v>600</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="E9" t="s">
-        <v>432</v>
+        <v>401</v>
+      </c>
+      <c r="F9" t="s">
+        <v>546</v>
+      </c>
+      <c r="K9" t="s">
+        <v>559</v>
       </c>
       <c r="O9" t="s">
-        <v>601</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
       <c r="E10" t="s">
-        <v>433</v>
+        <v>402</v>
+      </c>
+      <c r="F10" t="s">
+        <v>547</v>
+      </c>
+      <c r="K10" t="s">
+        <v>560</v>
       </c>
       <c r="O10" t="s">
-        <v>602</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="E11" t="s">
-        <v>434</v>
+        <v>403</v>
+      </c>
+      <c r="F11" t="s">
+        <v>548</v>
+      </c>
+      <c r="K11" t="s">
+        <v>561</v>
       </c>
       <c r="O11" t="s">
-        <v>603</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>435</v>
+        <v>404</v>
+      </c>
+      <c r="F12" t="s">
+        <v>549</v>
       </c>
       <c r="O12" t="s">
-        <v>604</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>436</v>
+        <v>405</v>
+      </c>
+      <c r="F13" t="s">
+        <v>550</v>
       </c>
       <c r="O13" t="s">
-        <v>605</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="B14">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="s">
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>437</v>
+        <v>406</v>
+      </c>
+      <c r="F14" t="s">
+        <v>551</v>
       </c>
       <c r="O14" t="s">
-        <v>606</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="B15">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="C15" t="s">
         <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>438</v>
+        <v>407</v>
+      </c>
+      <c r="F15" t="s">
+        <v>552</v>
       </c>
       <c r="O15" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="B16">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="C16" t="s">
         <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>439</v>
+        <v>408</v>
       </c>
       <c r="O16" t="s">
-        <v>608</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="2:15">
       <c r="B17">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="C17" t="s">
         <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>440</v>
+        <v>409</v>
       </c>
       <c r="O17" t="s">
-        <v>609</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="2:15">
       <c r="B18">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="C18" t="s">
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="O18" t="s">
-        <v>610</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" spans="2:15">
       <c r="B19">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
       </c>
       <c r="E19" t="s">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="O19" t="s">
-        <v>611</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" spans="2:15">
       <c r="B20">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="C20" t="s">
         <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>443</v>
+        <v>412</v>
       </c>
       <c r="O20" t="s">
-        <v>612</v>
+        <v>579</v>
       </c>
     </row>
     <row r="21" spans="2:15">
       <c r="B21">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="C21" t="s">
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="O21" t="s">
-        <v>613</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="2:15">
       <c r="B22">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="C22" t="s">
         <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>445</v>
+        <v>414</v>
       </c>
       <c r="O22" t="s">
-        <v>614</v>
+        <v>581</v>
       </c>
     </row>
     <row r="23" spans="2:15">
       <c r="B23">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="C23" t="s">
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>446</v>
+        <v>415</v>
       </c>
       <c r="O23" t="s">
-        <v>615</v>
+        <v>582</v>
       </c>
     </row>
     <row r="24" spans="2:15">
       <c r="B24">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="C24" t="s">
         <v>51</v>
       </c>
       <c r="E24" t="s">
-        <v>447</v>
+        <v>416</v>
       </c>
       <c r="O24" t="s">
-        <v>616</v>
+        <v>583</v>
       </c>
     </row>
     <row r="25" spans="2:15">
       <c r="B25">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="C25" t="s">
         <v>52</v>
       </c>
       <c r="E25" t="s">
-        <v>448</v>
+        <v>417</v>
       </c>
       <c r="O25" t="s">
-        <v>617</v>
+        <v>584</v>
       </c>
     </row>
     <row r="26" spans="2:15">
       <c r="B26">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="C26" t="s">
         <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="O26" t="s">
-        <v>618</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="2:15">
       <c r="B27">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="C27" t="s">
         <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>450</v>
+        <v>419</v>
       </c>
       <c r="O27" t="s">
-        <v>619</v>
+        <v>586</v>
       </c>
     </row>
     <row r="28" spans="2:15">
       <c r="B28">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C28" t="s">
         <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>451</v>
+        <v>420</v>
       </c>
       <c r="O28" t="s">
-        <v>350</v>
+        <v>587</v>
       </c>
     </row>
     <row r="29" spans="2:15">
       <c r="B29">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="C29" t="s">
         <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>452</v>
+        <v>421</v>
       </c>
       <c r="O29" t="s">
-        <v>116</v>
+        <v>588</v>
       </c>
     </row>
     <row r="30" spans="2:15">
       <c r="B30">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="C30" t="s">
         <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>453</v>
+        <v>422</v>
       </c>
       <c r="O30" t="s">
-        <v>352</v>
+        <v>589</v>
       </c>
     </row>
     <row r="31" spans="2:15">
       <c r="B31">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="C31" t="s">
         <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>454</v>
+        <v>423</v>
       </c>
       <c r="O31" t="s">
-        <v>360</v>
+        <v>590</v>
       </c>
     </row>
     <row r="32" spans="2:15">
       <c r="B32">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="C32" t="s">
         <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>455</v>
+        <v>424</v>
       </c>
       <c r="O32" t="s">
-        <v>111</v>
+        <v>591</v>
       </c>
     </row>
     <row r="33" spans="2:15">
       <c r="B33">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="O33" t="s">
-        <v>620</v>
+        <v>592</v>
       </c>
     </row>
     <row r="34" spans="2:15">
+      <c r="B34">
+        <v>2050</v>
+      </c>
       <c r="C34" t="s">
         <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>457</v>
+        <v>426</v>
       </c>
       <c r="O34" t="s">
-        <v>621</v>
+        <v>593</v>
       </c>
     </row>
     <row r="35" spans="2:15">
+      <c r="B35">
+        <v>2051</v>
+      </c>
       <c r="C35" t="s">
         <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>458</v>
+        <v>427</v>
       </c>
       <c r="O35" t="s">
-        <v>622</v>
+        <v>594</v>
       </c>
     </row>
     <row r="36" spans="2:15">
+      <c r="B36">
+        <v>2052</v>
+      </c>
       <c r="C36" t="s">
         <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>459</v>
+        <v>428</v>
       </c>
       <c r="O36" t="s">
-        <v>623</v>
+        <v>595</v>
       </c>
     </row>
     <row r="37" spans="2:15">
+      <c r="B37">
+        <v>2053</v>
+      </c>
       <c r="C37" t="s">
         <v>64</v>
       </c>
       <c r="E37" t="s">
-        <v>460</v>
+        <v>429</v>
       </c>
       <c r="O37" t="s">
-        <v>624</v>
+        <v>596</v>
       </c>
     </row>
     <row r="38" spans="2:15">
+      <c r="B38">
+        <v>2054</v>
+      </c>
       <c r="C38" t="s">
         <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>461</v>
+        <v>430</v>
       </c>
       <c r="O38" t="s">
-        <v>625</v>
+        <v>597</v>
       </c>
     </row>
     <row r="39" spans="2:15">
+      <c r="B39">
+        <v>2055</v>
+      </c>
       <c r="C39" t="s">
         <v>66</v>
       </c>
       <c r="E39" t="s">
-        <v>462</v>
+        <v>431</v>
       </c>
       <c r="O39" t="s">
-        <v>626</v>
+        <v>598</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -3388,10 +3409,10 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>463</v>
+        <v>432</v>
       </c>
       <c r="O40" t="s">
-        <v>627</v>
+        <v>599</v>
       </c>
     </row>
     <row r="41" spans="2:15">
@@ -3399,10 +3420,10 @@
         <v>68</v>
       </c>
       <c r="E41" t="s">
-        <v>464</v>
+        <v>433</v>
       </c>
       <c r="O41" t="s">
-        <v>628</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -3410,7 +3431,10 @@
         <v>69</v>
       </c>
       <c r="E42" t="s">
-        <v>465</v>
+        <v>434</v>
+      </c>
+      <c r="O42" t="s">
+        <v>601</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -3418,7 +3442,10 @@
         <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>466</v>
+        <v>435</v>
+      </c>
+      <c r="O43" t="s">
+        <v>602</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -3426,7 +3453,10 @@
         <v>71</v>
       </c>
       <c r="E44" t="s">
-        <v>176</v>
+        <v>436</v>
+      </c>
+      <c r="O44" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="45" spans="2:15">
@@ -3434,7 +3464,10 @@
         <v>72</v>
       </c>
       <c r="E45" t="s">
-        <v>467</v>
+        <v>437</v>
+      </c>
+      <c r="O45" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -3442,7 +3475,10 @@
         <v>73</v>
       </c>
       <c r="E46" t="s">
-        <v>468</v>
+        <v>438</v>
+      </c>
+      <c r="O46" t="s">
+        <v>605</v>
       </c>
     </row>
     <row r="47" spans="2:15">
@@ -3450,7 +3486,10 @@
         <v>74</v>
       </c>
       <c r="E47" t="s">
-        <v>469</v>
+        <v>439</v>
+      </c>
+      <c r="O47" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="48" spans="2:15">
@@ -3458,135 +3497,168 @@
         <v>75</v>
       </c>
       <c r="E48" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="49" spans="3:5">
+        <v>171</v>
+      </c>
+      <c r="O48" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15">
       <c r="C49" t="s">
         <v>76</v>
       </c>
       <c r="E49" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="50" spans="3:5">
+        <v>440</v>
+      </c>
+      <c r="O49" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15">
       <c r="C50" t="s">
         <v>77</v>
       </c>
       <c r="E50" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="51" spans="3:5">
+        <v>441</v>
+      </c>
+      <c r="O50" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15">
       <c r="C51" t="s">
         <v>78</v>
       </c>
       <c r="E51" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="52" spans="3:5">
+        <v>442</v>
+      </c>
+      <c r="O51" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15">
       <c r="C52" t="s">
         <v>79</v>
       </c>
       <c r="E52" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="53" spans="3:5">
+        <v>443</v>
+      </c>
+      <c r="O52" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15">
       <c r="C53" t="s">
         <v>80</v>
       </c>
       <c r="E53" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="54" spans="3:5">
+        <v>444</v>
+      </c>
+      <c r="O53" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15">
       <c r="C54" t="s">
         <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="55" spans="3:5">
+        <v>445</v>
+      </c>
+      <c r="O54" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15">
       <c r="C55" t="s">
         <v>82</v>
       </c>
       <c r="E55" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="56" spans="3:5">
+        <v>446</v>
+      </c>
+      <c r="O55" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="56" spans="3:15">
       <c r="C56" t="s">
         <v>83</v>
       </c>
       <c r="E56" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="57" spans="3:5">
+        <v>447</v>
+      </c>
+      <c r="O56" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="57" spans="3:15">
       <c r="C57" t="s">
         <v>84</v>
       </c>
       <c r="E57" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="58" spans="3:5">
+        <v>448</v>
+      </c>
+      <c r="O57" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15">
       <c r="C58" t="s">
         <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="59" spans="3:5">
+        <v>449</v>
+      </c>
+      <c r="O58" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15">
       <c r="C59" t="s">
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="60" spans="3:5">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15">
       <c r="C60" t="s">
         <v>87</v>
       </c>
       <c r="E60" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="61" spans="3:5">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15">
       <c r="C61" t="s">
         <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="62" spans="3:5">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15">
       <c r="C62" t="s">
         <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="63" spans="3:5">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15">
       <c r="C63" t="s">
         <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="64" spans="3:5">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15">
       <c r="C64" t="s">
         <v>91</v>
       </c>
       <c r="E64" t="s">
-        <v>483</v>
+        <v>455</v>
       </c>
     </row>
     <row r="65" spans="3:5">
@@ -3594,7 +3666,7 @@
         <v>92</v>
       </c>
       <c r="E65" t="s">
-        <v>484</v>
+        <v>456</v>
       </c>
     </row>
     <row r="66" spans="3:5">
@@ -3602,7 +3674,7 @@
         <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>485</v>
+        <v>457</v>
       </c>
     </row>
     <row r="67" spans="3:5">
@@ -3610,7 +3682,7 @@
         <v>94</v>
       </c>
       <c r="E67" t="s">
-        <v>486</v>
+        <v>458</v>
       </c>
     </row>
     <row r="68" spans="3:5">
@@ -3618,7 +3690,7 @@
         <v>95</v>
       </c>
       <c r="E68" t="s">
-        <v>487</v>
+        <v>459</v>
       </c>
     </row>
     <row r="69" spans="3:5">
@@ -3626,7 +3698,7 @@
         <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>488</v>
+        <v>460</v>
       </c>
     </row>
     <row r="70" spans="3:5">
@@ -3634,7 +3706,7 @@
         <v>97</v>
       </c>
       <c r="E70" t="s">
-        <v>489</v>
+        <v>461</v>
       </c>
     </row>
     <row r="71" spans="3:5">
@@ -3642,7 +3714,7 @@
         <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>490</v>
+        <v>462</v>
       </c>
     </row>
     <row r="72" spans="3:5">
@@ -3650,7 +3722,7 @@
         <v>99</v>
       </c>
       <c r="E72" t="s">
-        <v>491</v>
+        <v>463</v>
       </c>
     </row>
     <row r="73" spans="3:5">
@@ -3658,7 +3730,7 @@
         <v>100</v>
       </c>
       <c r="E73" t="s">
-        <v>492</v>
+        <v>464</v>
       </c>
     </row>
     <row r="74" spans="3:5">
@@ -3666,7 +3738,7 @@
         <v>101</v>
       </c>
       <c r="E74" t="s">
-        <v>493</v>
+        <v>465</v>
       </c>
     </row>
     <row r="75" spans="3:5">
@@ -3674,7 +3746,7 @@
         <v>102</v>
       </c>
       <c r="E75" t="s">
-        <v>494</v>
+        <v>466</v>
       </c>
     </row>
     <row r="76" spans="3:5">
@@ -3682,7 +3754,7 @@
         <v>103</v>
       </c>
       <c r="E76" t="s">
-        <v>495</v>
+        <v>467</v>
       </c>
     </row>
     <row r="77" spans="3:5">
@@ -3690,7 +3762,7 @@
         <v>104</v>
       </c>
       <c r="E77" t="s">
-        <v>496</v>
+        <v>468</v>
       </c>
     </row>
     <row r="78" spans="3:5">
@@ -3698,7 +3770,7 @@
         <v>105</v>
       </c>
       <c r="E78" t="s">
-        <v>497</v>
+        <v>469</v>
       </c>
     </row>
     <row r="79" spans="3:5">
@@ -3706,7 +3778,7 @@
         <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>498</v>
+        <v>470</v>
       </c>
     </row>
     <row r="80" spans="3:5">
@@ -3714,7 +3786,7 @@
         <v>107</v>
       </c>
       <c r="E80" t="s">
-        <v>499</v>
+        <v>471</v>
       </c>
     </row>
     <row r="81" spans="3:5">
@@ -3722,7 +3794,7 @@
         <v>108</v>
       </c>
       <c r="E81" t="s">
-        <v>500</v>
+        <v>472</v>
       </c>
     </row>
     <row r="82" spans="3:5">
@@ -3730,7 +3802,7 @@
         <v>109</v>
       </c>
       <c r="E82" t="s">
-        <v>501</v>
+        <v>473</v>
       </c>
     </row>
     <row r="83" spans="3:5">
@@ -3738,7 +3810,7 @@
         <v>110</v>
       </c>
       <c r="E83" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
     </row>
     <row r="84" spans="3:5">
@@ -3746,7 +3818,7 @@
         <v>111</v>
       </c>
       <c r="E84" t="s">
-        <v>503</v>
+        <v>475</v>
       </c>
     </row>
     <row r="85" spans="3:5">
@@ -3754,7 +3826,7 @@
         <v>112</v>
       </c>
       <c r="E85" t="s">
-        <v>504</v>
+        <v>476</v>
       </c>
     </row>
     <row r="86" spans="3:5">
@@ -3762,7 +3834,7 @@
         <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>505</v>
+        <v>477</v>
       </c>
     </row>
     <row r="87" spans="3:5">
@@ -3770,7 +3842,7 @@
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>506</v>
+        <v>478</v>
       </c>
     </row>
     <row r="88" spans="3:5">
@@ -3778,7 +3850,7 @@
         <v>115</v>
       </c>
       <c r="E88" t="s">
-        <v>507</v>
+        <v>479</v>
       </c>
     </row>
     <row r="89" spans="3:5">
@@ -3786,7 +3858,7 @@
         <v>116</v>
       </c>
       <c r="E89" t="s">
-        <v>508</v>
+        <v>480</v>
       </c>
     </row>
     <row r="90" spans="3:5">
@@ -3794,7 +3866,7 @@
         <v>117</v>
       </c>
       <c r="E90" t="s">
-        <v>509</v>
+        <v>481</v>
       </c>
     </row>
     <row r="91" spans="3:5">
@@ -3802,7 +3874,7 @@
         <v>118</v>
       </c>
       <c r="E91" t="s">
-        <v>510</v>
+        <v>482</v>
       </c>
     </row>
     <row r="92" spans="3:5">
@@ -3810,7 +3882,7 @@
         <v>119</v>
       </c>
       <c r="E92" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
     </row>
     <row r="93" spans="3:5">
@@ -3818,7 +3890,7 @@
         <v>120</v>
       </c>
       <c r="E93" t="s">
-        <v>512</v>
+        <v>484</v>
       </c>
     </row>
     <row r="94" spans="3:5">
@@ -3826,7 +3898,7 @@
         <v>121</v>
       </c>
       <c r="E94" t="s">
-        <v>513</v>
+        <v>485</v>
       </c>
     </row>
     <row r="95" spans="3:5">
@@ -3834,7 +3906,7 @@
         <v>122</v>
       </c>
       <c r="E95" t="s">
-        <v>514</v>
+        <v>486</v>
       </c>
     </row>
     <row r="96" spans="3:5">
@@ -3842,7 +3914,7 @@
         <v>123</v>
       </c>
       <c r="E96" t="s">
-        <v>515</v>
+        <v>487</v>
       </c>
     </row>
     <row r="97" spans="3:5">
@@ -3850,7 +3922,7 @@
         <v>124</v>
       </c>
       <c r="E97" t="s">
-        <v>516</v>
+        <v>488</v>
       </c>
     </row>
     <row r="98" spans="3:5">
@@ -3858,7 +3930,7 @@
         <v>125</v>
       </c>
       <c r="E98" t="s">
-        <v>517</v>
+        <v>489</v>
       </c>
     </row>
     <row r="99" spans="3:5">
@@ -3866,7 +3938,7 @@
         <v>126</v>
       </c>
       <c r="E99" t="s">
-        <v>518</v>
+        <v>490</v>
       </c>
     </row>
     <row r="100" spans="3:5">
@@ -3874,7 +3946,7 @@
         <v>127</v>
       </c>
       <c r="E100" t="s">
-        <v>519</v>
+        <v>491</v>
       </c>
     </row>
     <row r="101" spans="3:5">
@@ -3882,7 +3954,7 @@
         <v>128</v>
       </c>
       <c r="E101" t="s">
-        <v>520</v>
+        <v>492</v>
       </c>
     </row>
     <row r="102" spans="3:5">
@@ -3890,7 +3962,7 @@
         <v>129</v>
       </c>
       <c r="E102" t="s">
-        <v>521</v>
+        <v>493</v>
       </c>
     </row>
     <row r="103" spans="3:5">
@@ -3898,7 +3970,7 @@
         <v>130</v>
       </c>
       <c r="E103" t="s">
-        <v>522</v>
+        <v>494</v>
       </c>
     </row>
     <row r="104" spans="3:5">
@@ -3906,7 +3978,7 @@
         <v>131</v>
       </c>
       <c r="E104" t="s">
-        <v>523</v>
+        <v>495</v>
       </c>
     </row>
     <row r="105" spans="3:5">
@@ -3914,7 +3986,7 @@
         <v>132</v>
       </c>
       <c r="E105" t="s">
-        <v>524</v>
+        <v>496</v>
       </c>
     </row>
     <row r="106" spans="3:5">
@@ -3922,7 +3994,7 @@
         <v>133</v>
       </c>
       <c r="E106" t="s">
-        <v>525</v>
+        <v>497</v>
       </c>
     </row>
     <row r="107" spans="3:5">
@@ -3930,7 +4002,7 @@
         <v>134</v>
       </c>
       <c r="E107" t="s">
-        <v>526</v>
+        <v>498</v>
       </c>
     </row>
     <row r="108" spans="3:5">
@@ -3938,7 +4010,7 @@
         <v>135</v>
       </c>
       <c r="E108" t="s">
-        <v>527</v>
+        <v>499</v>
       </c>
     </row>
     <row r="109" spans="3:5">
@@ -3946,7 +4018,7 @@
         <v>136</v>
       </c>
       <c r="E109" t="s">
-        <v>528</v>
+        <v>500</v>
       </c>
     </row>
     <row r="110" spans="3:5">
@@ -3954,7 +4026,7 @@
         <v>137</v>
       </c>
       <c r="E110" t="s">
-        <v>529</v>
+        <v>242</v>
       </c>
     </row>
     <row r="111" spans="3:5">
@@ -3962,7 +4034,7 @@
         <v>138</v>
       </c>
       <c r="E111" t="s">
-        <v>530</v>
+        <v>501</v>
       </c>
     </row>
     <row r="112" spans="3:5">
@@ -3970,7 +4042,7 @@
         <v>139</v>
       </c>
       <c r="E112" t="s">
-        <v>531</v>
+        <v>502</v>
       </c>
     </row>
     <row r="113" spans="3:5">
@@ -3978,7 +4050,7 @@
         <v>140</v>
       </c>
       <c r="E113" t="s">
-        <v>532</v>
+        <v>503</v>
       </c>
     </row>
     <row r="114" spans="3:5">
@@ -3986,7 +4058,7 @@
         <v>141</v>
       </c>
       <c r="E114" t="s">
-        <v>533</v>
+        <v>504</v>
       </c>
     </row>
     <row r="115" spans="3:5">
@@ -3994,7 +4066,7 @@
         <v>142</v>
       </c>
       <c r="E115" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
     </row>
     <row r="116" spans="3:5">
@@ -4002,7 +4074,7 @@
         <v>143</v>
       </c>
       <c r="E116" t="s">
-        <v>535</v>
+        <v>506</v>
       </c>
     </row>
     <row r="117" spans="3:5">
@@ -4010,7 +4082,7 @@
         <v>144</v>
       </c>
       <c r="E117" t="s">
-        <v>536</v>
+        <v>507</v>
       </c>
     </row>
     <row r="118" spans="3:5">
@@ -4018,7 +4090,7 @@
         <v>145</v>
       </c>
       <c r="E118" t="s">
-        <v>537</v>
+        <v>508</v>
       </c>
     </row>
     <row r="119" spans="3:5">
@@ -4026,7 +4098,7 @@
         <v>146</v>
       </c>
       <c r="E119" t="s">
-        <v>538</v>
+        <v>509</v>
       </c>
     </row>
     <row r="120" spans="3:5">
@@ -4034,7 +4106,7 @@
         <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
     </row>
     <row r="121" spans="3:5">
@@ -4042,7 +4114,7 @@
         <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>540</v>
+        <v>511</v>
       </c>
     </row>
     <row r="122" spans="3:5">
@@ -4050,7 +4122,7 @@
         <v>149</v>
       </c>
       <c r="E122" t="s">
-        <v>541</v>
+        <v>512</v>
       </c>
     </row>
     <row r="123" spans="3:5">
@@ -4058,7 +4130,7 @@
         <v>150</v>
       </c>
       <c r="E123" t="s">
-        <v>542</v>
+        <v>513</v>
       </c>
     </row>
     <row r="124" spans="3:5">
@@ -4066,7 +4138,7 @@
         <v>151</v>
       </c>
       <c r="E124" t="s">
-        <v>543</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125" spans="3:5">
@@ -4074,7 +4146,7 @@
         <v>152</v>
       </c>
       <c r="E125" t="s">
-        <v>544</v>
+        <v>515</v>
       </c>
     </row>
     <row r="126" spans="3:5">
@@ -4082,7 +4154,7 @@
         <v>153</v>
       </c>
       <c r="E126" t="s">
-        <v>545</v>
+        <v>516</v>
       </c>
     </row>
     <row r="127" spans="3:5">
@@ -4090,7 +4162,7 @@
         <v>154</v>
       </c>
       <c r="E127" t="s">
-        <v>546</v>
+        <v>517</v>
       </c>
     </row>
     <row r="128" spans="3:5">
@@ -4098,7 +4170,7 @@
         <v>155</v>
       </c>
       <c r="E128" t="s">
-        <v>547</v>
+        <v>518</v>
       </c>
     </row>
     <row r="129" spans="3:5">
@@ -4106,7 +4178,7 @@
         <v>156</v>
       </c>
       <c r="E129" t="s">
-        <v>548</v>
+        <v>519</v>
       </c>
     </row>
     <row r="130" spans="3:5">
@@ -4114,7 +4186,7 @@
         <v>157</v>
       </c>
       <c r="E130" t="s">
-        <v>549</v>
+        <v>520</v>
       </c>
     </row>
     <row r="131" spans="3:5">
@@ -4122,7 +4194,7 @@
         <v>158</v>
       </c>
       <c r="E131" t="s">
-        <v>550</v>
+        <v>521</v>
       </c>
     </row>
     <row r="132" spans="3:5">
@@ -4130,7 +4202,7 @@
         <v>159</v>
       </c>
       <c r="E132" t="s">
-        <v>551</v>
+        <v>522</v>
       </c>
     </row>
     <row r="133" spans="3:5">
@@ -4138,7 +4210,7 @@
         <v>160</v>
       </c>
       <c r="E133" t="s">
-        <v>552</v>
+        <v>523</v>
       </c>
     </row>
     <row r="134" spans="3:5">
@@ -4146,7 +4218,7 @@
         <v>161</v>
       </c>
       <c r="E134" t="s">
-        <v>553</v>
+        <v>524</v>
       </c>
     </row>
     <row r="135" spans="3:5">
@@ -4154,7 +4226,7 @@
         <v>162</v>
       </c>
       <c r="E135" t="s">
-        <v>554</v>
+        <v>525</v>
       </c>
     </row>
     <row r="136" spans="3:5">
@@ -4162,7 +4234,7 @@
         <v>163</v>
       </c>
       <c r="E136" t="s">
-        <v>555</v>
+        <v>88</v>
       </c>
     </row>
     <row r="137" spans="3:5">
@@ -4170,7 +4242,7 @@
         <v>164</v>
       </c>
       <c r="E137" t="s">
-        <v>556</v>
+        <v>526</v>
       </c>
     </row>
     <row r="138" spans="3:5">
@@ -4178,7 +4250,7 @@
         <v>165</v>
       </c>
       <c r="E138" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
     </row>
     <row r="139" spans="3:5">
@@ -4186,7 +4258,7 @@
         <v>166</v>
       </c>
       <c r="E139" t="s">
-        <v>558</v>
+        <v>362</v>
       </c>
     </row>
     <row r="140" spans="3:5">
@@ -4194,7 +4266,7 @@
         <v>167</v>
       </c>
       <c r="E140" t="s">
-        <v>559</v>
+        <v>367</v>
       </c>
     </row>
     <row r="141" spans="3:5">
@@ -4202,7 +4274,7 @@
         <v>168</v>
       </c>
       <c r="E141" t="s">
-        <v>560</v>
+        <v>528</v>
       </c>
     </row>
     <row r="142" spans="3:5">
@@ -4210,7 +4282,7 @@
         <v>169</v>
       </c>
       <c r="E142" t="s">
-        <v>561</v>
+        <v>529</v>
       </c>
     </row>
     <row r="143" spans="3:5">
@@ -4218,7 +4290,7 @@
         <v>170</v>
       </c>
       <c r="E143" t="s">
-        <v>562</v>
+        <v>530</v>
       </c>
     </row>
     <row r="144" spans="3:5">
@@ -4226,7 +4298,7 @@
         <v>171</v>
       </c>
       <c r="E144" t="s">
-        <v>563</v>
+        <v>531</v>
       </c>
     </row>
     <row r="145" spans="3:5">
@@ -4234,7 +4306,7 @@
         <v>172</v>
       </c>
       <c r="E145" t="s">
-        <v>564</v>
+        <v>532</v>
       </c>
     </row>
     <row r="146" spans="3:5">
@@ -4242,7 +4314,7 @@
         <v>173</v>
       </c>
       <c r="E146" t="s">
-        <v>565</v>
+        <v>533</v>
       </c>
     </row>
     <row r="147" spans="3:5">
@@ -4250,7 +4322,7 @@
         <v>174</v>
       </c>
       <c r="E147" t="s">
-        <v>566</v>
+        <v>534</v>
       </c>
     </row>
     <row r="148" spans="3:5">
@@ -4258,7 +4330,7 @@
         <v>175</v>
       </c>
       <c r="E148" t="s">
-        <v>567</v>
+        <v>535</v>
       </c>
     </row>
     <row r="149" spans="3:5">
@@ -4266,7 +4338,7 @@
         <v>176</v>
       </c>
       <c r="E149" t="s">
-        <v>568</v>
+        <v>536</v>
       </c>
     </row>
     <row r="150" spans="3:5">
@@ -4274,7 +4346,7 @@
         <v>177</v>
       </c>
       <c r="E150" t="s">
-        <v>569</v>
+        <v>537</v>
       </c>
     </row>
     <row r="151" spans="3:5">
@@ -4282,7 +4354,7 @@
         <v>178</v>
       </c>
       <c r="E151" t="s">
-        <v>570</v>
+        <v>538</v>
       </c>
     </row>
     <row r="152" spans="3:5">
@@ -4290,7 +4362,7 @@
         <v>179</v>
       </c>
       <c r="E152" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
     </row>
     <row r="153" spans="3:5">
@@ -4298,159 +4370,120 @@
         <v>180</v>
       </c>
       <c r="E153" t="s">
-        <v>572</v>
+        <v>540</v>
       </c>
     </row>
     <row r="154" spans="3:5">
       <c r="C154" t="s">
         <v>181</v>
       </c>
-      <c r="E154" t="s">
-        <v>573</v>
-      </c>
     </row>
     <row r="155" spans="3:5">
       <c r="C155" t="s">
         <v>182</v>
       </c>
-      <c r="E155" t="s">
-        <v>574</v>
-      </c>
     </row>
     <row r="156" spans="3:5">
       <c r="C156" t="s">
         <v>183</v>
       </c>
-      <c r="E156" t="s">
-        <v>575</v>
-      </c>
     </row>
     <row r="157" spans="3:5">
       <c r="C157" t="s">
         <v>184</v>
       </c>
-      <c r="E157" t="s">
-        <v>576</v>
-      </c>
     </row>
     <row r="158" spans="3:5">
       <c r="C158" t="s">
         <v>185</v>
       </c>
-      <c r="E158" t="s">
-        <v>577</v>
-      </c>
     </row>
     <row r="159" spans="3:5">
       <c r="C159" t="s">
         <v>186</v>
       </c>
-      <c r="E159" t="s">
-        <v>578</v>
-      </c>
     </row>
     <row r="160" spans="3:5">
       <c r="C160" t="s">
         <v>187</v>
       </c>
-      <c r="E160" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="161" spans="3:5">
+    </row>
+    <row r="161" spans="3:3">
       <c r="C161" t="s">
         <v>188</v>
       </c>
-      <c r="E161" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="162" spans="3:5">
+    </row>
+    <row r="162" spans="3:3">
       <c r="C162" t="s">
         <v>189</v>
       </c>
-      <c r="E162" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="163" spans="3:5">
+    </row>
+    <row r="163" spans="3:3">
       <c r="C163" t="s">
         <v>190</v>
       </c>
-      <c r="E163" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="164" spans="3:5">
+    </row>
+    <row r="164" spans="3:3">
       <c r="C164" t="s">
         <v>191</v>
       </c>
-      <c r="E164" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="165" spans="3:5">
+    </row>
+    <row r="165" spans="3:3">
       <c r="C165" t="s">
         <v>192</v>
       </c>
-      <c r="E165" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="166" spans="3:5">
+    </row>
+    <row r="166" spans="3:3">
       <c r="C166" t="s">
         <v>193</v>
       </c>
-      <c r="E166" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="167" spans="3:5">
+    </row>
+    <row r="167" spans="3:3">
       <c r="C167" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="168" spans="3:5">
+    <row r="168" spans="3:3">
       <c r="C168" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="169" spans="3:5">
+    <row r="169" spans="3:3">
       <c r="C169" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="170" spans="3:5">
+    <row r="170" spans="3:3">
       <c r="C170" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="171" spans="3:5">
+    <row r="171" spans="3:3">
       <c r="C171" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="172" spans="3:5">
+    <row r="172" spans="3:3">
       <c r="C172" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="173" spans="3:5">
+    <row r="173" spans="3:3">
       <c r="C173" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="174" spans="3:5">
+    <row r="174" spans="3:3">
       <c r="C174" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="175" spans="3:5">
+    <row r="175" spans="3:3">
       <c r="C175" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="176" spans="3:5">
+    <row r="176" spans="3:3">
       <c r="C176" t="s">
         <v>203</v>
       </c>
@@ -5373,161 +5406,6 @@
     <row r="360" spans="3:3">
       <c r="C360" t="s">
         <v>387</v>
-      </c>
-    </row>
-    <row r="361" spans="3:3">
-      <c r="C361" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="362" spans="3:3">
-      <c r="C362" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="363" spans="3:3">
-      <c r="C363" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="364" spans="3:3">
-      <c r="C364" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="365" spans="3:3">
-      <c r="C365" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="366" spans="3:3">
-      <c r="C366" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="367" spans="3:3">
-      <c r="C367" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="368" spans="3:3">
-      <c r="C368" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="369" spans="3:3">
-      <c r="C369" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="370" spans="3:3">
-      <c r="C370" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="371" spans="3:3">
-      <c r="C371" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="372" spans="3:3">
-      <c r="C372" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="373" spans="3:3">
-      <c r="C373" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="374" spans="3:3">
-      <c r="C374" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="375" spans="3:3">
-      <c r="C375" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="376" spans="3:3">
-      <c r="C376" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="377" spans="3:3">
-      <c r="C377" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="378" spans="3:3">
-      <c r="C378" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="379" spans="3:3">
-      <c r="C379" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="380" spans="3:3">
-      <c r="C380" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="381" spans="3:3">
-      <c r="C381" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="382" spans="3:3">
-      <c r="C382" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="383" spans="3:3">
-      <c r="C383" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="384" spans="3:3">
-      <c r="C384" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="385" spans="3:3">
-      <c r="C385" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="386" spans="3:3">
-      <c r="C386" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="387" spans="3:3">
-      <c r="C387" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="388" spans="3:3">
-      <c r="C388" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="389" spans="3:3">
-      <c r="C389" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="390" spans="3:3">
-      <c r="C390" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="391" spans="3:3">
-      <c r="C391" t="s">
-        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -5542,37 +5420,37 @@
   <sheetData>
     <row r="1" spans="1:69">
       <c r="A1" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="B1" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="L1" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="O1" t="s">
-        <v>647</v>
+        <v>636</v>
       </c>
       <c r="AA1" t="s">
-        <v>660</v>
+        <v>649</v>
       </c>
       <c r="AE1" t="s">
-        <v>665</v>
+        <v>654</v>
       </c>
       <c r="AI1" t="s">
-        <v>670</v>
+        <v>659</v>
       </c>
       <c r="AM1" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="AP1" t="s">
-        <v>679</v>
+        <v>668</v>
       </c>
       <c r="AS1" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="AZ1" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="BM1" t="s">
         <v>16</v>
@@ -5580,211 +5458,211 @@
     </row>
     <row r="2" spans="1:69">
       <c r="A2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D2" t="s">
+        <v>623</v>
+      </c>
+      <c r="E2" t="s">
+        <v>624</v>
+      </c>
+      <c r="F2" t="s">
+        <v>626</v>
+      </c>
+      <c r="G2" t="s">
+        <v>627</v>
+      </c>
+      <c r="H2" t="s">
+        <v>628</v>
+      </c>
+      <c r="I2" t="s">
+        <v>629</v>
+      </c>
+      <c r="J2" t="s">
         <v>630</v>
       </c>
-      <c r="B2" t="s">
-        <v>632</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="K2" t="s">
+        <v>631</v>
+      </c>
+      <c r="L2" t="s">
         <v>633</v>
       </c>
-      <c r="D2" t="s">
+      <c r="M2" t="s">
         <v>634</v>
       </c>
-      <c r="E2" t="s">
+      <c r="N2" t="s">
         <v>635</v>
       </c>
-      <c r="F2" t="s">
+      <c r="O2" t="s">
         <v>637</v>
       </c>
-      <c r="G2" t="s">
+      <c r="P2" t="s">
         <v>638</v>
       </c>
-      <c r="H2" t="s">
+      <c r="Q2" t="s">
         <v>639</v>
       </c>
-      <c r="I2" t="s">
+      <c r="R2" t="s">
         <v>640</v>
       </c>
-      <c r="J2" t="s">
+      <c r="S2" t="s">
         <v>641</v>
       </c>
-      <c r="K2" t="s">
+      <c r="T2" t="s">
         <v>642</v>
       </c>
-      <c r="L2" t="s">
+      <c r="U2" t="s">
+        <v>643</v>
+      </c>
+      <c r="V2" t="s">
         <v>644</v>
       </c>
-      <c r="M2" t="s">
+      <c r="W2" t="s">
         <v>645</v>
       </c>
-      <c r="N2" t="s">
+      <c r="X2" t="s">
         <v>646</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Y2" t="s">
+        <v>647</v>
+      </c>
+      <c r="Z2" t="s">
         <v>648</v>
       </c>
-      <c r="P2" t="s">
-        <v>649</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="AA2" t="s">
         <v>650</v>
       </c>
-      <c r="R2" t="s">
+      <c r="AB2" t="s">
         <v>651</v>
       </c>
-      <c r="S2" t="s">
+      <c r="AC2" t="s">
         <v>652</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AD2" t="s">
         <v>653</v>
       </c>
-      <c r="U2" t="s">
-        <v>654</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="AE2" t="s">
         <v>655</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AF2" t="s">
         <v>656</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AG2" t="s">
         <v>657</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AH2" t="s">
         <v>658</v>
       </c>
-      <c r="Z2" t="s">
-        <v>659</v>
-      </c>
-      <c r="AA2" t="s">
+      <c r="AI2" t="s">
+        <v>660</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>661</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AK2" t="s">
         <v>662</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AL2" t="s">
         <v>663</v>
       </c>
-      <c r="AD2" t="s">
-        <v>664</v>
-      </c>
-      <c r="AE2" t="s">
+      <c r="AM2" t="s">
+        <v>665</v>
+      </c>
+      <c r="AN2" t="s">
         <v>666</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AO2" t="s">
         <v>667</v>
       </c>
-      <c r="AG2" t="s">
-        <v>668</v>
-      </c>
-      <c r="AH2" t="s">
+      <c r="AP2" t="s">
         <v>669</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AQ2" t="s">
+        <v>670</v>
+      </c>
+      <c r="AR2" t="s">
         <v>671</v>
       </c>
-      <c r="AJ2" t="s">
-        <v>672</v>
-      </c>
-      <c r="AK2" t="s">
+      <c r="AS2" t="s">
         <v>673</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AT2" t="s">
         <v>674</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AU2" t="s">
+        <v>675</v>
+      </c>
+      <c r="AV2" t="s">
         <v>676</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AW2" t="s">
         <v>677</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AX2" t="s">
         <v>678</v>
       </c>
-      <c r="AP2" t="s">
-        <v>680</v>
-      </c>
-      <c r="AQ2" t="s">
+      <c r="AY2" t="s">
+        <v>679</v>
+      </c>
+      <c r="AZ2" t="s">
         <v>681</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="BA2" t="s">
         <v>682</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="BB2" t="s">
+        <v>683</v>
+      </c>
+      <c r="BC2" t="s">
         <v>684</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="BD2" t="s">
         <v>685</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="BE2" t="s">
         <v>686</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="BF2" t="s">
         <v>687</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="BG2" t="s">
+        <v>653</v>
+      </c>
+      <c r="BH2" t="s">
         <v>688</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BI2" t="s">
         <v>689</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BJ2" t="s">
         <v>690</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BK2" t="s">
+        <v>691</v>
+      </c>
+      <c r="BL2" t="s">
         <v>692</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BM2" t="s">
         <v>693</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BN2" t="s">
         <v>694</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BO2" t="s">
         <v>695</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BP2" t="s">
         <v>696</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BQ2" t="s">
         <v>697</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>698</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>664</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>699</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>700</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>701</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>702</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>703</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>704</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>705</v>
-      </c>
-      <c r="BO2" t="s">
-        <v>706</v>
-      </c>
-      <c r="BP2" t="s">
-        <v>707</v>
-      </c>
-      <c r="BQ2" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="3" spans="1:69">
@@ -6210,7 +6088,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -6624,228 +6502,228 @@
   <sheetData>
     <row r="1" spans="1:66">
       <c r="A1" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="B1" t="s">
-        <v>643</v>
+        <v>632</v>
       </c>
       <c r="D1" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="J1" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="AA1" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="AK1" t="s">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="AV1" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
       <c r="BM1" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
     </row>
     <row r="2" spans="1:66">
       <c r="A2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B2" t="s">
+        <v>699</v>
+      </c>
+      <c r="C2" t="s">
+        <v>700</v>
+      </c>
+      <c r="D2" t="s">
+        <v>702</v>
+      </c>
+      <c r="E2" t="s">
+        <v>703</v>
+      </c>
+      <c r="F2" t="s">
+        <v>704</v>
+      </c>
+      <c r="G2" t="s">
+        <v>705</v>
+      </c>
+      <c r="H2" t="s">
+        <v>706</v>
+      </c>
+      <c r="I2" t="s">
+        <v>707</v>
+      </c>
+      <c r="J2" t="s">
         <v>709</v>
       </c>
-      <c r="B2" t="s">
+      <c r="K2" t="s">
         <v>710</v>
       </c>
-      <c r="C2" t="s">
+      <c r="L2" t="s">
         <v>711</v>
       </c>
-      <c r="D2" t="s">
+      <c r="M2" t="s">
+        <v>712</v>
+      </c>
+      <c r="N2" t="s">
         <v>713</v>
       </c>
-      <c r="E2" t="s">
+      <c r="O2" t="s">
         <v>714</v>
       </c>
-      <c r="F2" t="s">
+      <c r="P2" t="s">
         <v>715</v>
       </c>
-      <c r="G2" t="s">
+      <c r="Q2" t="s">
         <v>716</v>
       </c>
-      <c r="H2" t="s">
+      <c r="R2" t="s">
         <v>717</v>
       </c>
-      <c r="I2" t="s">
+      <c r="S2" t="s">
         <v>718</v>
       </c>
-      <c r="J2" t="s">
+      <c r="T2" t="s">
+        <v>719</v>
+      </c>
+      <c r="U2" t="s">
         <v>720</v>
       </c>
-      <c r="K2" t="s">
+      <c r="V2" t="s">
         <v>721</v>
       </c>
-      <c r="L2" t="s">
+      <c r="W2" t="s">
         <v>722</v>
       </c>
-      <c r="M2" t="s">
+      <c r="X2" t="s">
         <v>723</v>
       </c>
-      <c r="N2" t="s">
+      <c r="Y2" t="s">
         <v>724</v>
       </c>
-      <c r="O2" t="s">
+      <c r="Z2" t="s">
         <v>725</v>
       </c>
-      <c r="P2" t="s">
-        <v>726</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="AA2" t="s">
         <v>727</v>
       </c>
-      <c r="R2" t="s">
+      <c r="AB2" t="s">
         <v>728</v>
       </c>
-      <c r="S2" t="s">
+      <c r="AC2" t="s">
         <v>729</v>
       </c>
-      <c r="T2" t="s">
+      <c r="AD2" t="s">
         <v>730</v>
       </c>
-      <c r="U2" t="s">
+      <c r="AE2" t="s">
         <v>731</v>
       </c>
-      <c r="V2" t="s">
+      <c r="AF2" t="s">
         <v>732</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AG2" t="s">
         <v>733</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AH2" t="s">
         <v>734</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AI2" t="s">
         <v>735</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AJ2" t="s">
         <v>736</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AK2" t="s">
+        <v>737</v>
+      </c>
+      <c r="AL2" t="s">
         <v>738</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AM2" t="s">
         <v>739</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AN2" t="s">
         <v>740</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AO2" t="s">
         <v>741</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AP2" t="s">
         <v>742</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AQ2" t="s">
         <v>743</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AR2" t="s">
         <v>744</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AS2" t="s">
         <v>745</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AT2" t="s">
         <v>746</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AU2" t="s">
         <v>747</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AV2" t="s">
         <v>748</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AW2" t="s">
         <v>749</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AX2" t="s">
         <v>750</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AY2" t="s">
         <v>751</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AZ2" t="s">
         <v>752</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="BA2" t="s">
         <v>753</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="BB2" t="s">
         <v>754</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="BC2" t="s">
         <v>755</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="BD2" t="s">
         <v>756</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="BE2" t="s">
         <v>757</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="BF2" t="s">
         <v>758</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="BG2" t="s">
         <v>759</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="BH2" t="s">
         <v>760</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="BI2" t="s">
         <v>761</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="BJ2" t="s">
         <v>762</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BK2" t="s">
         <v>763</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BL2" t="s">
         <v>764</v>
       </c>
-      <c r="BB2" t="s">
-        <v>765</v>
-      </c>
-      <c r="BC2" t="s">
+      <c r="BM2" t="s">
         <v>766</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BN2" t="s">
         <v>767</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>768</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>769</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>770</v>
-      </c>
-      <c r="BH2" t="s">
-        <v>771</v>
-      </c>
-      <c r="BI2" t="s">
-        <v>772</v>
-      </c>
-      <c r="BJ2" t="s">
-        <v>773</v>
-      </c>
-      <c r="BK2" t="s">
-        <v>774</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>775</v>
-      </c>
-      <c r="BM2" t="s">
-        <v>777</v>
-      </c>
-      <c r="BN2" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="3" spans="1:66">
@@ -7319,7 +7197,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>

--- a/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
+++ b/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="858">
   <si>
     <t>set</t>
   </si>
@@ -111,1552 +111,1837 @@
     <t>u</t>
   </si>
   <si>
-    <t>DUMREWET</t>
-  </si>
-  <si>
-    <t>DUMDEWET</t>
-  </si>
-  <si>
-    <t>ACCPWRWAT</t>
-  </si>
-  <si>
-    <t>ACCMINWAT</t>
-  </si>
-  <si>
-    <t>ACCAGRWAT1</t>
-  </si>
-  <si>
-    <t>ACCAGRWAT0</t>
+    <t>EXPDSL</t>
+  </si>
+  <si>
+    <t>EXPGSL</t>
+  </si>
+  <si>
+    <t>EXPHFO</t>
+  </si>
+  <si>
+    <t>MINNGS002</t>
+  </si>
+  <si>
+    <t>MINNGS003</t>
+  </si>
+  <si>
+    <t>PWRSOL004</t>
+  </si>
+  <si>
+    <t>PWRSOL003</t>
+  </si>
+  <si>
+    <t>PWRBIO002</t>
+  </si>
+  <si>
+    <t>PWRHYD005</t>
+  </si>
+  <si>
+    <t>TRANGSMCYNEW</t>
+  </si>
+  <si>
+    <t>PWRNUC</t>
+  </si>
+  <si>
+    <t>WSTLFLUNMG</t>
+  </si>
+  <si>
+    <t>TRAINF</t>
+  </si>
+  <si>
+    <t>INDOTHPLTIMP</t>
+  </si>
+  <si>
+    <t>INDMERPLTIMP</t>
+  </si>
+  <si>
+    <t>INDCHMPLTIMP</t>
+  </si>
+  <si>
+    <t>INDFBTPLTIMP</t>
+  </si>
+  <si>
+    <t>INDIRSPLTIMP</t>
+  </si>
+  <si>
+    <t>INDCEMPLTIMP</t>
+  </si>
+  <si>
+    <t>TRANMTINF</t>
+  </si>
+  <si>
+    <t>TRANGSHTRNEW</t>
+  </si>
+  <si>
+    <t>TRANGSLTRNEW</t>
+  </si>
+  <si>
+    <t>TRANGSMTRNEW</t>
+  </si>
+  <si>
+    <t>TRANGSBUSNEW</t>
+  </si>
+  <si>
+    <t>TRANGSMNBNEW</t>
+  </si>
+  <si>
+    <t>TRANGSCARNEW</t>
+  </si>
+  <si>
+    <t>DEMTRANGS</t>
+  </si>
+  <si>
+    <t>LVSMANCNV</t>
+  </si>
+  <si>
+    <t>LVSMANM01</t>
+  </si>
+  <si>
+    <t>LVSMANM02</t>
+  </si>
+  <si>
+    <t>RSCBIO</t>
+  </si>
+  <si>
+    <t>MINBIO</t>
+  </si>
+  <si>
+    <t>MINOIL</t>
+  </si>
+  <si>
+    <t>EXPOIL</t>
+  </si>
+  <si>
+    <t>UPSOILREF</t>
+  </si>
+  <si>
+    <t>UPSBIOCHAIMP</t>
+  </si>
+  <si>
+    <t>UPSBIOCHABBE</t>
+  </si>
+  <si>
+    <t>INDCHMGSLMDR</t>
+  </si>
+  <si>
+    <t>INDCHMDSLMDR</t>
+  </si>
+  <si>
+    <t>INDCHMELCMDR</t>
+  </si>
+  <si>
+    <t>INDFBTGSLMDR</t>
+  </si>
+  <si>
+    <t>INDFBTDSLMDR</t>
+  </si>
+  <si>
+    <t>INDFBTELCMDR</t>
+  </si>
+  <si>
+    <t>UPSBIOCHAMND</t>
+  </si>
+  <si>
+    <t>UPSBIOOTH</t>
+  </si>
+  <si>
+    <t>REGRS</t>
+  </si>
+  <si>
+    <t>DEGRS</t>
+  </si>
+  <si>
+    <t>RESHR</t>
+  </si>
+  <si>
+    <t>DESHR</t>
+  </si>
+  <si>
+    <t>RECRP</t>
+  </si>
+  <si>
+    <t>DECRP</t>
+  </si>
+  <si>
+    <t>REPET</t>
+  </si>
+  <si>
+    <t>DEPET</t>
+  </si>
+  <si>
+    <t>REWET</t>
+  </si>
+  <si>
+    <t>DEWET</t>
+  </si>
+  <si>
+    <t>LNDPET</t>
+  </si>
+  <si>
+    <t>TRAEVSCHG001</t>
+  </si>
+  <si>
+    <t>TRAEVSCHG002</t>
+  </si>
+  <si>
+    <t>TRAEVSCHG003</t>
+  </si>
+  <si>
+    <t>INDOTHELCHTH</t>
+  </si>
+  <si>
+    <t>INDOTHDSLHTH</t>
+  </si>
+  <si>
+    <t>INDOTHNGSHTH</t>
+  </si>
+  <si>
+    <t>INDOTHBIOHTH</t>
+  </si>
+  <si>
+    <t>INDOTHCOAHTH</t>
+  </si>
+  <si>
+    <t>INDOTHHDGHTH</t>
+  </si>
+  <si>
+    <t>INDOTHGSLMDR</t>
+  </si>
+  <si>
+    <t>INDOTHDSLMDR</t>
+  </si>
+  <si>
+    <t>INDOTHELCMDR</t>
+  </si>
+  <si>
+    <t>INDOTHPLT</t>
+  </si>
+  <si>
+    <t>INDMERELCHTH</t>
+  </si>
+  <si>
+    <t>INDMERDSLHTH</t>
+  </si>
+  <si>
+    <t>INDMERNGSHTH</t>
+  </si>
+  <si>
+    <t>INDMERBIOHTH</t>
+  </si>
+  <si>
+    <t>INDMERCOAHTH</t>
+  </si>
+  <si>
+    <t>INDMERHDGHTH</t>
+  </si>
+  <si>
+    <t>INDMERGSLMDR</t>
+  </si>
+  <si>
+    <t>INDMERDSLMDR</t>
+  </si>
+  <si>
+    <t>INDMERELCMDR</t>
+  </si>
+  <si>
+    <t>INDMERPLT</t>
+  </si>
+  <si>
+    <t>INDCHMPLT</t>
+  </si>
+  <si>
+    <t>INDCHMELCHTH</t>
+  </si>
+  <si>
+    <t>INDCHMKERHTH</t>
+  </si>
+  <si>
+    <t>INDCHMNGSHTH</t>
+  </si>
+  <si>
+    <t>INDCHMBIOHTH</t>
+  </si>
+  <si>
+    <t>INDCHMCOAHTH</t>
+  </si>
+  <si>
+    <t>INDCHMHDGHTH</t>
+  </si>
+  <si>
+    <t>INDFBTELCHTH</t>
+  </si>
+  <si>
+    <t>INDFBTPLT</t>
+  </si>
+  <si>
+    <t>INDFBTHFOHTH</t>
+  </si>
+  <si>
+    <t>INDFBTNGSHTH</t>
+  </si>
+  <si>
+    <t>INDFBTBIOHTH</t>
+  </si>
+  <si>
+    <t>INDFBTCHAHTH</t>
+  </si>
+  <si>
+    <t>INDFBTHDGHTH</t>
+  </si>
+  <si>
+    <t>DEMINDHDG</t>
+  </si>
+  <si>
+    <t>INDIRSPLT</t>
+  </si>
+  <si>
+    <t>AGRGSLFSH</t>
+  </si>
+  <si>
+    <t>DEMINDWST</t>
+  </si>
+  <si>
+    <t>DEMINDCOA</t>
+  </si>
+  <si>
+    <t>DEMINDNGS</t>
+  </si>
+  <si>
+    <t>DEMINDHFO</t>
+  </si>
+  <si>
+    <t>INDCEMPLT</t>
+  </si>
+  <si>
+    <t>LNDCRPFAL</t>
+  </si>
+  <si>
+    <t>AGRFER</t>
+  </si>
+  <si>
+    <t>DEMAGRGSL</t>
+  </si>
+  <si>
+    <t>AGRDSLMCH</t>
+  </si>
+  <si>
+    <t>AGRGSLMCH</t>
+  </si>
+  <si>
+    <t>AGRELCMCH</t>
+  </si>
+  <si>
+    <t>TRAHYBCARCUR</t>
+  </si>
+  <si>
+    <t>TRADSLPRL</t>
+  </si>
+  <si>
+    <t>TRAELCPRL</t>
+  </si>
+  <si>
+    <t>TRADSLFRL</t>
+  </si>
+  <si>
+    <t>TRAELCFRL</t>
+  </si>
+  <si>
+    <t>TRAGSLNAV</t>
+  </si>
+  <si>
+    <t>TRAKERAVI</t>
+  </si>
+  <si>
+    <t>LVSCTLIMP</t>
+  </si>
+  <si>
+    <t>LVSSHPIMP</t>
+  </si>
+  <si>
+    <t>LVSGOAIMP</t>
+  </si>
+  <si>
+    <t>RESELCCURR</t>
+  </si>
+  <si>
+    <t>RESELCCKNR</t>
+  </si>
+  <si>
+    <t>RESLPGCKNR</t>
+  </si>
+  <si>
+    <t>RESCHACKNR</t>
+  </si>
+  <si>
+    <t>RESBIOCKNIMPR</t>
+  </si>
+  <si>
+    <t>RESBIOCKNR</t>
+  </si>
+  <si>
+    <t>RESELCWTHR</t>
+  </si>
+  <si>
+    <t>RESBIOWTHR</t>
+  </si>
+  <si>
+    <t>RESLPGWTHR</t>
+  </si>
+  <si>
+    <t>RESCHAWTHR</t>
+  </si>
+  <si>
+    <t>RESKERLGTR</t>
+  </si>
+  <si>
+    <t>RESELCLGTR</t>
+  </si>
+  <si>
+    <t>EXPSOY</t>
+  </si>
+  <si>
+    <t>EXPSOR</t>
+  </si>
+  <si>
+    <t>EXPSES</t>
+  </si>
+  <si>
+    <t>EXPRIC</t>
+  </si>
+  <si>
+    <t>EXPVEG</t>
+  </si>
+  <si>
+    <t>IMPRIC</t>
+  </si>
+  <si>
+    <t>IMPSES</t>
+  </si>
+  <si>
+    <t>IMPSOR</t>
+  </si>
+  <si>
+    <t>IMPSOY</t>
+  </si>
+  <si>
+    <t>IMPVEG</t>
+  </si>
+  <si>
+    <t>LNDSORHR</t>
+  </si>
+  <si>
+    <t>LNDSORHI</t>
+  </si>
+  <si>
+    <t>LNDSORLR</t>
+  </si>
+  <si>
+    <t>LNDSORLI</t>
+  </si>
+  <si>
+    <t>LNDSESHR</t>
+  </si>
+  <si>
+    <t>LNDSESHI</t>
+  </si>
+  <si>
+    <t>LNDSESLR</t>
+  </si>
+  <si>
+    <t>LNDSESLI</t>
+  </si>
+  <si>
+    <t>LNDRICHR</t>
+  </si>
+  <si>
+    <t>LNDRICHI</t>
+  </si>
+  <si>
+    <t>LNDRICLR</t>
+  </si>
+  <si>
+    <t>LNDRICLI</t>
+  </si>
+  <si>
+    <t>LNDSOYHR</t>
+  </si>
+  <si>
+    <t>LNDSOYHI</t>
+  </si>
+  <si>
+    <t>LNDSOYLR</t>
+  </si>
+  <si>
+    <t>LNDSOYLI</t>
+  </si>
+  <si>
+    <t>LNDVEGHR</t>
+  </si>
+  <si>
+    <t>LNDVEGHI</t>
+  </si>
+  <si>
+    <t>LNDVEGLR</t>
+  </si>
+  <si>
+    <t>LNDVEGLI</t>
+  </si>
+  <si>
+    <t>GH2COAL</t>
+  </si>
+  <si>
+    <t>GH2NGS</t>
+  </si>
+  <si>
+    <t>BH2NGS</t>
+  </si>
+  <si>
+    <t>GH2ELC</t>
+  </si>
+  <si>
+    <t>PLANTIS</t>
+  </si>
+  <si>
+    <t>INDIRSDSLHTH</t>
+  </si>
+  <si>
+    <t>INDIRSNGSHTHCCS</t>
+  </si>
+  <si>
+    <t>INDIRSHDGDRI</t>
+  </si>
+  <si>
+    <t>INDIRSNGSDRI</t>
+  </si>
+  <si>
+    <t>INDIRSELCEAF</t>
+  </si>
+  <si>
+    <t>INDIRSBIOHTH</t>
+  </si>
+  <si>
+    <t>INDIRSBIOHTHCCS</t>
+  </si>
+  <si>
+    <t>INDIRSCOAHTH</t>
+  </si>
+  <si>
+    <t>INDIRSCOAHTHCCS</t>
+  </si>
+  <si>
+    <t>INDIRSHDGHTH</t>
+  </si>
+  <si>
+    <t>INDIRSNGSHTH</t>
+  </si>
+  <si>
+    <t>PLANTNMM</t>
+  </si>
+  <si>
+    <t>INDWSTKLN</t>
+  </si>
+  <si>
+    <t>INDHFOKLN</t>
+  </si>
+  <si>
+    <t>INDNGSKLNCCS</t>
+  </si>
+  <si>
+    <t>INDNGSKLN</t>
+  </si>
+  <si>
+    <t>INDBIOKLNCCS</t>
+  </si>
+  <si>
+    <t>INDBIOKLN</t>
+  </si>
+  <si>
+    <t>INDCOAKLNCCS</t>
+  </si>
+  <si>
+    <t>INDKLNCOA</t>
+  </si>
+  <si>
+    <t>PWRBATIN</t>
+  </si>
+  <si>
+    <t>PWRBATOUT</t>
+  </si>
+  <si>
+    <t>PWRTRNIMP</t>
+  </si>
+  <si>
+    <t>DEMPWRDSL</t>
+  </si>
+  <si>
+    <t>PWRDSL</t>
+  </si>
+  <si>
+    <t>LWTADA</t>
+  </si>
+  <si>
+    <t>LWTCAR</t>
+  </si>
+  <si>
+    <t>LWTLAG</t>
+  </si>
+  <si>
+    <t>LWTLAT</t>
+  </si>
+  <si>
+    <t>LWTSPT</t>
+  </si>
+  <si>
+    <t>LWTSWR</t>
+  </si>
+  <si>
+    <t>LWTGEN</t>
+  </si>
+  <si>
+    <t>RESELCBSTU</t>
+  </si>
+  <si>
+    <t>COMELCBST</t>
+  </si>
+  <si>
+    <t>RESELCCFFU</t>
+  </si>
+  <si>
+    <t>COMELCCFF</t>
+  </si>
+  <si>
+    <t>TRAELCHTRCUR</t>
+  </si>
+  <si>
+    <t>TRAELCMTRCUR</t>
+  </si>
+  <si>
+    <t>TRAELCLTRCUR</t>
+  </si>
+  <si>
+    <t>TRAELCBUSCUR</t>
+  </si>
+  <si>
+    <t>TRALPGBUSNEW</t>
+  </si>
+  <si>
+    <t>TRAELCMNBCUR</t>
+  </si>
+  <si>
+    <t>TRALPGMNBNEW</t>
+  </si>
+  <si>
+    <t>TRADSLMCYNEW</t>
+  </si>
+  <si>
+    <t>TRAELCMCYCUR</t>
+  </si>
+  <si>
+    <t>TRAELCCARCUR</t>
+  </si>
+  <si>
+    <t>TRALPGCARNEW</t>
+  </si>
+  <si>
+    <t>DEMTRALPG</t>
+  </si>
+  <si>
+    <t>IMPLFO</t>
+  </si>
+  <si>
+    <t>MINWND</t>
+  </si>
+  <si>
+    <t>MINCOA</t>
+  </si>
+  <si>
+    <t>MINNGS001</t>
+  </si>
+  <si>
+    <t>PWROHC003</t>
+  </si>
+  <si>
+    <t>DEMPWRWND</t>
+  </si>
+  <si>
+    <t>PWRWND001</t>
+  </si>
+  <si>
+    <t>PWRNGS002</t>
+  </si>
+  <si>
+    <t>PWRNGS001</t>
+  </si>
+  <si>
+    <t>DEMPWRNGS</t>
+  </si>
+  <si>
+    <t>PWROHC002</t>
+  </si>
+  <si>
+    <t>DEMPWRHFO</t>
+  </si>
+  <si>
+    <t>PWRCOA001</t>
+  </si>
+  <si>
+    <t>DEMPWRCOA</t>
+  </si>
+  <si>
+    <t>TRAELCLTRNEW</t>
+  </si>
+  <si>
+    <t>PWRLFG001</t>
+  </si>
+  <si>
+    <t>DEMPWRLFG</t>
+  </si>
+  <si>
+    <t>WSTLFLSANT</t>
+  </si>
+  <si>
+    <t>WSTINC</t>
+  </si>
+  <si>
+    <t>WSTHZD</t>
+  </si>
+  <si>
+    <t>WSTGLS</t>
+  </si>
+  <si>
+    <t>WSTPLR</t>
+  </si>
+  <si>
+    <t>WSTPAR</t>
+  </si>
+  <si>
+    <t>WSTMTR</t>
+  </si>
+  <si>
+    <t>WSTCMP</t>
+  </si>
+  <si>
+    <t>WSTDGS</t>
+  </si>
+  <si>
+    <t>WSTSEP</t>
+  </si>
+  <si>
+    <t>WSTORG</t>
+  </si>
+  <si>
+    <t>WSTUNS</t>
+  </si>
+  <si>
+    <t>WSTCOL</t>
+  </si>
+  <si>
+    <t>WSTDMP</t>
+  </si>
+  <si>
+    <t>WSTOPB</t>
+  </si>
+  <si>
+    <t>WSTGEN</t>
   </si>
   <si>
     <t>LNDWET</t>
   </si>
   <si>
-    <t>STOBATIN</t>
-  </si>
-  <si>
-    <t>STOBATOUT</t>
-  </si>
-  <si>
-    <t>LVSOTHCF</t>
-  </si>
-  <si>
-    <t>LVSOTHCU</t>
-  </si>
-  <si>
-    <t>LNDCANLR</t>
-  </si>
-  <si>
-    <t>LNDCANLI</t>
-  </si>
-  <si>
-    <t>LNDCANHR</t>
-  </si>
-  <si>
-    <t>LNDCANHI</t>
-  </si>
-  <si>
-    <t>DEMAGRCOA</t>
-  </si>
-  <si>
-    <t>DEMAGRLPG</t>
+    <t>DEFOR</t>
+  </si>
+  <si>
+    <t>REFOR</t>
+  </si>
+  <si>
+    <t>DUMLUC</t>
+  </si>
+  <si>
+    <t>MINHYD</t>
+  </si>
+  <si>
+    <t>PWRHYD001</t>
+  </si>
+  <si>
+    <t>PWRTRN</t>
+  </si>
+  <si>
+    <t>DEMINDELC</t>
+  </si>
+  <si>
+    <t>DEMRESELC</t>
+  </si>
+  <si>
+    <t>DEMCOMELC</t>
+  </si>
+  <si>
+    <t>PWRHYD002</t>
+  </si>
+  <si>
+    <t>PWRHYD003</t>
+  </si>
+  <si>
+    <t>PWRHYD004</t>
+  </si>
+  <si>
+    <t>IMPHFO</t>
+  </si>
+  <si>
+    <t>UPSREF001</t>
+  </si>
+  <si>
+    <t>UPSREF002</t>
+  </si>
+  <si>
+    <t>MINSOL</t>
+  </si>
+  <si>
+    <t>PWRSOL001</t>
+  </si>
+  <si>
+    <t>PWRSOL002</t>
+  </si>
+  <si>
+    <t>MINGEO</t>
+  </si>
+  <si>
+    <t>PWRGEO001</t>
+  </si>
+  <si>
+    <t>IMPBIO</t>
+  </si>
+  <si>
+    <t>PWRBIO001</t>
+  </si>
+  <si>
+    <t>PWRTRNEXP</t>
+  </si>
+  <si>
+    <t>PWRCSP001</t>
+  </si>
+  <si>
+    <t>RSCLND</t>
+  </si>
+  <si>
+    <t>LNDPLAHR</t>
+  </si>
+  <si>
+    <t>LNDPLAHI</t>
+  </si>
+  <si>
+    <t>LNDPLALR</t>
+  </si>
+  <si>
+    <t>LNDPLALI</t>
+  </si>
+  <si>
+    <t>LNDMAIHR</t>
+  </si>
+  <si>
+    <t>LNDMAIHI</t>
+  </si>
+  <si>
+    <t>LNDMAILR</t>
+  </si>
+  <si>
+    <t>LNDMAILI</t>
+  </si>
+  <si>
+    <t>LNDCASHR</t>
+  </si>
+  <si>
+    <t>LNDCASHI</t>
+  </si>
+  <si>
+    <t>LNDCASLR</t>
+  </si>
+  <si>
+    <t>LNDCASLI</t>
+  </si>
+  <si>
+    <t>LNDBEAHR</t>
+  </si>
+  <si>
+    <t>LNDBEAHI</t>
+  </si>
+  <si>
+    <t>LNDBEALR</t>
+  </si>
+  <si>
+    <t>LNDBEALI</t>
+  </si>
+  <si>
+    <t>LNDCOFHR</t>
+  </si>
+  <si>
+    <t>LNDCOFHI</t>
+  </si>
+  <si>
+    <t>LNDCOFLR</t>
+  </si>
+  <si>
+    <t>LNDCOFLI</t>
+  </si>
+  <si>
+    <t>LNDGROHR</t>
+  </si>
+  <si>
+    <t>LNDGROHI</t>
+  </si>
+  <si>
+    <t>LNDGROLR</t>
+  </si>
+  <si>
+    <t>LNDGROLI</t>
+  </si>
+  <si>
+    <t>LNDSUNHR</t>
+  </si>
+  <si>
+    <t>LNDSUNHI</t>
+  </si>
+  <si>
+    <t>LNDSUNLR</t>
+  </si>
+  <si>
+    <t>LNDSUNLI</t>
+  </si>
+  <si>
+    <t>LNDOTCHR</t>
+  </si>
+  <si>
+    <t>LNDOTCHI</t>
+  </si>
+  <si>
+    <t>LNDOTCLR</t>
+  </si>
+  <si>
+    <t>LNDOTCLI</t>
+  </si>
+  <si>
+    <t>LNDPTSHR</t>
+  </si>
+  <si>
+    <t>LNDPTSHI</t>
+  </si>
+  <si>
+    <t>LNDPTSLR</t>
+  </si>
+  <si>
+    <t>LNDPTSLI</t>
+  </si>
+  <si>
+    <t>LNDFOR</t>
+  </si>
+  <si>
+    <t>LNDBLT</t>
+  </si>
+  <si>
+    <t>LNDWAT</t>
+  </si>
+  <si>
+    <t>LNDOTH</t>
+  </si>
+  <si>
+    <t>IMPPLA</t>
+  </si>
+  <si>
+    <t>IMPMAI</t>
+  </si>
+  <si>
+    <t>IMPCAS</t>
+  </si>
+  <si>
+    <t>IMPBEA</t>
+  </si>
+  <si>
+    <t>IMPCOF</t>
+  </si>
+  <si>
+    <t>IMPSUN</t>
+  </si>
+  <si>
+    <t>IMPOTC</t>
+  </si>
+  <si>
+    <t>MINPRC</t>
+  </si>
+  <si>
+    <t>DEMAGRSURWAT</t>
+  </si>
+  <si>
+    <t>DEMAGRGWTWAT</t>
+  </si>
+  <si>
+    <t>DEMPUBSURWAT</t>
+  </si>
+  <si>
+    <t>DEMPUBGWTWAT</t>
+  </si>
+  <si>
+    <t>DEMPWRSURWAT</t>
+  </si>
+  <si>
+    <t>DEMPWRGWTWAT</t>
+  </si>
+  <si>
+    <t>IMPDSL</t>
+  </si>
+  <si>
+    <t>DEMAGRDSL</t>
+  </si>
+  <si>
+    <t>RESELCCKNU</t>
+  </si>
+  <si>
+    <t>COMELCHEL</t>
+  </si>
+  <si>
+    <t>LNDCRP</t>
+  </si>
+  <si>
+    <t>EXPPLA</t>
+  </si>
+  <si>
+    <t>EXPMAI</t>
+  </si>
+  <si>
+    <t>EXPCAS</t>
+  </si>
+  <si>
+    <t>EXPBEA</t>
+  </si>
+  <si>
+    <t>EXPCOF</t>
+  </si>
+  <si>
+    <t>EXPGRO</t>
+  </si>
+  <si>
+    <t>EXPPTS</t>
+  </si>
+  <si>
+    <t>EXPSUN</t>
+  </si>
+  <si>
+    <t>EXPOTC</t>
+  </si>
+  <si>
+    <t>LNDGRA</t>
+  </si>
+  <si>
+    <t>PST001</t>
+  </si>
+  <si>
+    <t>PST002</t>
+  </si>
+  <si>
+    <t>LVSCTLCUR</t>
+  </si>
+  <si>
+    <t>LVSSHPCUR</t>
+  </si>
+  <si>
+    <t>LVSGOACUR</t>
+  </si>
+  <si>
+    <t>LNDSHR</t>
+  </si>
+  <si>
+    <t>DEMPWRBIO</t>
+  </si>
+  <si>
+    <t>DEMPWRHYD</t>
+  </si>
+  <si>
+    <t>DEMPWRSOL</t>
+  </si>
+  <si>
+    <t>DEMPWRGEO</t>
+  </si>
+  <si>
+    <t>COMELCCUR</t>
+  </si>
+  <si>
+    <t>RESELCCURU</t>
+  </si>
+  <si>
+    <t>DEMINDDSL</t>
+  </si>
+  <si>
+    <t>DEMINDGSL</t>
+  </si>
+  <si>
+    <t>DEMINDKER</t>
+  </si>
+  <si>
+    <t>DEMCOMLPG</t>
+  </si>
+  <si>
+    <t>DEMRESLPG</t>
+  </si>
+  <si>
+    <t>DEMRESKER</t>
+  </si>
+  <si>
+    <t>COMLPGHEL</t>
+  </si>
+  <si>
+    <t>RESLPGCKNU</t>
+  </si>
+  <si>
+    <t>RESKERLGTU</t>
+  </si>
+  <si>
+    <t>RESELCLGTU</t>
+  </si>
+  <si>
+    <t>DEMRESCHA</t>
+  </si>
+  <si>
+    <t>RESELCCOLU</t>
+  </si>
+  <si>
+    <t>DEMCOMCHA</t>
+  </si>
+  <si>
+    <t>RESCHACKNU</t>
+  </si>
+  <si>
+    <t>IMPGSL</t>
+  </si>
+  <si>
+    <t>IMPLPG</t>
+  </si>
+  <si>
+    <t>IMPKER</t>
+  </si>
+  <si>
+    <t>MINBIOWST</t>
+  </si>
+  <si>
+    <t>RESBIOSPHR</t>
+  </si>
+  <si>
+    <t>RESELCWTHU</t>
+  </si>
+  <si>
+    <t>RESBIOWTHU</t>
+  </si>
+  <si>
+    <t>RESLPGWTHU</t>
+  </si>
+  <si>
+    <t>RESCHAWTHU</t>
+  </si>
+  <si>
+    <t>XRESCKNU</t>
+  </si>
+  <si>
+    <t>XRESELCOTH</t>
+  </si>
+  <si>
+    <t>XRESLGTU</t>
+  </si>
+  <si>
+    <t>XRESCOLU</t>
+  </si>
+  <si>
+    <t>XRESSPHR</t>
+  </si>
+  <si>
+    <t>XRESWTHU</t>
+  </si>
+  <si>
+    <t>XCOMHEL</t>
+  </si>
+  <si>
+    <t>XCOMELCOTH</t>
+  </si>
+  <si>
+    <t>RESBIOCKNU</t>
+  </si>
+  <si>
+    <t>RESBGSCKNR</t>
+  </si>
+  <si>
+    <t>COMBIOHEL</t>
+  </si>
+  <si>
+    <t>COMCHAHEL</t>
+  </si>
+  <si>
+    <t>COMBGSHEL</t>
+  </si>
+  <si>
+    <t>DEMRESBIO</t>
+  </si>
+  <si>
+    <t>DEMRESBGS</t>
+  </si>
+  <si>
+    <t>DEMCOMBIO</t>
+  </si>
+  <si>
+    <t>DEMCOMBGS</t>
+  </si>
+  <si>
+    <t>DEMINDCHA</t>
+  </si>
+  <si>
+    <t>RESBIOCKNIMPU</t>
+  </si>
+  <si>
+    <t>DEMINDBIO</t>
+  </si>
+  <si>
+    <t>DEMTRAELC</t>
+  </si>
+  <si>
+    <t>TRAELCCARNEW</t>
+  </si>
+  <si>
+    <t>DEMTRADSL</t>
+  </si>
+  <si>
+    <t>TRADSLCARCUR</t>
+  </si>
+  <si>
+    <t>DEMTRAGSL</t>
+  </si>
+  <si>
+    <t>TRAGSLCARCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLCARNEW</t>
+  </si>
+  <si>
+    <t>TRADSLCARNEW</t>
+  </si>
+  <si>
+    <t>TRAHYBCARNEW</t>
+  </si>
+  <si>
+    <t>TRADSLBUSCUR</t>
+  </si>
+  <si>
+    <t>TRADSLBUSNEW</t>
+  </si>
+  <si>
+    <t>TRAELCBUSNEW</t>
+  </si>
+  <si>
+    <t>TRAHYBBUSNEW</t>
+  </si>
+  <si>
+    <t>TRADSLMNBCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLMNBCUR</t>
+  </si>
+  <si>
+    <t>TRADSLMNBNEW</t>
+  </si>
+  <si>
+    <t>TRAGSLMNBNEW</t>
+  </si>
+  <si>
+    <t>TRAHYBMNBNEW</t>
+  </si>
+  <si>
+    <t>TRAELCMNBNEW</t>
+  </si>
+  <si>
+    <t>TRAGSLMCYCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLMCYNEW</t>
+  </si>
+  <si>
+    <t>TRAELCMCYNEW</t>
+  </si>
+  <si>
+    <t>TRAGSLLTRCUR</t>
+  </si>
+  <si>
+    <t>TRADSLLTRCUR</t>
+  </si>
+  <si>
+    <t>TRAGSLLTRNEW</t>
+  </si>
+  <si>
+    <t>TRADSLLTRNEW</t>
+  </si>
+  <si>
+    <t>TRAHYBLTRNEW</t>
+  </si>
+  <si>
+    <t>TRADSLMTRCUR</t>
+  </si>
+  <si>
+    <t>TRADSLMTRNEW</t>
+  </si>
+  <si>
+    <t>TRAELCMTRNEW</t>
+  </si>
+  <si>
+    <t>TRADSLHTRCUR</t>
+  </si>
+  <si>
+    <t>TRADSLHTRNEW</t>
+  </si>
+  <si>
+    <t>TRAELCHTRNEW</t>
+  </si>
+  <si>
+    <t>DEMTRAKER</t>
   </si>
   <si>
     <t>DEMAGRELC</t>
   </si>
   <si>
-    <t>AGRELCCUR</t>
-  </si>
-  <si>
-    <t>AGRHEATCOA</t>
-  </si>
-  <si>
-    <t>AGRHEATLPG</t>
-  </si>
-  <si>
-    <t>AGRHEATELC</t>
-  </si>
-  <si>
-    <t>AGRMOTLPG</t>
-  </si>
-  <si>
-    <t>AGRMOTELC</t>
-  </si>
-  <si>
-    <t>PROPROCBIOF</t>
-  </si>
-  <si>
-    <t>BLENDBIOF</t>
-  </si>
-  <si>
-    <t>DEMTRABIO</t>
-  </si>
-  <si>
-    <t>BLENDJETKER</t>
-  </si>
-  <si>
-    <t>INDMINHPHBIOCCS</t>
-  </si>
-  <si>
-    <t>INDMINHPHCOACCS</t>
-  </si>
-  <si>
-    <t>INDASHHPHBIOCCS</t>
-  </si>
-  <si>
-    <t>INDASHHPHCOACCS</t>
-  </si>
-  <si>
-    <t>INDOTHHPHBIOCCS</t>
-  </si>
-  <si>
-    <t>INDOTHHPHCOACCS</t>
-  </si>
-  <si>
-    <t>INDKILNBIOCCS</t>
-  </si>
-  <si>
-    <t>INDKILNCOACCS</t>
-  </si>
-  <si>
-    <t>INDOTHLPHELC</t>
-  </si>
-  <si>
-    <t>INDPLANTCCSASH</t>
-  </si>
-  <si>
-    <t>BSTOPPWRWAT</t>
-  </si>
-  <si>
-    <t>BSTOPPUBWAT</t>
-  </si>
-  <si>
-    <t>BSTOPOTHWAT</t>
-  </si>
-  <si>
-    <t>BSTOPMINWAT</t>
-  </si>
-  <si>
-    <t>BSTOPRESWAT</t>
-  </si>
-  <si>
-    <t>BSTOPGOVWAT</t>
-  </si>
-  <si>
-    <t>BSTOPAGRWAT</t>
-  </si>
-  <si>
-    <t>BSTOPWSTCO2</t>
-  </si>
-  <si>
-    <t>DEMTOURELC</t>
-  </si>
-  <si>
-    <t>TOURELCHET</t>
-  </si>
-  <si>
-    <t>TOURELCCUR</t>
-  </si>
-  <si>
-    <t>DEMTOURLPG</t>
-  </si>
-  <si>
-    <t>TOURLPGHET</t>
-  </si>
-  <si>
-    <t>DEMTOURBIO</t>
-  </si>
-  <si>
-    <t>TOURBIOHET</t>
-  </si>
-  <si>
-    <t>DEMTOURCOA</t>
-  </si>
-  <si>
-    <t>TOURCOAHET</t>
-  </si>
-  <si>
-    <t>DEMTOURDSL</t>
-  </si>
-  <si>
-    <t>TOURDSLHET</t>
-  </si>
-  <si>
-    <t>DUMLUC</t>
-  </si>
-  <si>
-    <t>DEMPWRCBM</t>
-  </si>
-  <si>
-    <t>IMPJETKER</t>
-  </si>
-  <si>
-    <t>MINCBM</t>
-  </si>
-  <si>
-    <t>PWRCBM001</t>
-  </si>
-  <si>
-    <t>LNDCRPOTH</t>
-  </si>
-  <si>
-    <t>INDPLANTOTH</t>
-  </si>
-  <si>
-    <t>INDOTHLPHDSL</t>
-  </si>
-  <si>
-    <t>INDOTHLPHLPG</t>
-  </si>
-  <si>
-    <t>INDOTHLPHHFO</t>
-  </si>
-  <si>
-    <t>INDOTHLPHCOA</t>
-  </si>
-  <si>
-    <t>INDOTHLPHBIO</t>
-  </si>
-  <si>
-    <t>INDOTHHPHDSL</t>
-  </si>
-  <si>
-    <t>INDOTHHPHLPG</t>
-  </si>
-  <si>
-    <t>INDOTHHPHHFO</t>
-  </si>
-  <si>
-    <t>INDOTHHPHCOA</t>
-  </si>
-  <si>
-    <t>INDOTHHPHBIO</t>
-  </si>
-  <si>
-    <t>INDMINMOTDSL</t>
-  </si>
-  <si>
-    <t>INDMINMOTELE</t>
-  </si>
-  <si>
-    <t>INDMINUNIT</t>
-  </si>
-  <si>
-    <t>INDMINHPHLPG</t>
-  </si>
-  <si>
-    <t>INDMINHPHHFO</t>
-  </si>
-  <si>
-    <t>INDMINHPHDSL</t>
-  </si>
-  <si>
-    <t>INDMINHPHCOA</t>
-  </si>
-  <si>
-    <t>INDMINHPHBIO</t>
-  </si>
-  <si>
-    <t>INDKILNBIO</t>
-  </si>
-  <si>
-    <t>INDASHHPHBIO</t>
-  </si>
-  <si>
-    <t>INDASHHPHLPG</t>
-  </si>
-  <si>
-    <t>INDASHHPHHFO</t>
-  </si>
-  <si>
-    <t>INDASHHPHDSL</t>
-  </si>
-  <si>
-    <t>INDASHHPHCOA</t>
-  </si>
-  <si>
-    <t>INDPLANTASH</t>
-  </si>
-  <si>
-    <t>INDKILNDSL</t>
-  </si>
-  <si>
-    <t>INDKILNLPG</t>
-  </si>
-  <si>
-    <t>INDKILNHFO</t>
-  </si>
-  <si>
-    <t>INDKILNCOA</t>
-  </si>
-  <si>
-    <t>INDPLANTCEM</t>
-  </si>
-  <si>
-    <t>TRAELCRAILP</t>
-  </si>
-  <si>
-    <t>TRADSLRAILP</t>
-  </si>
-  <si>
-    <t>DEMMINWAT</t>
-  </si>
-  <si>
-    <t>DEMRESWAT</t>
-  </si>
-  <si>
-    <t>DEMOTHWAT</t>
-  </si>
-  <si>
-    <t>DEMPWRWAT</t>
-  </si>
-  <si>
-    <t>DEMGOVWAT</t>
-  </si>
-  <si>
-    <t>DEMAGRWAT</t>
-  </si>
-  <si>
-    <t>WATSURMIN</t>
-  </si>
-  <si>
-    <t>WATGWTMIN</t>
-  </si>
-  <si>
-    <t>IMPWAT</t>
-  </si>
-  <si>
-    <t>PWRCOA003</t>
-  </si>
-  <si>
-    <t>WSTLFLGEN</t>
-  </si>
-  <si>
-    <t>WSTINCGEN</t>
-  </si>
-  <si>
-    <t>LVSCTLCF</t>
-  </si>
-  <si>
-    <t>LVSGOACF</t>
-  </si>
-  <si>
-    <t>LVSSHPCF</t>
-  </si>
-  <si>
-    <t>DEMPWRSOL</t>
-  </si>
-  <si>
-    <t>DEMPWRWND</t>
-  </si>
-  <si>
-    <t>DEMPWRGEO</t>
-  </si>
-  <si>
-    <t>MINSOL</t>
-  </si>
-  <si>
-    <t>MINWND</t>
-  </si>
-  <si>
-    <t>MINGEO</t>
-  </si>
-  <si>
-    <t>PWRCOA_CCS</t>
-  </si>
-  <si>
-    <t>PWRBIO_CCS</t>
-  </si>
-  <si>
-    <t>LWTADA</t>
-  </si>
-  <si>
-    <t>LWTCAR</t>
-  </si>
-  <si>
-    <t>LWTLAG</t>
-  </si>
-  <si>
-    <t>LWTLAT</t>
-  </si>
-  <si>
-    <t>LWTSPT</t>
-  </si>
-  <si>
-    <t>LWTSWR</t>
-  </si>
-  <si>
-    <t>LWTGEN</t>
-  </si>
-  <si>
-    <t>TRADSLMCYNEW</t>
-  </si>
-  <si>
-    <t>MINNGS</t>
-  </si>
-  <si>
-    <t>MINCOA</t>
-  </si>
-  <si>
-    <t>PWRNGS001</t>
-  </si>
-  <si>
-    <t>PWRCOA001</t>
-  </si>
-  <si>
-    <t>PWRSOL001</t>
-  </si>
-  <si>
-    <t>PWRTRN</t>
-  </si>
-  <si>
-    <t>PWRNGS002</t>
-  </si>
-  <si>
-    <t>MINBIO</t>
-  </si>
-  <si>
-    <t>PWRBIO001</t>
-  </si>
-  <si>
-    <t>COMELCCUR</t>
-  </si>
-  <si>
-    <t>RESELCCUR</t>
-  </si>
-  <si>
-    <t>PWRWND001</t>
-  </si>
-  <si>
-    <t>PWRWND001S</t>
+    <t>S11</t>
+  </si>
+  <si>
+    <t>S12</t>
+  </si>
+  <si>
+    <t>S13</t>
+  </si>
+  <si>
+    <t>S14</t>
+  </si>
+  <si>
+    <t>S21</t>
+  </si>
+  <si>
+    <t>S22</t>
+  </si>
+  <si>
+    <t>S23</t>
+  </si>
+  <si>
+    <t>S24</t>
+  </si>
+  <si>
+    <t>URN</t>
+  </si>
+  <si>
+    <t>TRANMT</t>
+  </si>
+  <si>
+    <t>TRANGS</t>
+  </si>
+  <si>
+    <t>BIOWDY</t>
+  </si>
+  <si>
+    <t>CRU</t>
+  </si>
+  <si>
+    <t>BIOWST</t>
+  </si>
+  <si>
+    <t>INDCHMMDR</t>
+  </si>
+  <si>
+    <t>IOT</t>
+  </si>
+  <si>
+    <t>INDFBTMDR</t>
+  </si>
+  <si>
+    <t>PETLND</t>
+  </si>
+  <si>
+    <t>INDOTHHTH</t>
+  </si>
+  <si>
+    <t>INDOTHMDR</t>
+  </si>
+  <si>
+    <t>OTH</t>
+  </si>
+  <si>
+    <t>INDMERHTH</t>
+  </si>
+  <si>
+    <t>INDMERMDR</t>
+  </si>
+  <si>
+    <t>MER</t>
+  </si>
+  <si>
+    <t>INDCHMHTH</t>
+  </si>
+  <si>
+    <t>CHM</t>
+  </si>
+  <si>
+    <t>FBT</t>
+  </si>
+  <si>
+    <t>INDFBTHTH</t>
+  </si>
+  <si>
+    <t>INDHDG</t>
+  </si>
+  <si>
+    <t>FSH</t>
+  </si>
+  <si>
+    <t>INDWST</t>
+  </si>
+  <si>
+    <t>INDCOA</t>
+  </si>
+  <si>
+    <t>INDNGS</t>
+  </si>
+  <si>
+    <t>INDHFO</t>
+  </si>
+  <si>
+    <t>CEM</t>
+  </si>
+  <si>
+    <t>FER</t>
+  </si>
+  <si>
+    <t>AGRMCH</t>
+  </si>
+  <si>
+    <t>TRAPRL</t>
+  </si>
+  <si>
+    <t>TRAFRL</t>
+  </si>
+  <si>
+    <t>TRANAV</t>
+  </si>
+  <si>
+    <t>TRAAVI</t>
+  </si>
+  <si>
+    <t>RESELCOTHR</t>
+  </si>
+  <si>
+    <t>RESLGTR</t>
+  </si>
+  <si>
+    <t>RESCKNR</t>
+  </si>
+  <si>
+    <t>RESWTHR</t>
+  </si>
+  <si>
+    <t>CRPSOY</t>
+  </si>
+  <si>
+    <t>CRPSOR</t>
+  </si>
+  <si>
+    <t>CRPSES</t>
+  </si>
+  <si>
+    <t>CRPVEG</t>
+  </si>
+  <si>
+    <t>CRPRIC</t>
+  </si>
+  <si>
+    <t>HDG</t>
+  </si>
+  <si>
+    <t>INDIRSHTH</t>
+  </si>
+  <si>
+    <t>INDSCR</t>
+  </si>
+  <si>
+    <t>INDSTL</t>
+  </si>
+  <si>
+    <t>STL</t>
+  </si>
+  <si>
+    <t>NMM</t>
+  </si>
+  <si>
+    <t>CLK</t>
+  </si>
+  <si>
+    <t>CSP</t>
+  </si>
+  <si>
+    <t>LWTCOL</t>
+  </si>
+  <si>
+    <t>LWT</t>
+  </si>
+  <si>
+    <t>TRALPG</t>
+  </si>
+  <si>
+    <t>PWRWND</t>
+  </si>
+  <si>
+    <t>PWRLFO</t>
+  </si>
+  <si>
+    <t>WND</t>
+  </si>
+  <si>
+    <t>LFO</t>
+  </si>
+  <si>
+    <t>PWRLFG</t>
+  </si>
+  <si>
+    <t>LFG</t>
+  </si>
+  <si>
+    <t>WSTHET</t>
+  </si>
+  <si>
+    <t>WSTHAZ</t>
+  </si>
+  <si>
+    <t>WSTPLA</t>
+  </si>
+  <si>
+    <t>WSTPPR</t>
+  </si>
+  <si>
+    <t>WSTMET</t>
+  </si>
+  <si>
+    <t>WSTRES</t>
+  </si>
+  <si>
+    <t>WSTCLT</t>
+  </si>
+  <si>
+    <t>WETLND</t>
+  </si>
+  <si>
+    <t>DUM</t>
+  </si>
+  <si>
+    <t>DUM2</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>ELC001</t>
+  </si>
+  <si>
+    <t>ELC002</t>
+  </si>
+  <si>
+    <t>ELC003</t>
+  </si>
+  <si>
+    <t>INDELC</t>
+  </si>
+  <si>
+    <t>RESELC</t>
+  </si>
+  <si>
+    <t>COMELC</t>
+  </si>
+  <si>
+    <t>HFO</t>
+  </si>
+  <si>
+    <t>OIL</t>
+  </si>
+  <si>
+    <t>COA</t>
+  </si>
+  <si>
+    <t>NGS</t>
+  </si>
+  <si>
+    <t>SOL</t>
+  </si>
+  <si>
+    <t>GEO</t>
+  </si>
+  <si>
+    <t>BIO</t>
+  </si>
+  <si>
+    <t>LND</t>
+  </si>
+  <si>
+    <t>CRPPLA</t>
+  </si>
+  <si>
+    <t>CRPMAI</t>
+  </si>
+  <si>
+    <t>CRPCAS</t>
+  </si>
+  <si>
+    <t>CRPBEA</t>
+  </si>
+  <si>
+    <t>CRPCOF</t>
+  </si>
+  <si>
+    <t>CRPGRO</t>
+  </si>
+  <si>
+    <t>CRPPTS</t>
+  </si>
+  <si>
+    <t>CRPSUN</t>
+  </si>
+  <si>
+    <t>CRPOTC</t>
+  </si>
+  <si>
+    <t>LFOR</t>
+  </si>
+  <si>
+    <t>LBLT</t>
+  </si>
+  <si>
+    <t>LWAT</t>
+  </si>
+  <si>
+    <t>LOTH</t>
+  </si>
+  <si>
+    <t>WTRPRC</t>
+  </si>
+  <si>
+    <t>AGRWAT</t>
+  </si>
+  <si>
+    <t>WTREVT</t>
+  </si>
+  <si>
+    <t>WTRGWT</t>
+  </si>
+  <si>
+    <t>WTRSUR</t>
+  </si>
+  <si>
+    <t>PUBWAT</t>
+  </si>
+  <si>
+    <t>PWRWAT</t>
+  </si>
+  <si>
+    <t>DSL</t>
+  </si>
+  <si>
+    <t>AGRDSL</t>
+  </si>
+  <si>
+    <t>RESCKNU</t>
+  </si>
+  <si>
+    <t>COMHEL</t>
+  </si>
+  <si>
+    <t>CRPLND</t>
+  </si>
+  <si>
+    <t>GRALND</t>
+  </si>
+  <si>
+    <t>SHRLND</t>
+  </si>
+  <si>
+    <t>PSTCU</t>
+  </si>
+  <si>
+    <t>PSTCF</t>
+  </si>
+  <si>
+    <t>CTL</t>
+  </si>
+  <si>
+    <t>SHP</t>
+  </si>
+  <si>
+    <t>GOA</t>
+  </si>
+  <si>
+    <t>PWRCOA</t>
+  </si>
+  <si>
+    <t>INDBIO</t>
+  </si>
+  <si>
+    <t>PWRBIO</t>
+  </si>
+  <si>
+    <t>PWRHYD</t>
+  </si>
+  <si>
+    <t>PWRHFO</t>
+  </si>
+  <si>
+    <t>PWRNGS</t>
+  </si>
+  <si>
+    <t>PWRSOL</t>
   </si>
   <si>
     <t>PWRGEO</t>
   </si>
   <si>
-    <t>PWROHC002</t>
-  </si>
-  <si>
-    <t>PWROHC003</t>
-  </si>
-  <si>
-    <t>MINURN</t>
-  </si>
-  <si>
-    <t>PWRNUC</t>
-  </si>
-  <si>
-    <t>IMPBIO</t>
-  </si>
-  <si>
-    <t>IMPLPG</t>
-  </si>
-  <si>
-    <t>IMPHFO</t>
-  </si>
-  <si>
-    <t>IMPNGS</t>
-  </si>
-  <si>
-    <t>IMPURN</t>
-  </si>
-  <si>
-    <t>PWRTRNIMP</t>
-  </si>
-  <si>
-    <t>PWRTRNEXP</t>
-  </si>
-  <si>
-    <t>MINLND</t>
-  </si>
-  <si>
-    <t>LNDFOR</t>
-  </si>
-  <si>
-    <t>LNDBLT</t>
-  </si>
-  <si>
-    <t>LNDWAT</t>
-  </si>
-  <si>
-    <t>LNDOTH</t>
-  </si>
-  <si>
-    <t>PWRCSP002</t>
-  </si>
-  <si>
-    <t>PWRCSP001</t>
-  </si>
-  <si>
-    <t>PWRSOL001S</t>
-  </si>
-  <si>
-    <t>BACKSTOP001</t>
-  </si>
-  <si>
-    <t>BSTOPCOMELC</t>
-  </si>
-  <si>
-    <t>BSTOPRESELC</t>
-  </si>
-  <si>
-    <t>MINPRC</t>
-  </si>
-  <si>
-    <t>WATSURAGR</t>
-  </si>
-  <si>
-    <t>WATGWTAGR</t>
-  </si>
-  <si>
-    <t>WATSURPUB</t>
-  </si>
-  <si>
-    <t>WATGWTPUB</t>
-  </si>
-  <si>
-    <t>LNDMAIHR</t>
-  </si>
-  <si>
-    <t>LNDMAILR</t>
-  </si>
-  <si>
-    <t>LNDMAIHI</t>
-  </si>
-  <si>
-    <t>LNDMAILI</t>
-  </si>
-  <si>
-    <t>LNDPULHR</t>
-  </si>
-  <si>
-    <t>LNDPULLR</t>
-  </si>
-  <si>
-    <t>LNDPULHI</t>
-  </si>
-  <si>
-    <t>LNDPULLI</t>
-  </si>
-  <si>
-    <t>LNDSORHR</t>
-  </si>
-  <si>
-    <t>LNDSORLR</t>
-  </si>
-  <si>
-    <t>LNDSORHI</t>
-  </si>
-  <si>
-    <t>LNDSORLI</t>
-  </si>
-  <si>
-    <t>LNDMTPHR</t>
-  </si>
-  <si>
-    <t>LNDMTPLR</t>
-  </si>
-  <si>
-    <t>LNDMTPHI</t>
-  </si>
-  <si>
-    <t>LNDMTPLI</t>
-  </si>
-  <si>
-    <t>LNDGROHR</t>
-  </si>
-  <si>
-    <t>LNDGROLR</t>
-  </si>
-  <si>
-    <t>LNDGROHI</t>
-  </si>
-  <si>
-    <t>LNDGROLI</t>
-  </si>
-  <si>
-    <t>LNDWHEHR</t>
-  </si>
-  <si>
-    <t>LNDWHELR</t>
-  </si>
-  <si>
-    <t>LNDWHEHI</t>
-  </si>
-  <si>
-    <t>LNDWHELI</t>
-  </si>
-  <si>
-    <t>LNDSUNHR</t>
-  </si>
-  <si>
-    <t>LNDSUNLR</t>
-  </si>
-  <si>
-    <t>LNDSUNHI</t>
-  </si>
-  <si>
-    <t>LNDSUNLI</t>
-  </si>
-  <si>
-    <t>LNDOTCHR</t>
-  </si>
-  <si>
-    <t>LNDOTCLR</t>
-  </si>
-  <si>
-    <t>LNDOTCHI</t>
-  </si>
-  <si>
-    <t>LNDOTCLI</t>
-  </si>
-  <si>
-    <t>IMPMAI</t>
-  </si>
-  <si>
-    <t>IMPPUL</t>
-  </si>
-  <si>
-    <t>IMPSOR</t>
-  </si>
-  <si>
-    <t>IMPMTP</t>
-  </si>
-  <si>
-    <t>IMPGRO</t>
-  </si>
-  <si>
-    <t>IMPWHE</t>
-  </si>
-  <si>
-    <t>IMPSUN</t>
-  </si>
-  <si>
-    <t>IMPOTC</t>
-  </si>
-  <si>
-    <t>WATSURPWR</t>
-  </si>
-  <si>
-    <t>WATGWTPWR</t>
-  </si>
-  <si>
-    <t>IMPDSL</t>
-  </si>
-  <si>
-    <t>PWRDSL</t>
-  </si>
-  <si>
-    <t>RESELCCKN</t>
-  </si>
-  <si>
-    <t>RESBIOCKN</t>
-  </si>
-  <si>
-    <t>TRAELCMCYCUR</t>
-  </si>
-  <si>
-    <t>TRAELCCARCUR</t>
-  </si>
-  <si>
-    <t>TRAELCBUSCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLCARCUR</t>
-  </si>
-  <si>
-    <t>TRADSLBUSCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLMCYCUR</t>
-  </si>
-  <si>
-    <t>RESELCEFF</t>
-  </si>
-  <si>
-    <t>RESELCBST</t>
-  </si>
-  <si>
-    <t>COMELCEFF</t>
-  </si>
-  <si>
-    <t>COMELCBST</t>
-  </si>
-  <si>
-    <t>COMDSLHET</t>
-  </si>
-  <si>
-    <t>COMBIOHET</t>
-  </si>
-  <si>
-    <t>COMELCHET</t>
-  </si>
-  <si>
-    <t>RESBIOHEL</t>
-  </si>
-  <si>
-    <t>RESELCHEL</t>
-  </si>
-  <si>
-    <t>BSTOPMCY</t>
-  </si>
-  <si>
-    <t>BSTOPCAR</t>
-  </si>
-  <si>
-    <t>BSTOPBUS</t>
-  </si>
-  <si>
-    <t>BSTOPCOMHET</t>
-  </si>
-  <si>
-    <t>BSTOPRESHEL</t>
-  </si>
-  <si>
-    <t>BSTOPRESCKN</t>
-  </si>
-  <si>
-    <t>COMCOAHET</t>
-  </si>
-  <si>
-    <t>EXPMAI</t>
-  </si>
-  <si>
-    <t>EXPSOR</t>
-  </si>
-  <si>
-    <t>EXPMTP</t>
-  </si>
-  <si>
-    <t>EXPWHE</t>
-  </si>
-  <si>
-    <t>EXPSUN</t>
-  </si>
-  <si>
-    <t>LNDCRP</t>
-  </si>
-  <si>
-    <t>EXPOTC</t>
-  </si>
-  <si>
-    <t>EXPCOA</t>
-  </si>
-  <si>
-    <t>LNDGRS</t>
-  </si>
-  <si>
-    <t>LNDPSTCU</t>
-  </si>
-  <si>
-    <t>LNDPSTCF</t>
-  </si>
-  <si>
-    <t>LVSCTLCU</t>
-  </si>
-  <si>
-    <t>LVSGOACU</t>
-  </si>
-  <si>
-    <t>LVSSHPCU</t>
-  </si>
-  <si>
-    <t>DEMINDELC</t>
-  </si>
-  <si>
-    <t>DEMINDCOA</t>
-  </si>
-  <si>
-    <t>DEMINDBIO</t>
-  </si>
-  <si>
-    <t>DEMRESELC</t>
-  </si>
-  <si>
-    <t>DEMRESBIO</t>
-  </si>
-  <si>
-    <t>DEMCOMCOA</t>
-  </si>
-  <si>
-    <t>DEMCOMBIO</t>
-  </si>
-  <si>
-    <t>DEMCOMELC</t>
-  </si>
-  <si>
-    <t>DEMPWRCOA</t>
-  </si>
-  <si>
-    <t>DEMPWRNGS</t>
-  </si>
-  <si>
-    <t>DEMPWRBIO</t>
-  </si>
-  <si>
-    <t>DEMPWRHFO</t>
-  </si>
-  <si>
-    <t>DEMPWRURN</t>
-  </si>
-  <si>
-    <t>DEMPWRDSL</t>
-  </si>
-  <si>
-    <t>DEMTRAELC</t>
-  </si>
-  <si>
-    <t>DEMTRAGSL</t>
-  </si>
-  <si>
-    <t>DEMTRADSL</t>
-  </si>
-  <si>
-    <t>DEMINDHFO</t>
-  </si>
-  <si>
-    <t>DEMINDDSL</t>
-  </si>
-  <si>
-    <t>DEMINDLPG</t>
-  </si>
-  <si>
-    <t>DEMCOMDSL</t>
-  </si>
-  <si>
-    <t>DEMRESLPG</t>
-  </si>
-  <si>
-    <t>DEMRESKER</t>
-  </si>
-  <si>
-    <t>RESDSLHEL</t>
-  </si>
-  <si>
-    <t>RESLPGHEL</t>
-  </si>
-  <si>
-    <t>RESLPGCKN</t>
-  </si>
-  <si>
-    <t>RESELCLGT</t>
-  </si>
-  <si>
-    <t>RESKERLGT</t>
-  </si>
-  <si>
-    <t>RESBIOLGT</t>
-  </si>
-  <si>
-    <t>RESELCCOL</t>
-  </si>
-  <si>
-    <t>DEMTRAJETKER</t>
-  </si>
-  <si>
-    <t>TRAJFLAVI</t>
-  </si>
-  <si>
-    <t>RESELCWHT</t>
-  </si>
-  <si>
-    <t>RESDSLWHT</t>
-  </si>
-  <si>
-    <t>RESBIOWHT</t>
-  </si>
-  <si>
-    <t>RESLPGWHT</t>
-  </si>
-  <si>
-    <t>RESKERWHT</t>
-  </si>
-  <si>
-    <t>COMLPGHET</t>
-  </si>
-  <si>
-    <t>IMPKER</t>
-  </si>
-  <si>
-    <t>TRADSLCARCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLCARNEW</t>
-  </si>
-  <si>
-    <t>TRADSLCARNEW</t>
-  </si>
-  <si>
-    <t>TRADSHCARNEW</t>
-  </si>
-  <si>
-    <t>TRAELCCARNEW</t>
-  </si>
-  <si>
-    <t>TRAGSLMCYNEW</t>
-  </si>
-  <si>
-    <t>TRAELCMCYNEW</t>
-  </si>
-  <si>
-    <t>TRADSLBUSNEW</t>
-  </si>
-  <si>
-    <t>TRADSHBUSNEW</t>
-  </si>
-  <si>
-    <t>TRAELCBUSNEW</t>
-  </si>
-  <si>
-    <t>IMPGSL</t>
-  </si>
-  <si>
-    <t>RESKERCKN</t>
-  </si>
-  <si>
-    <t>DEMRESDSL</t>
-  </si>
-  <si>
-    <t>TRAGSLMNBCUR</t>
-  </si>
-  <si>
-    <t>TRADSLMNBCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLMNBNEW</t>
-  </si>
-  <si>
-    <t>TRADSLMNBNEW</t>
-  </si>
-  <si>
-    <t>TRADSHMNBNEW</t>
-  </si>
-  <si>
-    <t>TRAELCMNBCUR</t>
-  </si>
-  <si>
-    <t>TRAELCMNBNEW</t>
-  </si>
-  <si>
-    <t>TRAGSLLTRCUR</t>
-  </si>
-  <si>
-    <t>TRADSLLTRCUR</t>
-  </si>
-  <si>
-    <t>TRAGSLLTRNEW</t>
-  </si>
-  <si>
-    <t>TRADSLLTRNEW</t>
-  </si>
-  <si>
-    <t>TRADSHLTRNEW</t>
-  </si>
-  <si>
-    <t>TRAELCLTRCUR</t>
-  </si>
-  <si>
-    <t>TRAELCLTRNEW</t>
-  </si>
-  <si>
-    <t>TRADSLMTRCUR</t>
-  </si>
-  <si>
-    <t>TRADSLMTRNEW</t>
-  </si>
-  <si>
-    <t>TRAELCMTRCUR</t>
-  </si>
-  <si>
-    <t>TRAELCMTRNEW</t>
-  </si>
-  <si>
-    <t>TRADSLHTRCUR</t>
-  </si>
-  <si>
-    <t>TRADSLHTRNEW</t>
-  </si>
-  <si>
-    <t>TRAELCHTRCUR</t>
-  </si>
-  <si>
-    <t>TRAELCHTRNEW</t>
-  </si>
-  <si>
-    <t>DEMCOMLPG</t>
-  </si>
-  <si>
-    <t>DEMRESSOL</t>
-  </si>
-  <si>
-    <t>BSTOPRESWHT</t>
-  </si>
-  <si>
-    <t>BSTOPRESLGT</t>
-  </si>
-  <si>
-    <t>RESLPGLGT</t>
-  </si>
-  <si>
-    <t>DUMDEFOR</t>
-  </si>
-  <si>
-    <t>DUMREFOR</t>
-  </si>
-  <si>
-    <t>WSTGEN</t>
-  </si>
-  <si>
-    <t>WSTOPB</t>
-  </si>
-  <si>
-    <t>WSTDMP</t>
-  </si>
-  <si>
-    <t>WSTCOL</t>
-  </si>
-  <si>
-    <t>WSTUNS</t>
-  </si>
-  <si>
-    <t>WSTORG</t>
-  </si>
-  <si>
-    <t>WSTSEP</t>
-  </si>
-  <si>
-    <t>WSTDGS</t>
-  </si>
-  <si>
-    <t>WSTCMP</t>
-  </si>
-  <si>
-    <t>WSTMTR</t>
-  </si>
-  <si>
-    <t>WSTPAR</t>
-  </si>
-  <si>
-    <t>WSTPLR</t>
-  </si>
-  <si>
-    <t>WSTGLR</t>
-  </si>
-  <si>
-    <t>WSTHZD</t>
-  </si>
-  <si>
-    <t>WSTINCRES</t>
-  </si>
-  <si>
-    <t>WSTLFLRES</t>
-  </si>
-  <si>
-    <t>DEMPWRLFG</t>
-  </si>
-  <si>
-    <t>PWRLFG001</t>
-  </si>
-  <si>
-    <t>PWRCOA002</t>
-  </si>
-  <si>
-    <t>MINBGS</t>
-  </si>
-  <si>
-    <t>DEMRESBGS</t>
-  </si>
-  <si>
-    <t>RESBGSCKN</t>
-  </si>
-  <si>
-    <t>RESBGSHEL</t>
-  </si>
-  <si>
-    <t>RESBGSWHT</t>
-  </si>
-  <si>
-    <t>TRADSLRAILF</t>
-  </si>
-  <si>
-    <t>TRAELCRAILF</t>
-  </si>
-  <si>
-    <t>S11</t>
-  </si>
-  <si>
-    <t>S12</t>
-  </si>
-  <si>
-    <t>S13</t>
-  </si>
-  <si>
-    <t>S14</t>
-  </si>
-  <si>
-    <t>S21</t>
-  </si>
-  <si>
-    <t>S22</t>
-  </si>
-  <si>
-    <t>S23</t>
-  </si>
-  <si>
-    <t>S24</t>
-  </si>
-  <si>
-    <t>PWRWAT0</t>
-  </si>
-  <si>
-    <t>MINWAT0</t>
-  </si>
-  <si>
-    <t>AGRWAT1</t>
-  </si>
-  <si>
-    <t>AGRWAT0</t>
-  </si>
-  <si>
-    <t>LWET</t>
-  </si>
-  <si>
-    <t>LVSOTH</t>
-  </si>
-  <si>
-    <t>CRPCAN</t>
-  </si>
-  <si>
-    <t>AGRELCOTH</t>
-  </si>
-  <si>
-    <t>AGRHEAT</t>
-  </si>
-  <si>
-    <t>AGRMOT</t>
-  </si>
-  <si>
-    <t>AGRLPG</t>
-  </si>
-  <si>
-    <t>AGRCOA</t>
+    <t>PWROIL</t>
+  </si>
+  <si>
+    <t>COMHEH</t>
+  </si>
+  <si>
+    <t>PWRCSP</t>
+  </si>
+  <si>
+    <t>COMELCOTH</t>
+  </si>
+  <si>
+    <t>RESELCOTHU</t>
+  </si>
+  <si>
+    <t>GSL</t>
+  </si>
+  <si>
+    <t>LPG</t>
+  </si>
+  <si>
+    <t>KER</t>
+  </si>
+  <si>
+    <t>INDDSL</t>
+  </si>
+  <si>
+    <t>INDGSL</t>
+  </si>
+  <si>
+    <t>INDKER</t>
+  </si>
+  <si>
+    <t>COMDSL</t>
+  </si>
+  <si>
+    <t>COMLPG</t>
+  </si>
+  <si>
+    <t>RESLPG</t>
+  </si>
+  <si>
+    <t>RESKER</t>
+  </si>
+  <si>
+    <t>AGRGSL</t>
+  </si>
+  <si>
+    <t>RESLGTU</t>
+  </si>
+  <si>
+    <t>RESCOLU</t>
+  </si>
+  <si>
+    <t>CHA</t>
+  </si>
+  <si>
+    <t>RESCHA</t>
+  </si>
+  <si>
+    <t>COMCHA</t>
+  </si>
+  <si>
+    <t>RESSPHR</t>
+  </si>
+  <si>
+    <t>RESWTHU</t>
+  </si>
+  <si>
+    <t>COMCOA</t>
+  </si>
+  <si>
+    <t>BGS</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>RIH</t>
+  </si>
+  <si>
+    <t>RESBGS</t>
+  </si>
+  <si>
+    <t>RESBIO</t>
+  </si>
+  <si>
+    <t>INDCHA</t>
+  </si>
+  <si>
+    <t>COMBIO</t>
+  </si>
+  <si>
+    <t>COMBGS</t>
+  </si>
+  <si>
+    <t>TRAELC</t>
+  </si>
+  <si>
+    <t>TRACAR</t>
+  </si>
+  <si>
+    <t>TRAGSL</t>
+  </si>
+  <si>
+    <t>TRADSL</t>
+  </si>
+  <si>
+    <t>TRABUS</t>
+  </si>
+  <si>
+    <t>TRAMNB</t>
+  </si>
+  <si>
+    <t>TRAMCY</t>
+  </si>
+  <si>
+    <t>TRALTR</t>
+  </si>
+  <si>
+    <t>TRAMTR</t>
+  </si>
+  <si>
+    <t>TRAHTR</t>
+  </si>
+  <si>
+    <t>TRAKER</t>
   </si>
   <si>
     <t>AGRELC</t>
   </si>
   <si>
-    <t>TRABIOF</t>
-  </si>
-  <si>
-    <t>TRABIO</t>
-  </si>
-  <si>
-    <t>TRAJFL</t>
-  </si>
-  <si>
-    <t>TOURELCOTH</t>
-  </si>
-  <si>
-    <t>TOURHET</t>
-  </si>
-  <si>
-    <t>TOURELC</t>
-  </si>
-  <si>
-    <t>TOURCOA</t>
-  </si>
-  <si>
-    <t>TOURBIO</t>
-  </si>
-  <si>
-    <t>TOURDSL</t>
-  </si>
-  <si>
-    <t>TOURLPG</t>
-  </si>
-  <si>
-    <t>PWRCBM</t>
-  </si>
-  <si>
-    <t>JETKER</t>
-  </si>
-  <si>
-    <t>CBM</t>
-  </si>
-  <si>
-    <t>INDOTHLPH</t>
-  </si>
-  <si>
-    <t>INDOTHHPH</t>
-  </si>
-  <si>
-    <t>INDOTH</t>
-  </si>
-  <si>
-    <t>INDMINMOT</t>
-  </si>
-  <si>
-    <t>CLK</t>
-  </si>
-  <si>
-    <t>INDHPHASH</t>
-  </si>
-  <si>
-    <t>INDHPHMIN</t>
-  </si>
-  <si>
-    <t>INDASH</t>
-  </si>
-  <si>
-    <t>INDCEM</t>
-  </si>
-  <si>
-    <t>TRARAILP</t>
-  </si>
-  <si>
-    <t>WSTWAT</t>
-  </si>
-  <si>
-    <t>RESWAT</t>
-  </si>
-  <si>
-    <t>OTHWAT</t>
-  </si>
-  <si>
-    <t>GOVWAT</t>
-  </si>
-  <si>
-    <t>MINWAT1</t>
-  </si>
-  <si>
-    <t>INDDSL</t>
-  </si>
-  <si>
-    <t>PWRSOL</t>
-  </si>
-  <si>
-    <t>PWRWND</t>
-  </si>
-  <si>
-    <t>SOL</t>
-  </si>
-  <si>
-    <t>WND</t>
-  </si>
-  <si>
-    <t>GEO</t>
-  </si>
-  <si>
-    <t>LWTCOL</t>
-  </si>
-  <si>
-    <t>LWT</t>
-  </si>
-  <si>
-    <t>NGS</t>
-  </si>
-  <si>
-    <t>COA</t>
-  </si>
-  <si>
-    <t>ELC001</t>
-  </si>
-  <si>
-    <t>ELC002</t>
-  </si>
-  <si>
-    <t>BIO</t>
-  </si>
-  <si>
-    <t>COMELCOTH</t>
-  </si>
-  <si>
-    <t>RESELCOTH</t>
-  </si>
-  <si>
-    <t>HFO</t>
-  </si>
-  <si>
-    <t>URN</t>
-  </si>
-  <si>
-    <t>LND</t>
-  </si>
-  <si>
-    <t>CRPMAI</t>
-  </si>
-  <si>
-    <t>CRPSOR</t>
-  </si>
-  <si>
-    <t>CRPMTP</t>
-  </si>
-  <si>
-    <t>CRPPUL</t>
-  </si>
-  <si>
-    <t>LFOR</t>
-  </si>
-  <si>
-    <t>LBLT</t>
-  </si>
-  <si>
-    <t>LWAT</t>
-  </si>
-  <si>
-    <t>LOTH</t>
-  </si>
-  <si>
-    <t>WATPRC</t>
-  </si>
-  <si>
-    <t>AGRWAT2</t>
-  </si>
-  <si>
-    <t>WATEVT</t>
-  </si>
-  <si>
-    <t>WATGWT</t>
-  </si>
-  <si>
-    <t>WATSUR</t>
-  </si>
-  <si>
-    <t>CRPGRO</t>
-  </si>
-  <si>
-    <t>CRPWHE</t>
-  </si>
-  <si>
-    <t>PUBWAT</t>
-  </si>
-  <si>
-    <t>CRPSUN</t>
-  </si>
-  <si>
-    <t>CRPOTC</t>
-  </si>
-  <si>
-    <t>PWRWAT1</t>
-  </si>
-  <si>
-    <t>DSL</t>
-  </si>
-  <si>
-    <t>RESCKN</t>
-  </si>
-  <si>
-    <t>TRAMCY</t>
-  </si>
-  <si>
-    <t>TRACAR</t>
-  </si>
-  <si>
-    <t>TRABUS</t>
-  </si>
-  <si>
-    <t>COMHET</t>
-  </si>
-  <si>
-    <t>RESHEL</t>
-  </si>
-  <si>
-    <t>CRPLND</t>
-  </si>
-  <si>
-    <t>LGRS</t>
-  </si>
-  <si>
-    <t>PSTCU</t>
-  </si>
-  <si>
-    <t>PSTCF</t>
-  </si>
-  <si>
-    <t>LVSCTL</t>
-  </si>
-  <si>
-    <t>LVSSHP</t>
-  </si>
-  <si>
-    <t>LVSGOA</t>
-  </si>
-  <si>
-    <t>INDELC</t>
-  </si>
-  <si>
-    <t>INDCOA</t>
-  </si>
-  <si>
-    <t>INDBIO</t>
-  </si>
-  <si>
-    <t>RESELC</t>
-  </si>
-  <si>
-    <t>RESBIO</t>
-  </si>
-  <si>
-    <t>COMELC</t>
-  </si>
-  <si>
-    <t>COMCOA</t>
-  </si>
-  <si>
-    <t>COMBIO</t>
-  </si>
-  <si>
-    <t>PWRNGS</t>
-  </si>
-  <si>
-    <t>PWRCOA</t>
-  </si>
-  <si>
-    <t>PWRBIO</t>
-  </si>
-  <si>
-    <t>PWRHFO</t>
-  </si>
-  <si>
-    <t>PWRURN</t>
-  </si>
-  <si>
-    <t>TRAELC001</t>
-  </si>
-  <si>
-    <t>TRAGSL</t>
-  </si>
-  <si>
-    <t>GSL</t>
-  </si>
-  <si>
-    <t>LPG</t>
-  </si>
-  <si>
-    <t>KER</t>
-  </si>
-  <si>
-    <t>INDHFO</t>
-  </si>
-  <si>
-    <t>INDMIN</t>
-  </si>
-  <si>
-    <t>INDLPG</t>
-  </si>
-  <si>
-    <t>COMDSL</t>
-  </si>
-  <si>
-    <t>RESLPG</t>
-  </si>
-  <si>
-    <t>RESKER</t>
-  </si>
-  <si>
-    <t>TRADSL</t>
-  </si>
-  <si>
-    <t>RESLGT</t>
-  </si>
-  <si>
-    <t>RESCOL</t>
-  </si>
-  <si>
-    <t>TRAAVI</t>
-  </si>
-  <si>
-    <t>TRAJETKER</t>
-  </si>
-  <si>
-    <t>RESDSL</t>
-  </si>
-  <si>
-    <t>RESWHT</t>
-  </si>
-  <si>
-    <t>RESSOL</t>
-  </si>
-  <si>
-    <t>COMLPG</t>
-  </si>
-  <si>
-    <t>TRAMNB</t>
-  </si>
-  <si>
-    <t>TRALTR</t>
-  </si>
-  <si>
-    <t>TRAMTR</t>
-  </si>
-  <si>
-    <t>TRAHTR</t>
-  </si>
-  <si>
-    <t>DUMLND</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>WSTCLT</t>
-  </si>
-  <si>
-    <t>WSTRES</t>
-  </si>
-  <si>
-    <t>WSTMET</t>
-  </si>
-  <si>
-    <t>WSTPPR</t>
-  </si>
-  <si>
-    <t>WSTPLA</t>
-  </si>
-  <si>
-    <t>WSTGLS</t>
-  </si>
-  <si>
-    <t>WSTHAZ</t>
-  </si>
-  <si>
-    <t>WSTHET</t>
-  </si>
-  <si>
-    <t>LFG</t>
-  </si>
-  <si>
-    <t>PWRLFG</t>
-  </si>
-  <si>
-    <t>BGS</t>
-  </si>
-  <si>
-    <t>RESBGS</t>
-  </si>
-  <si>
-    <t>TRARAILF</t>
-  </si>
-  <si>
-    <t>TRAELC002</t>
-  </si>
-  <si>
     <t>CO2</t>
   </si>
   <si>
     <t>CH4</t>
   </si>
   <si>
-    <t>N20</t>
+    <t>N2O</t>
   </si>
   <si>
     <t>CO2eq</t>
   </si>
   <si>
-    <t>LVSCO2eq</t>
-  </si>
-  <si>
-    <t>WSTCH4</t>
+    <t>MAN</t>
   </si>
   <si>
     <t>EXTIAP</t>
@@ -1692,19 +1977,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>STOBAT</t>
+    <t>STGBAT</t>
   </si>
   <si>
     <t>FORBAL</t>
@@ -1725,34 +1998,43 @@
     <t>ORGWST</t>
   </si>
   <si>
+    <t>RESELCCKGBALU</t>
+  </si>
+  <si>
+    <t>RESELCCURBALU</t>
+  </si>
+  <si>
+    <t>RESELCEFFBALU</t>
+  </si>
+  <si>
+    <t>RESELCBSTBALU</t>
+  </si>
+  <si>
+    <t>COMELCCURBAL</t>
+  </si>
+  <si>
+    <t>COMELCHELBAL</t>
+  </si>
+  <si>
+    <t>COMELCEFFBAL</t>
+  </si>
+  <si>
     <t>COMELCBSTBAL</t>
   </si>
   <si>
-    <t>COMELCEFFBAL</t>
-  </si>
-  <si>
-    <t>RESELCBSTBAL</t>
-  </si>
-  <si>
-    <t>RESELCEFFBAL</t>
-  </si>
-  <si>
-    <t>RESELCCOLBAL</t>
-  </si>
-  <si>
-    <t>RESELCHELBAL</t>
-  </si>
-  <si>
-    <t>RESELCLGTBAL</t>
-  </si>
-  <si>
-    <t>RESELCWHTBAL</t>
-  </si>
-  <si>
-    <t>RESELCCKNBAL</t>
-  </si>
-  <si>
-    <t>RESELCCURBAL</t>
+    <t>INDELCCURBAL</t>
+  </si>
+  <si>
+    <t>INDELCHEHBAL</t>
+  </si>
+  <si>
+    <t>INDELCHELBAL</t>
+  </si>
+  <si>
+    <t>INDELCEFFBAL</t>
+  </si>
+  <si>
+    <t>INDELCBSTBAL</t>
   </si>
   <si>
     <t>TOTLWT</t>
@@ -1761,115 +2043,103 @@
     <t>COLLWT</t>
   </si>
   <si>
-    <t>PWRREN</t>
-  </si>
-  <si>
-    <t>TRAMCYCAP</t>
-  </si>
-  <si>
-    <t>TRACARCAP</t>
-  </si>
-  <si>
-    <t>TRAMNBCAP</t>
-  </si>
-  <si>
-    <t>TRABUSCAP</t>
-  </si>
-  <si>
-    <t>TRARAILFCAP</t>
-  </si>
-  <si>
-    <t>TRALTRCAP</t>
-  </si>
-  <si>
     <t>RESMAR</t>
   </si>
   <si>
-    <t>DEMAGRWATSHARE</t>
-  </si>
-  <si>
-    <t>DEMPWRWATSHARE</t>
-  </si>
-  <si>
-    <t>DEMMINWATSHARE</t>
-  </si>
-  <si>
-    <t>IRRIGSHARE</t>
+    <t>RESELCCKGBALR</t>
+  </si>
+  <si>
+    <t>RESELCCURBALR</t>
+  </si>
+  <si>
+    <t>RESCKNCLNU</t>
+  </si>
+  <si>
+    <t>RESCKNCLNR</t>
+  </si>
+  <si>
+    <t>RESWTHCLU</t>
+  </si>
+  <si>
+    <t>RESWTHCLR</t>
+  </si>
+  <si>
+    <t>NEWCAPCAR</t>
+  </si>
+  <si>
+    <t>FALLND</t>
+  </si>
+  <si>
+    <t>EVCHRG001</t>
+  </si>
+  <si>
+    <t>EVCHRG002</t>
+  </si>
+  <si>
+    <t>EVCHRG003</t>
   </si>
   <si>
     <t>WETBAL</t>
   </si>
   <si>
-    <t>REWETBAL</t>
-  </si>
-  <si>
-    <t>TOTLND</t>
-  </si>
-  <si>
-    <t>CRPOTHBAL</t>
-  </si>
-  <si>
-    <t>DEFORBAL</t>
-  </si>
-  <si>
-    <t>LNDGRSBAL</t>
-  </si>
-  <si>
-    <t>2TRACAREVCAP</t>
-  </si>
-  <si>
-    <t>2TRAMCYEVCAP</t>
-  </si>
-  <si>
-    <t>2TRAMNBEVCAP</t>
-  </si>
-  <si>
-    <t>2TRABUSEVCAP</t>
-  </si>
-  <si>
-    <t>2TRALTREVCAP</t>
-  </si>
-  <si>
-    <t>2TRAMTREVCAP</t>
-  </si>
-  <si>
-    <t>2TRAHTREVCAP</t>
-  </si>
-  <si>
-    <t>RECWST</t>
-  </si>
-  <si>
-    <t>RESTRICTWAT</t>
-  </si>
-  <si>
-    <t>TRADSLHTRCURCAP</t>
-  </si>
-  <si>
-    <t>TRADSLHTRNEWCAP</t>
-  </si>
-  <si>
-    <t>TRAELCHTRCURCAP</t>
-  </si>
-  <si>
-    <t>TRAELCHTRNEWCAP</t>
-  </si>
-  <si>
-    <t>TRADSLMTRCURCAP</t>
-  </si>
-  <si>
-    <t>TRADSLMTRNEWCAP</t>
-  </si>
-  <si>
-    <t>TRAELCMTRCURCAP</t>
-  </si>
-  <si>
-    <t>TRAELCMTRNEWCAP</t>
-  </si>
-  <si>
-    <t>TRABUSACTCAP</t>
-  </si>
-  <si>
-    <t>INDOTHLPHELCSHARE</t>
+    <t>SHRBAL</t>
+  </si>
+  <si>
+    <t>GRSBAL</t>
+  </si>
+  <si>
+    <t>CRPBAL</t>
+  </si>
+  <si>
+    <t>PETBAL</t>
+  </si>
+  <si>
+    <t>EVCARSHR</t>
+  </si>
+  <si>
+    <t>NDCCTL</t>
+  </si>
+  <si>
+    <t>TEst</t>
+  </si>
+  <si>
+    <t>DEFORCNT</t>
+  </si>
+  <si>
+    <t>DEFORCHK</t>
+  </si>
+  <si>
+    <t>COMHETSHR</t>
+  </si>
+  <si>
+    <t>BRNWST</t>
+  </si>
+  <si>
+    <t>SANTSHAR</t>
+  </si>
+  <si>
+    <t>PWRBAL</t>
+  </si>
+  <si>
+    <t>SOLINV</t>
+  </si>
+  <si>
+    <t>BIOPWRCF</t>
+  </si>
+  <si>
+    <t>NEWCAPMNB</t>
+  </si>
+  <si>
+    <t>NEWCAPBUS</t>
+  </si>
+  <si>
+    <t>NEWCAPLTR</t>
+  </si>
+  <si>
+    <t>NEWCAPMTR</t>
+  </si>
+  <si>
+    <t>NEWCAPHTR</t>
   </si>
   <si>
     <t>category</t>
@@ -2651,7 +2921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O360"/>
+  <dimension ref="A1:O433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2753,19 +3023,19 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>357</v>
+        <v>430</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2780,7 +3050,7 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -2792,616 +3062,583 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="B4">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>388</v>
+        <v>461</v>
       </c>
       <c r="E4" t="s">
-        <v>396</v>
+        <v>469</v>
       </c>
       <c r="F4" t="s">
-        <v>541</v>
+        <v>637</v>
       </c>
       <c r="G4" t="s">
-        <v>553</v>
+        <v>648</v>
       </c>
       <c r="H4" t="s">
-        <v>554</v>
+        <v>649</v>
       </c>
       <c r="I4" t="s">
-        <v>553</v>
+        <v>648</v>
       </c>
       <c r="J4" t="s">
-        <v>553</v>
+        <v>648</v>
       </c>
       <c r="K4" t="s">
-        <v>553</v>
+        <v>648</v>
       </c>
       <c r="L4" t="s">
-        <v>562</v>
+        <v>653</v>
       </c>
       <c r="M4" t="s">
-        <v>562</v>
+        <v>653</v>
       </c>
       <c r="O4" t="s">
-        <v>563</v>
+        <v>654</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="B5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>389</v>
+        <v>462</v>
       </c>
       <c r="E5" t="s">
-        <v>397</v>
+        <v>470</v>
       </c>
       <c r="F5" t="s">
-        <v>542</v>
+        <v>638</v>
       </c>
       <c r="I5" t="s">
-        <v>555</v>
+        <v>650</v>
       </c>
       <c r="K5" t="s">
-        <v>555</v>
+        <v>650</v>
       </c>
       <c r="O5" t="s">
-        <v>564</v>
+        <v>655</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="B6">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>390</v>
+        <v>463</v>
       </c>
       <c r="E6" t="s">
-        <v>398</v>
+        <v>471</v>
       </c>
       <c r="F6" t="s">
-        <v>543</v>
+        <v>639</v>
       </c>
       <c r="K6" t="s">
-        <v>556</v>
+        <v>651</v>
       </c>
       <c r="O6" t="s">
-        <v>565</v>
+        <v>656</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="B7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>391</v>
+        <v>464</v>
       </c>
       <c r="E7" t="s">
-        <v>399</v>
+        <v>472</v>
       </c>
       <c r="F7" t="s">
-        <v>544</v>
+        <v>640</v>
       </c>
       <c r="K7" t="s">
-        <v>557</v>
+        <v>652</v>
       </c>
       <c r="O7" t="s">
-        <v>566</v>
+        <v>657</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="B8">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>392</v>
+        <v>465</v>
       </c>
       <c r="E8" t="s">
-        <v>400</v>
+        <v>473</v>
       </c>
       <c r="F8" t="s">
-        <v>545</v>
-      </c>
-      <c r="K8" t="s">
-        <v>558</v>
+        <v>641</v>
       </c>
       <c r="O8" t="s">
-        <v>567</v>
+        <v>658</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="B9">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C9" t="s">
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>393</v>
+        <v>466</v>
       </c>
       <c r="E9" t="s">
-        <v>401</v>
+        <v>474</v>
       </c>
       <c r="F9" t="s">
-        <v>546</v>
-      </c>
-      <c r="K9" t="s">
-        <v>559</v>
+        <v>642</v>
       </c>
       <c r="O9" t="s">
-        <v>568</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="C10" t="s">
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>467</v>
       </c>
       <c r="E10" t="s">
-        <v>402</v>
+        <v>475</v>
       </c>
       <c r="F10" t="s">
-        <v>547</v>
-      </c>
-      <c r="K10" t="s">
-        <v>560</v>
+        <v>643</v>
       </c>
       <c r="O10" t="s">
-        <v>569</v>
+        <v>660</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>395</v>
+        <v>468</v>
       </c>
       <c r="E11" t="s">
-        <v>403</v>
+        <v>476</v>
       </c>
       <c r="F11" t="s">
-        <v>548</v>
-      </c>
-      <c r="K11" t="s">
-        <v>561</v>
+        <v>644</v>
       </c>
       <c r="O11" t="s">
-        <v>570</v>
+        <v>661</v>
       </c>
     </row>
     <row r="12" spans="1:15">
       <c r="B12">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>404</v>
+        <v>477</v>
       </c>
       <c r="F12" t="s">
-        <v>549</v>
+        <v>645</v>
       </c>
       <c r="O12" t="s">
-        <v>571</v>
+        <v>662</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="B13">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="C13" t="s">
         <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>405</v>
+        <v>478</v>
       </c>
       <c r="F13" t="s">
-        <v>550</v>
+        <v>646</v>
       </c>
       <c r="O13" t="s">
-        <v>572</v>
+        <v>663</v>
       </c>
     </row>
     <row r="14" spans="1:15">
       <c r="B14">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C14" t="s">
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>406</v>
+        <v>479</v>
       </c>
       <c r="F14" t="s">
-        <v>551</v>
+        <v>647</v>
       </c>
       <c r="O14" t="s">
-        <v>573</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="B15">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="C15" t="s">
         <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>407</v>
-      </c>
-      <c r="F15" t="s">
-        <v>552</v>
+        <v>480</v>
       </c>
       <c r="O15" t="s">
-        <v>574</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="B16">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="C16" t="s">
         <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>408</v>
+        <v>481</v>
       </c>
       <c r="O16" t="s">
-        <v>575</v>
+        <v>666</v>
       </c>
     </row>
     <row r="17" spans="2:15">
       <c r="B17">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="C17" t="s">
         <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>409</v>
+        <v>482</v>
       </c>
       <c r="O17" t="s">
-        <v>576</v>
+        <v>667</v>
       </c>
     </row>
     <row r="18" spans="2:15">
       <c r="B18">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="C18" t="s">
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>410</v>
+        <v>483</v>
       </c>
       <c r="O18" t="s">
-        <v>577</v>
+        <v>668</v>
       </c>
     </row>
     <row r="19" spans="2:15">
       <c r="B19">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="C19" t="s">
         <v>46</v>
       </c>
       <c r="E19" t="s">
-        <v>411</v>
+        <v>484</v>
       </c>
       <c r="O19" t="s">
-        <v>578</v>
+        <v>669</v>
       </c>
     </row>
     <row r="20" spans="2:15">
       <c r="B20">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="C20" t="s">
         <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>412</v>
+        <v>485</v>
       </c>
       <c r="O20" t="s">
-        <v>579</v>
+        <v>670</v>
       </c>
     </row>
     <row r="21" spans="2:15">
       <c r="B21">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="C21" t="s">
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>413</v>
+        <v>486</v>
       </c>
       <c r="O21" t="s">
-        <v>580</v>
+        <v>671</v>
       </c>
     </row>
     <row r="22" spans="2:15">
       <c r="B22">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="C22" t="s">
         <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>414</v>
+        <v>487</v>
       </c>
       <c r="O22" t="s">
-        <v>581</v>
+        <v>672</v>
       </c>
     </row>
     <row r="23" spans="2:15">
       <c r="B23">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="C23" t="s">
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>415</v>
+        <v>488</v>
       </c>
       <c r="O23" t="s">
-        <v>582</v>
+        <v>673</v>
       </c>
     </row>
     <row r="24" spans="2:15">
       <c r="B24">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="C24" t="s">
         <v>51</v>
       </c>
       <c r="E24" t="s">
-        <v>416</v>
+        <v>489</v>
       </c>
       <c r="O24" t="s">
-        <v>583</v>
+        <v>674</v>
       </c>
     </row>
     <row r="25" spans="2:15">
       <c r="B25">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="C25" t="s">
         <v>52</v>
       </c>
       <c r="E25" t="s">
-        <v>417</v>
+        <v>490</v>
       </c>
       <c r="O25" t="s">
-        <v>584</v>
+        <v>675</v>
       </c>
     </row>
     <row r="26" spans="2:15">
       <c r="B26">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="C26" t="s">
         <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>418</v>
+        <v>491</v>
       </c>
       <c r="O26" t="s">
-        <v>585</v>
+        <v>676</v>
       </c>
     </row>
     <row r="27" spans="2:15">
       <c r="B27">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="C27" t="s">
         <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>419</v>
+        <v>492</v>
       </c>
       <c r="O27" t="s">
-        <v>586</v>
+        <v>677</v>
       </c>
     </row>
     <row r="28" spans="2:15">
       <c r="B28">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="C28" t="s">
         <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>420</v>
+        <v>493</v>
       </c>
       <c r="O28" t="s">
-        <v>587</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29" spans="2:15">
       <c r="B29">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="C29" t="s">
         <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>421</v>
+        <v>494</v>
       </c>
       <c r="O29" t="s">
-        <v>588</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="2:15">
       <c r="B30">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="C30" t="s">
         <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>422</v>
+        <v>495</v>
       </c>
       <c r="O30" t="s">
-        <v>589</v>
+        <v>394</v>
       </c>
     </row>
     <row r="31" spans="2:15">
       <c r="B31">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="C31" t="s">
         <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>423</v>
+        <v>496</v>
       </c>
       <c r="O31" t="s">
-        <v>590</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" spans="2:15">
       <c r="B32">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="C32" t="s">
         <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>424</v>
+        <v>497</v>
       </c>
       <c r="O32" t="s">
-        <v>591</v>
+        <v>154</v>
       </c>
     </row>
     <row r="33" spans="2:15">
       <c r="B33">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="C33" t="s">
         <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>425</v>
+        <v>498</v>
       </c>
       <c r="O33" t="s">
-        <v>592</v>
+        <v>678</v>
       </c>
     </row>
     <row r="34" spans="2:15">
-      <c r="B34">
-        <v>2050</v>
-      </c>
       <c r="C34" t="s">
         <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>426</v>
+        <v>499</v>
       </c>
       <c r="O34" t="s">
-        <v>593</v>
+        <v>679</v>
       </c>
     </row>
     <row r="35" spans="2:15">
-      <c r="B35">
-        <v>2051</v>
-      </c>
       <c r="C35" t="s">
         <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>427</v>
+        <v>500</v>
       </c>
       <c r="O35" t="s">
-        <v>594</v>
+        <v>680</v>
       </c>
     </row>
     <row r="36" spans="2:15">
-      <c r="B36">
-        <v>2052</v>
-      </c>
       <c r="C36" t="s">
         <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>428</v>
+        <v>501</v>
       </c>
       <c r="O36" t="s">
-        <v>595</v>
+        <v>681</v>
       </c>
     </row>
     <row r="37" spans="2:15">
-      <c r="B37">
-        <v>2053</v>
-      </c>
       <c r="C37" t="s">
         <v>64</v>
       </c>
       <c r="E37" t="s">
-        <v>429</v>
+        <v>502</v>
       </c>
       <c r="O37" t="s">
-        <v>596</v>
+        <v>682</v>
       </c>
     </row>
     <row r="38" spans="2:15">
-      <c r="B38">
-        <v>2054</v>
-      </c>
       <c r="C38" t="s">
         <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>430</v>
+        <v>503</v>
       </c>
       <c r="O38" t="s">
-        <v>597</v>
+        <v>683</v>
       </c>
     </row>
     <row r="39" spans="2:15">
-      <c r="B39">
-        <v>2055</v>
-      </c>
       <c r="C39" t="s">
         <v>66</v>
       </c>
       <c r="E39" t="s">
-        <v>431</v>
+        <v>504</v>
       </c>
       <c r="O39" t="s">
-        <v>598</v>
+        <v>684</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -3409,10 +3646,10 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>432</v>
+        <v>505</v>
       </c>
       <c r="O40" t="s">
-        <v>599</v>
+        <v>685</v>
       </c>
     </row>
     <row r="41" spans="2:15">
@@ -3420,10 +3657,10 @@
         <v>68</v>
       </c>
       <c r="E41" t="s">
-        <v>433</v>
+        <v>506</v>
       </c>
       <c r="O41" t="s">
-        <v>600</v>
+        <v>686</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -3431,10 +3668,10 @@
         <v>69</v>
       </c>
       <c r="E42" t="s">
-        <v>434</v>
+        <v>507</v>
       </c>
       <c r="O42" t="s">
-        <v>601</v>
+        <v>687</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -3442,10 +3679,10 @@
         <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>435</v>
+        <v>508</v>
       </c>
       <c r="O43" t="s">
-        <v>602</v>
+        <v>688</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -3453,10 +3690,10 @@
         <v>71</v>
       </c>
       <c r="E44" t="s">
-        <v>436</v>
+        <v>509</v>
       </c>
       <c r="O44" t="s">
-        <v>603</v>
+        <v>689</v>
       </c>
     </row>
     <row r="45" spans="2:15">
@@ -3464,10 +3701,10 @@
         <v>72</v>
       </c>
       <c r="E45" t="s">
-        <v>437</v>
+        <v>510</v>
       </c>
       <c r="O45" t="s">
-        <v>604</v>
+        <v>690</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -3475,10 +3712,10 @@
         <v>73</v>
       </c>
       <c r="E46" t="s">
-        <v>438</v>
+        <v>511</v>
       </c>
       <c r="O46" t="s">
-        <v>605</v>
+        <v>691</v>
       </c>
     </row>
     <row r="47" spans="2:15">
@@ -3486,10 +3723,10 @@
         <v>74</v>
       </c>
       <c r="E47" t="s">
-        <v>439</v>
+        <v>512</v>
       </c>
       <c r="O47" t="s">
-        <v>606</v>
+        <v>692</v>
       </c>
     </row>
     <row r="48" spans="2:15">
@@ -3497,10 +3734,10 @@
         <v>75</v>
       </c>
       <c r="E48" t="s">
-        <v>171</v>
+        <v>513</v>
       </c>
       <c r="O48" t="s">
-        <v>607</v>
+        <v>693</v>
       </c>
     </row>
     <row r="49" spans="3:15">
@@ -3508,10 +3745,10 @@
         <v>76</v>
       </c>
       <c r="E49" t="s">
-        <v>440</v>
+        <v>514</v>
       </c>
       <c r="O49" t="s">
-        <v>608</v>
+        <v>694</v>
       </c>
     </row>
     <row r="50" spans="3:15">
@@ -3519,10 +3756,10 @@
         <v>77</v>
       </c>
       <c r="E50" t="s">
-        <v>441</v>
+        <v>515</v>
       </c>
       <c r="O50" t="s">
-        <v>609</v>
+        <v>695</v>
       </c>
     </row>
     <row r="51" spans="3:15">
@@ -3530,10 +3767,10 @@
         <v>78</v>
       </c>
       <c r="E51" t="s">
-        <v>442</v>
+        <v>516</v>
       </c>
       <c r="O51" t="s">
-        <v>610</v>
+        <v>696</v>
       </c>
     </row>
     <row r="52" spans="3:15">
@@ -3541,10 +3778,10 @@
         <v>79</v>
       </c>
       <c r="E52" t="s">
-        <v>443</v>
+        <v>517</v>
       </c>
       <c r="O52" t="s">
-        <v>611</v>
+        <v>697</v>
       </c>
     </row>
     <row r="53" spans="3:15">
@@ -3552,10 +3789,10 @@
         <v>80</v>
       </c>
       <c r="E53" t="s">
-        <v>444</v>
+        <v>219</v>
       </c>
       <c r="O53" t="s">
-        <v>612</v>
+        <v>698</v>
       </c>
     </row>
     <row r="54" spans="3:15">
@@ -3563,10 +3800,10 @@
         <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>445</v>
+        <v>518</v>
       </c>
       <c r="O54" t="s">
-        <v>613</v>
+        <v>699</v>
       </c>
     </row>
     <row r="55" spans="3:15">
@@ -3574,10 +3811,10 @@
         <v>82</v>
       </c>
       <c r="E55" t="s">
-        <v>446</v>
+        <v>519</v>
       </c>
       <c r="O55" t="s">
-        <v>614</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56" spans="3:15">
@@ -3585,10 +3822,10 @@
         <v>83</v>
       </c>
       <c r="E56" t="s">
-        <v>447</v>
+        <v>520</v>
       </c>
       <c r="O56" t="s">
-        <v>615</v>
+        <v>701</v>
       </c>
     </row>
     <row r="57" spans="3:15">
@@ -3596,10 +3833,10 @@
         <v>84</v>
       </c>
       <c r="E57" t="s">
-        <v>448</v>
+        <v>521</v>
       </c>
       <c r="O57" t="s">
-        <v>616</v>
+        <v>702</v>
       </c>
     </row>
     <row r="58" spans="3:15">
@@ -3607,10 +3844,10 @@
         <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>449</v>
+        <v>522</v>
       </c>
       <c r="O58" t="s">
-        <v>617</v>
+        <v>703</v>
       </c>
     </row>
     <row r="59" spans="3:15">
@@ -3618,7 +3855,10 @@
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>450</v>
+        <v>523</v>
+      </c>
+      <c r="O59" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="60" spans="3:15">
@@ -3626,7 +3866,10 @@
         <v>87</v>
       </c>
       <c r="E60" t="s">
-        <v>451</v>
+        <v>524</v>
+      </c>
+      <c r="O60" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="61" spans="3:15">
@@ -3634,7 +3877,10 @@
         <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>452</v>
+        <v>525</v>
+      </c>
+      <c r="O61" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="62" spans="3:15">
@@ -3642,7 +3888,10 @@
         <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>453</v>
+        <v>526</v>
+      </c>
+      <c r="O62" t="s">
+        <v>707</v>
       </c>
     </row>
     <row r="63" spans="3:15">
@@ -3650,7 +3899,7 @@
         <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>454</v>
+        <v>527</v>
       </c>
     </row>
     <row r="64" spans="3:15">
@@ -3658,7 +3907,7 @@
         <v>91</v>
       </c>
       <c r="E64" t="s">
-        <v>455</v>
+        <v>528</v>
       </c>
     </row>
     <row r="65" spans="3:5">
@@ -3666,7 +3915,7 @@
         <v>92</v>
       </c>
       <c r="E65" t="s">
-        <v>456</v>
+        <v>529</v>
       </c>
     </row>
     <row r="66" spans="3:5">
@@ -3674,7 +3923,7 @@
         <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>457</v>
+        <v>263</v>
       </c>
     </row>
     <row r="67" spans="3:5">
@@ -3682,7 +3931,7 @@
         <v>94</v>
       </c>
       <c r="E67" t="s">
-        <v>458</v>
+        <v>530</v>
       </c>
     </row>
     <row r="68" spans="3:5">
@@ -3690,7 +3939,7 @@
         <v>95</v>
       </c>
       <c r="E68" t="s">
-        <v>459</v>
+        <v>531</v>
       </c>
     </row>
     <row r="69" spans="3:5">
@@ -3698,7 +3947,7 @@
         <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>460</v>
+        <v>532</v>
       </c>
     </row>
     <row r="70" spans="3:5">
@@ -3706,7 +3955,7 @@
         <v>97</v>
       </c>
       <c r="E70" t="s">
-        <v>461</v>
+        <v>533</v>
       </c>
     </row>
     <row r="71" spans="3:5">
@@ -3714,7 +3963,7 @@
         <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>462</v>
+        <v>270</v>
       </c>
     </row>
     <row r="72" spans="3:5">
@@ -3722,7 +3971,7 @@
         <v>99</v>
       </c>
       <c r="E72" t="s">
-        <v>463</v>
+        <v>275</v>
       </c>
     </row>
     <row r="73" spans="3:5">
@@ -3730,7 +3979,7 @@
         <v>100</v>
       </c>
       <c r="E73" t="s">
-        <v>464</v>
+        <v>534</v>
       </c>
     </row>
     <row r="74" spans="3:5">
@@ -3738,7 +3987,7 @@
         <v>101</v>
       </c>
       <c r="E74" t="s">
-        <v>465</v>
+        <v>535</v>
       </c>
     </row>
     <row r="75" spans="3:5">
@@ -3746,7 +3995,7 @@
         <v>102</v>
       </c>
       <c r="E75" t="s">
-        <v>466</v>
+        <v>536</v>
       </c>
     </row>
     <row r="76" spans="3:5">
@@ -3754,7 +4003,7 @@
         <v>103</v>
       </c>
       <c r="E76" t="s">
-        <v>467</v>
+        <v>537</v>
       </c>
     </row>
     <row r="77" spans="3:5">
@@ -3762,7 +4011,7 @@
         <v>104</v>
       </c>
       <c r="E77" t="s">
-        <v>468</v>
+        <v>538</v>
       </c>
     </row>
     <row r="78" spans="3:5">
@@ -3770,7 +4019,7 @@
         <v>105</v>
       </c>
       <c r="E78" t="s">
-        <v>469</v>
+        <v>539</v>
       </c>
     </row>
     <row r="79" spans="3:5">
@@ -3778,7 +4027,7 @@
         <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>470</v>
+        <v>540</v>
       </c>
     </row>
     <row r="80" spans="3:5">
@@ -3786,7 +4035,7 @@
         <v>107</v>
       </c>
       <c r="E80" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
     </row>
     <row r="81" spans="3:5">
@@ -3794,7 +4043,7 @@
         <v>108</v>
       </c>
       <c r="E81" t="s">
-        <v>472</v>
+        <v>542</v>
       </c>
     </row>
     <row r="82" spans="3:5">
@@ -3802,7 +4051,7 @@
         <v>109</v>
       </c>
       <c r="E82" t="s">
-        <v>473</v>
+        <v>543</v>
       </c>
     </row>
     <row r="83" spans="3:5">
@@ -3810,7 +4059,7 @@
         <v>110</v>
       </c>
       <c r="E83" t="s">
-        <v>474</v>
+        <v>544</v>
       </c>
     </row>
     <row r="84" spans="3:5">
@@ -3818,7 +4067,7 @@
         <v>111</v>
       </c>
       <c r="E84" t="s">
-        <v>475</v>
+        <v>545</v>
       </c>
     </row>
     <row r="85" spans="3:5">
@@ -3826,7 +4075,7 @@
         <v>112</v>
       </c>
       <c r="E85" t="s">
-        <v>476</v>
+        <v>546</v>
       </c>
     </row>
     <row r="86" spans="3:5">
@@ -3834,7 +4083,7 @@
         <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>477</v>
+        <v>547</v>
       </c>
     </row>
     <row r="87" spans="3:5">
@@ -3842,7 +4091,7 @@
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>478</v>
+        <v>548</v>
       </c>
     </row>
     <row r="88" spans="3:5">
@@ -3850,7 +4099,7 @@
         <v>115</v>
       </c>
       <c r="E88" t="s">
-        <v>479</v>
+        <v>549</v>
       </c>
     </row>
     <row r="89" spans="3:5">
@@ -3858,7 +4107,7 @@
         <v>116</v>
       </c>
       <c r="E89" t="s">
-        <v>480</v>
+        <v>550</v>
       </c>
     </row>
     <row r="90" spans="3:5">
@@ -3866,7 +4115,7 @@
         <v>117</v>
       </c>
       <c r="E90" t="s">
-        <v>481</v>
+        <v>551</v>
       </c>
     </row>
     <row r="91" spans="3:5">
@@ -3874,7 +4123,7 @@
         <v>118</v>
       </c>
       <c r="E91" t="s">
-        <v>482</v>
+        <v>552</v>
       </c>
     </row>
     <row r="92" spans="3:5">
@@ -3882,7 +4131,7 @@
         <v>119</v>
       </c>
       <c r="E92" t="s">
-        <v>483</v>
+        <v>553</v>
       </c>
     </row>
     <row r="93" spans="3:5">
@@ -3890,7 +4139,7 @@
         <v>120</v>
       </c>
       <c r="E93" t="s">
-        <v>484</v>
+        <v>554</v>
       </c>
     </row>
     <row r="94" spans="3:5">
@@ -3898,7 +4147,7 @@
         <v>121</v>
       </c>
       <c r="E94" t="s">
-        <v>485</v>
+        <v>555</v>
       </c>
     </row>
     <row r="95" spans="3:5">
@@ -3906,7 +4155,7 @@
         <v>122</v>
       </c>
       <c r="E95" t="s">
-        <v>486</v>
+        <v>556</v>
       </c>
     </row>
     <row r="96" spans="3:5">
@@ -3914,7 +4163,7 @@
         <v>123</v>
       </c>
       <c r="E96" t="s">
-        <v>487</v>
+        <v>557</v>
       </c>
     </row>
     <row r="97" spans="3:5">
@@ -3922,7 +4171,7 @@
         <v>124</v>
       </c>
       <c r="E97" t="s">
-        <v>488</v>
+        <v>558</v>
       </c>
     </row>
     <row r="98" spans="3:5">
@@ -3930,7 +4179,7 @@
         <v>125</v>
       </c>
       <c r="E98" t="s">
-        <v>489</v>
+        <v>559</v>
       </c>
     </row>
     <row r="99" spans="3:5">
@@ -3938,7 +4187,7 @@
         <v>126</v>
       </c>
       <c r="E99" t="s">
-        <v>490</v>
+        <v>560</v>
       </c>
     </row>
     <row r="100" spans="3:5">
@@ -3946,7 +4195,7 @@
         <v>127</v>
       </c>
       <c r="E100" t="s">
-        <v>491</v>
+        <v>561</v>
       </c>
     </row>
     <row r="101" spans="3:5">
@@ -3954,7 +4203,7 @@
         <v>128</v>
       </c>
       <c r="E101" t="s">
-        <v>492</v>
+        <v>562</v>
       </c>
     </row>
     <row r="102" spans="3:5">
@@ -3962,7 +4211,7 @@
         <v>129</v>
       </c>
       <c r="E102" t="s">
-        <v>493</v>
+        <v>563</v>
       </c>
     </row>
     <row r="103" spans="3:5">
@@ -3970,7 +4219,7 @@
         <v>130</v>
       </c>
       <c r="E103" t="s">
-        <v>494</v>
+        <v>564</v>
       </c>
     </row>
     <row r="104" spans="3:5">
@@ -3978,7 +4227,7 @@
         <v>131</v>
       </c>
       <c r="E104" t="s">
-        <v>495</v>
+        <v>565</v>
       </c>
     </row>
     <row r="105" spans="3:5">
@@ -3986,7 +4235,7 @@
         <v>132</v>
       </c>
       <c r="E105" t="s">
-        <v>496</v>
+        <v>566</v>
       </c>
     </row>
     <row r="106" spans="3:5">
@@ -3994,7 +4243,7 @@
         <v>133</v>
       </c>
       <c r="E106" t="s">
-        <v>497</v>
+        <v>567</v>
       </c>
     </row>
     <row r="107" spans="3:5">
@@ -4002,7 +4251,7 @@
         <v>134</v>
       </c>
       <c r="E107" t="s">
-        <v>498</v>
+        <v>568</v>
       </c>
     </row>
     <row r="108" spans="3:5">
@@ -4010,7 +4259,7 @@
         <v>135</v>
       </c>
       <c r="E108" t="s">
-        <v>499</v>
+        <v>569</v>
       </c>
     </row>
     <row r="109" spans="3:5">
@@ -4018,7 +4267,7 @@
         <v>136</v>
       </c>
       <c r="E109" t="s">
-        <v>500</v>
+        <v>570</v>
       </c>
     </row>
     <row r="110" spans="3:5">
@@ -4026,7 +4275,7 @@
         <v>137</v>
       </c>
       <c r="E110" t="s">
-        <v>242</v>
+        <v>571</v>
       </c>
     </row>
     <row r="111" spans="3:5">
@@ -4034,7 +4283,7 @@
         <v>138</v>
       </c>
       <c r="E111" t="s">
-        <v>501</v>
+        <v>572</v>
       </c>
     </row>
     <row r="112" spans="3:5">
@@ -4042,7 +4291,7 @@
         <v>139</v>
       </c>
       <c r="E112" t="s">
-        <v>502</v>
+        <v>573</v>
       </c>
     </row>
     <row r="113" spans="3:5">
@@ -4050,7 +4299,7 @@
         <v>140</v>
       </c>
       <c r="E113" t="s">
-        <v>503</v>
+        <v>574</v>
       </c>
     </row>
     <row r="114" spans="3:5">
@@ -4058,7 +4307,7 @@
         <v>141</v>
       </c>
       <c r="E114" t="s">
-        <v>504</v>
+        <v>575</v>
       </c>
     </row>
     <row r="115" spans="3:5">
@@ -4066,7 +4315,7 @@
         <v>142</v>
       </c>
       <c r="E115" t="s">
-        <v>505</v>
+        <v>576</v>
       </c>
     </row>
     <row r="116" spans="3:5">
@@ -4074,7 +4323,7 @@
         <v>143</v>
       </c>
       <c r="E116" t="s">
-        <v>506</v>
+        <v>577</v>
       </c>
     </row>
     <row r="117" spans="3:5">
@@ -4082,7 +4331,7 @@
         <v>144</v>
       </c>
       <c r="E117" t="s">
-        <v>507</v>
+        <v>578</v>
       </c>
     </row>
     <row r="118" spans="3:5">
@@ -4090,7 +4339,7 @@
         <v>145</v>
       </c>
       <c r="E118" t="s">
-        <v>508</v>
+        <v>579</v>
       </c>
     </row>
     <row r="119" spans="3:5">
@@ -4098,7 +4347,7 @@
         <v>146</v>
       </c>
       <c r="E119" t="s">
-        <v>509</v>
+        <v>580</v>
       </c>
     </row>
     <row r="120" spans="3:5">
@@ -4106,7 +4355,7 @@
         <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>510</v>
+        <v>581</v>
       </c>
     </row>
     <row r="121" spans="3:5">
@@ -4114,7 +4363,7 @@
         <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>511</v>
+        <v>582</v>
       </c>
     </row>
     <row r="122" spans="3:5">
@@ -4122,7 +4371,7 @@
         <v>149</v>
       </c>
       <c r="E122" t="s">
-        <v>512</v>
+        <v>583</v>
       </c>
     </row>
     <row r="123" spans="3:5">
@@ -4130,7 +4379,7 @@
         <v>150</v>
       </c>
       <c r="E123" t="s">
-        <v>513</v>
+        <v>584</v>
       </c>
     </row>
     <row r="124" spans="3:5">
@@ -4138,7 +4387,7 @@
         <v>151</v>
       </c>
       <c r="E124" t="s">
-        <v>514</v>
+        <v>585</v>
       </c>
     </row>
     <row r="125" spans="3:5">
@@ -4146,7 +4395,7 @@
         <v>152</v>
       </c>
       <c r="E125" t="s">
-        <v>515</v>
+        <v>586</v>
       </c>
     </row>
     <row r="126" spans="3:5">
@@ -4154,7 +4403,7 @@
         <v>153</v>
       </c>
       <c r="E126" t="s">
-        <v>516</v>
+        <v>587</v>
       </c>
     </row>
     <row r="127" spans="3:5">
@@ -4162,7 +4411,7 @@
         <v>154</v>
       </c>
       <c r="E127" t="s">
-        <v>517</v>
+        <v>588</v>
       </c>
     </row>
     <row r="128" spans="3:5">
@@ -4170,7 +4419,7 @@
         <v>155</v>
       </c>
       <c r="E128" t="s">
-        <v>518</v>
+        <v>589</v>
       </c>
     </row>
     <row r="129" spans="3:5">
@@ -4178,7 +4427,7 @@
         <v>156</v>
       </c>
       <c r="E129" t="s">
-        <v>519</v>
+        <v>590</v>
       </c>
     </row>
     <row r="130" spans="3:5">
@@ -4186,7 +4435,7 @@
         <v>157</v>
       </c>
       <c r="E130" t="s">
-        <v>520</v>
+        <v>591</v>
       </c>
     </row>
     <row r="131" spans="3:5">
@@ -4194,7 +4443,7 @@
         <v>158</v>
       </c>
       <c r="E131" t="s">
-        <v>521</v>
+        <v>592</v>
       </c>
     </row>
     <row r="132" spans="3:5">
@@ -4202,7 +4451,7 @@
         <v>159</v>
       </c>
       <c r="E132" t="s">
-        <v>522</v>
+        <v>593</v>
       </c>
     </row>
     <row r="133" spans="3:5">
@@ -4210,7 +4459,7 @@
         <v>160</v>
       </c>
       <c r="E133" t="s">
-        <v>523</v>
+        <v>594</v>
       </c>
     </row>
     <row r="134" spans="3:5">
@@ -4218,7 +4467,7 @@
         <v>161</v>
       </c>
       <c r="E134" t="s">
-        <v>524</v>
+        <v>595</v>
       </c>
     </row>
     <row r="135" spans="3:5">
@@ -4226,7 +4475,7 @@
         <v>162</v>
       </c>
       <c r="E135" t="s">
-        <v>525</v>
+        <v>596</v>
       </c>
     </row>
     <row r="136" spans="3:5">
@@ -4234,7 +4483,7 @@
         <v>163</v>
       </c>
       <c r="E136" t="s">
-        <v>88</v>
+        <v>597</v>
       </c>
     </row>
     <row r="137" spans="3:5">
@@ -4242,7 +4491,7 @@
         <v>164</v>
       </c>
       <c r="E137" t="s">
-        <v>526</v>
+        <v>598</v>
       </c>
     </row>
     <row r="138" spans="3:5">
@@ -4250,7 +4499,7 @@
         <v>165</v>
       </c>
       <c r="E138" t="s">
-        <v>527</v>
+        <v>599</v>
       </c>
     </row>
     <row r="139" spans="3:5">
@@ -4258,7 +4507,7 @@
         <v>166</v>
       </c>
       <c r="E139" t="s">
-        <v>362</v>
+        <v>600</v>
       </c>
     </row>
     <row r="140" spans="3:5">
@@ -4266,7 +4515,7 @@
         <v>167</v>
       </c>
       <c r="E140" t="s">
-        <v>367</v>
+        <v>601</v>
       </c>
     </row>
     <row r="141" spans="3:5">
@@ -4274,7 +4523,7 @@
         <v>168</v>
       </c>
       <c r="E141" t="s">
-        <v>528</v>
+        <v>602</v>
       </c>
     </row>
     <row r="142" spans="3:5">
@@ -4282,7 +4531,7 @@
         <v>169</v>
       </c>
       <c r="E142" t="s">
-        <v>529</v>
+        <v>603</v>
       </c>
     </row>
     <row r="143" spans="3:5">
@@ -4290,7 +4539,7 @@
         <v>170</v>
       </c>
       <c r="E143" t="s">
-        <v>530</v>
+        <v>604</v>
       </c>
     </row>
     <row r="144" spans="3:5">
@@ -4298,7 +4547,7 @@
         <v>171</v>
       </c>
       <c r="E144" t="s">
-        <v>531</v>
+        <v>605</v>
       </c>
     </row>
     <row r="145" spans="3:5">
@@ -4306,7 +4555,7 @@
         <v>172</v>
       </c>
       <c r="E145" t="s">
-        <v>532</v>
+        <v>606</v>
       </c>
     </row>
     <row r="146" spans="3:5">
@@ -4314,7 +4563,7 @@
         <v>173</v>
       </c>
       <c r="E146" t="s">
-        <v>533</v>
+        <v>607</v>
       </c>
     </row>
     <row r="147" spans="3:5">
@@ -4322,7 +4571,7 @@
         <v>174</v>
       </c>
       <c r="E147" t="s">
-        <v>534</v>
+        <v>608</v>
       </c>
     </row>
     <row r="148" spans="3:5">
@@ -4330,7 +4579,7 @@
         <v>175</v>
       </c>
       <c r="E148" t="s">
-        <v>535</v>
+        <v>609</v>
       </c>
     </row>
     <row r="149" spans="3:5">
@@ -4338,7 +4587,7 @@
         <v>176</v>
       </c>
       <c r="E149" t="s">
-        <v>536</v>
+        <v>610</v>
       </c>
     </row>
     <row r="150" spans="3:5">
@@ -4346,7 +4595,7 @@
         <v>177</v>
       </c>
       <c r="E150" t="s">
-        <v>537</v>
+        <v>611</v>
       </c>
     </row>
     <row r="151" spans="3:5">
@@ -4354,7 +4603,7 @@
         <v>178</v>
       </c>
       <c r="E151" t="s">
-        <v>538</v>
+        <v>612</v>
       </c>
     </row>
     <row r="152" spans="3:5">
@@ -4362,7 +4611,7 @@
         <v>179</v>
       </c>
       <c r="E152" t="s">
-        <v>539</v>
+        <v>613</v>
       </c>
     </row>
     <row r="153" spans="3:5">
@@ -4370,120 +4619,186 @@
         <v>180</v>
       </c>
       <c r="E153" t="s">
-        <v>540</v>
+        <v>614</v>
       </c>
     </row>
     <row r="154" spans="3:5">
       <c r="C154" t="s">
         <v>181</v>
       </c>
+      <c r="E154" t="s">
+        <v>615</v>
+      </c>
     </row>
     <row r="155" spans="3:5">
       <c r="C155" t="s">
         <v>182</v>
       </c>
+      <c r="E155" t="s">
+        <v>616</v>
+      </c>
     </row>
     <row r="156" spans="3:5">
       <c r="C156" t="s">
         <v>183</v>
       </c>
+      <c r="E156" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="157" spans="3:5">
       <c r="C157" t="s">
         <v>184</v>
       </c>
+      <c r="E157" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="158" spans="3:5">
       <c r="C158" t="s">
         <v>185</v>
       </c>
+      <c r="E158" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="159" spans="3:5">
       <c r="C159" t="s">
         <v>186</v>
       </c>
+      <c r="E159" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="160" spans="3:5">
       <c r="C160" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="161" spans="3:3">
+      <c r="E160" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="161" spans="3:5">
       <c r="C161" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="162" spans="3:3">
+      <c r="E161" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="162" spans="3:5">
       <c r="C162" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="163" spans="3:3">
+      <c r="E162" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="163" spans="3:5">
       <c r="C163" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="164" spans="3:3">
+      <c r="E163" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="164" spans="3:5">
       <c r="C164" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="165" spans="3:3">
+      <c r="E164" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="165" spans="3:5">
       <c r="C165" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="166" spans="3:3">
+      <c r="E165" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="166" spans="3:5">
       <c r="C166" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="167" spans="3:3">
+      <c r="E166" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="167" spans="3:5">
       <c r="C167" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="168" spans="3:3">
+      <c r="E167" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="168" spans="3:5">
       <c r="C168" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="169" spans="3:3">
+      <c r="E168" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="169" spans="3:5">
       <c r="C169" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="170" spans="3:3">
+      <c r="E169" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="170" spans="3:5">
       <c r="C170" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="171" spans="3:3">
+      <c r="E170" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="171" spans="3:5">
       <c r="C171" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="172" spans="3:3">
+      <c r="E171" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="172" spans="3:5">
       <c r="C172" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="173" spans="3:3">
+      <c r="E172" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="173" spans="3:5">
       <c r="C173" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="174" spans="3:3">
+      <c r="E173" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="174" spans="3:5">
       <c r="C174" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="175" spans="3:3">
+      <c r="E174" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="175" spans="3:5">
       <c r="C175" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="176" spans="3:3">
+      <c r="E175" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="176" spans="3:5">
       <c r="C176" t="s">
         <v>203</v>
       </c>
@@ -5406,6 +5721,371 @@
     <row r="360" spans="3:3">
       <c r="C360" t="s">
         <v>387</v>
+      </c>
+    </row>
+    <row r="361" spans="3:3">
+      <c r="C361" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="362" spans="3:3">
+      <c r="C362" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="363" spans="3:3">
+      <c r="C363" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="364" spans="3:3">
+      <c r="C364" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="365" spans="3:3">
+      <c r="C365" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="366" spans="3:3">
+      <c r="C366" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="367" spans="3:3">
+      <c r="C367" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="368" spans="3:3">
+      <c r="C368" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="369" spans="3:3">
+      <c r="C369" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="370" spans="3:3">
+      <c r="C370" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="371" spans="3:3">
+      <c r="C371" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="372" spans="3:3">
+      <c r="C372" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="373" spans="3:3">
+      <c r="C373" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="374" spans="3:3">
+      <c r="C374" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="375" spans="3:3">
+      <c r="C375" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="376" spans="3:3">
+      <c r="C376" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="377" spans="3:3">
+      <c r="C377" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="378" spans="3:3">
+      <c r="C378" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="379" spans="3:3">
+      <c r="C379" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="380" spans="3:3">
+      <c r="C380" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="381" spans="3:3">
+      <c r="C381" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="382" spans="3:3">
+      <c r="C382" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="383" spans="3:3">
+      <c r="C383" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="384" spans="3:3">
+      <c r="C384" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="385" spans="3:3">
+      <c r="C385" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="386" spans="3:3">
+      <c r="C386" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="387" spans="3:3">
+      <c r="C387" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="388" spans="3:3">
+      <c r="C388" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="389" spans="3:3">
+      <c r="C389" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="390" spans="3:3">
+      <c r="C390" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="391" spans="3:3">
+      <c r="C391" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="392" spans="3:3">
+      <c r="C392" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="393" spans="3:3">
+      <c r="C393" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="394" spans="3:3">
+      <c r="C394" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="395" spans="3:3">
+      <c r="C395" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="396" spans="3:3">
+      <c r="C396" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="397" spans="3:3">
+      <c r="C397" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="398" spans="3:3">
+      <c r="C398" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="399" spans="3:3">
+      <c r="C399" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="400" spans="3:3">
+      <c r="C400" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="401" spans="3:3">
+      <c r="C401" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="402" spans="3:3">
+      <c r="C402" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="403" spans="3:3">
+      <c r="C403" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="404" spans="3:3">
+      <c r="C404" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="405" spans="3:3">
+      <c r="C405" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="406" spans="3:3">
+      <c r="C406" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="407" spans="3:3">
+      <c r="C407" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="408" spans="3:3">
+      <c r="C408" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="409" spans="3:3">
+      <c r="C409" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="410" spans="3:3">
+      <c r="C410" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="411" spans="3:3">
+      <c r="C411" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="412" spans="3:3">
+      <c r="C412" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="413" spans="3:3">
+      <c r="C413" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="414" spans="3:3">
+      <c r="C414" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="415" spans="3:3">
+      <c r="C415" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="416" spans="3:3">
+      <c r="C416" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="417" spans="3:3">
+      <c r="C417" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="418" spans="3:3">
+      <c r="C418" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="419" spans="3:3">
+      <c r="C419" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="420" spans="3:3">
+      <c r="C420" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="421" spans="3:3">
+      <c r="C421" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="422" spans="3:3">
+      <c r="C422" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="423" spans="3:3">
+      <c r="C423" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="424" spans="3:3">
+      <c r="C424" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="425" spans="3:3">
+      <c r="C425" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="426" spans="3:3">
+      <c r="C426" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="427" spans="3:3">
+      <c r="C427" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="428" spans="3:3">
+      <c r="C428" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="429" spans="3:3">
+      <c r="C429" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="430" spans="3:3">
+      <c r="C430" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="431" spans="3:3">
+      <c r="C431" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="432" spans="3:3">
+      <c r="C432" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="433" spans="3:3">
+      <c r="C433" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -5420,37 +6100,37 @@
   <sheetData>
     <row r="1" spans="1:69">
       <c r="A1" t="s">
-        <v>618</v>
+        <v>708</v>
       </c>
       <c r="B1" t="s">
-        <v>620</v>
+        <v>710</v>
       </c>
       <c r="L1" t="s">
-        <v>632</v>
+        <v>722</v>
       </c>
       <c r="O1" t="s">
-        <v>636</v>
+        <v>726</v>
       </c>
       <c r="AA1" t="s">
-        <v>649</v>
+        <v>739</v>
       </c>
       <c r="AE1" t="s">
-        <v>654</v>
+        <v>744</v>
       </c>
       <c r="AI1" t="s">
-        <v>659</v>
+        <v>749</v>
       </c>
       <c r="AM1" t="s">
-        <v>664</v>
+        <v>754</v>
       </c>
       <c r="AP1" t="s">
-        <v>668</v>
+        <v>758</v>
       </c>
       <c r="AS1" t="s">
-        <v>672</v>
+        <v>762</v>
       </c>
       <c r="AZ1" t="s">
-        <v>680</v>
+        <v>770</v>
       </c>
       <c r="BM1" t="s">
         <v>16</v>
@@ -5458,211 +6138,211 @@
     </row>
     <row r="2" spans="1:69">
       <c r="A2" t="s">
-        <v>619</v>
+        <v>709</v>
       </c>
       <c r="B2" t="s">
-        <v>621</v>
+        <v>711</v>
       </c>
       <c r="C2" t="s">
-        <v>622</v>
+        <v>712</v>
       </c>
       <c r="D2" t="s">
-        <v>623</v>
+        <v>713</v>
       </c>
       <c r="E2" t="s">
-        <v>624</v>
+        <v>714</v>
       </c>
       <c r="F2" t="s">
-        <v>626</v>
+        <v>716</v>
       </c>
       <c r="G2" t="s">
-        <v>627</v>
+        <v>717</v>
       </c>
       <c r="H2" t="s">
-        <v>628</v>
+        <v>718</v>
       </c>
       <c r="I2" t="s">
-        <v>629</v>
+        <v>719</v>
       </c>
       <c r="J2" t="s">
-        <v>630</v>
+        <v>720</v>
       </c>
       <c r="K2" t="s">
-        <v>631</v>
+        <v>721</v>
       </c>
       <c r="L2" t="s">
-        <v>633</v>
+        <v>723</v>
       </c>
       <c r="M2" t="s">
-        <v>634</v>
+        <v>724</v>
       </c>
       <c r="N2" t="s">
-        <v>635</v>
+        <v>725</v>
       </c>
       <c r="O2" t="s">
-        <v>637</v>
+        <v>727</v>
       </c>
       <c r="P2" t="s">
-        <v>638</v>
+        <v>728</v>
       </c>
       <c r="Q2" t="s">
-        <v>639</v>
+        <v>729</v>
       </c>
       <c r="R2" t="s">
-        <v>640</v>
+        <v>730</v>
       </c>
       <c r="S2" t="s">
-        <v>641</v>
+        <v>731</v>
       </c>
       <c r="T2" t="s">
-        <v>642</v>
+        <v>732</v>
       </c>
       <c r="U2" t="s">
-        <v>643</v>
+        <v>733</v>
       </c>
       <c r="V2" t="s">
-        <v>644</v>
+        <v>734</v>
       </c>
       <c r="W2" t="s">
-        <v>645</v>
+        <v>735</v>
       </c>
       <c r="X2" t="s">
-        <v>646</v>
+        <v>736</v>
       </c>
       <c r="Y2" t="s">
-        <v>647</v>
+        <v>737</v>
       </c>
       <c r="Z2" t="s">
-        <v>648</v>
+        <v>738</v>
       </c>
       <c r="AA2" t="s">
-        <v>650</v>
+        <v>740</v>
       </c>
       <c r="AB2" t="s">
-        <v>651</v>
+        <v>741</v>
       </c>
       <c r="AC2" t="s">
-        <v>652</v>
+        <v>742</v>
       </c>
       <c r="AD2" t="s">
-        <v>653</v>
+        <v>743</v>
       </c>
       <c r="AE2" t="s">
-        <v>655</v>
+        <v>745</v>
       </c>
       <c r="AF2" t="s">
-        <v>656</v>
+        <v>746</v>
       </c>
       <c r="AG2" t="s">
-        <v>657</v>
+        <v>747</v>
       </c>
       <c r="AH2" t="s">
-        <v>658</v>
+        <v>748</v>
       </c>
       <c r="AI2" t="s">
-        <v>660</v>
+        <v>750</v>
       </c>
       <c r="AJ2" t="s">
-        <v>661</v>
+        <v>751</v>
       </c>
       <c r="AK2" t="s">
-        <v>662</v>
+        <v>752</v>
       </c>
       <c r="AL2" t="s">
-        <v>663</v>
+        <v>753</v>
       </c>
       <c r="AM2" t="s">
-        <v>665</v>
+        <v>755</v>
       </c>
       <c r="AN2" t="s">
-        <v>666</v>
+        <v>756</v>
       </c>
       <c r="AO2" t="s">
-        <v>667</v>
+        <v>757</v>
       </c>
       <c r="AP2" t="s">
-        <v>669</v>
+        <v>759</v>
       </c>
       <c r="AQ2" t="s">
-        <v>670</v>
+        <v>760</v>
       </c>
       <c r="AR2" t="s">
-        <v>671</v>
+        <v>761</v>
       </c>
       <c r="AS2" t="s">
-        <v>673</v>
+        <v>763</v>
       </c>
       <c r="AT2" t="s">
-        <v>674</v>
+        <v>764</v>
       </c>
       <c r="AU2" t="s">
-        <v>675</v>
+        <v>765</v>
       </c>
       <c r="AV2" t="s">
-        <v>676</v>
+        <v>766</v>
       </c>
       <c r="AW2" t="s">
-        <v>677</v>
+        <v>767</v>
       </c>
       <c r="AX2" t="s">
-        <v>678</v>
+        <v>768</v>
       </c>
       <c r="AY2" t="s">
-        <v>679</v>
+        <v>769</v>
       </c>
       <c r="AZ2" t="s">
-        <v>681</v>
+        <v>771</v>
       </c>
       <c r="BA2" t="s">
-        <v>682</v>
+        <v>772</v>
       </c>
       <c r="BB2" t="s">
-        <v>683</v>
+        <v>773</v>
       </c>
       <c r="BC2" t="s">
-        <v>684</v>
+        <v>774</v>
       </c>
       <c r="BD2" t="s">
-        <v>685</v>
+        <v>775</v>
       </c>
       <c r="BE2" t="s">
-        <v>686</v>
+        <v>776</v>
       </c>
       <c r="BF2" t="s">
-        <v>687</v>
+        <v>777</v>
       </c>
       <c r="BG2" t="s">
-        <v>653</v>
+        <v>743</v>
       </c>
       <c r="BH2" t="s">
-        <v>688</v>
+        <v>778</v>
       </c>
       <c r="BI2" t="s">
-        <v>689</v>
+        <v>779</v>
       </c>
       <c r="BJ2" t="s">
-        <v>690</v>
+        <v>780</v>
       </c>
       <c r="BK2" t="s">
-        <v>691</v>
+        <v>781</v>
       </c>
       <c r="BL2" t="s">
-        <v>692</v>
+        <v>782</v>
       </c>
       <c r="BM2" t="s">
-        <v>693</v>
+        <v>783</v>
       </c>
       <c r="BN2" t="s">
-        <v>694</v>
+        <v>784</v>
       </c>
       <c r="BO2" t="s">
-        <v>695</v>
+        <v>785</v>
       </c>
       <c r="BP2" t="s">
-        <v>696</v>
+        <v>786</v>
       </c>
       <c r="BQ2" t="s">
-        <v>697</v>
+        <v>787</v>
       </c>
     </row>
     <row r="3" spans="1:69">
@@ -6088,7 +6768,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>625</v>
+        <v>715</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -6502,228 +7182,228 @@
   <sheetData>
     <row r="1" spans="1:66">
       <c r="A1" t="s">
-        <v>618</v>
+        <v>708</v>
       </c>
       <c r="B1" t="s">
-        <v>632</v>
+        <v>722</v>
       </c>
       <c r="D1" t="s">
-        <v>701</v>
+        <v>791</v>
       </c>
       <c r="J1" t="s">
-        <v>708</v>
+        <v>798</v>
       </c>
       <c r="AA1" t="s">
-        <v>726</v>
+        <v>816</v>
       </c>
       <c r="AK1" t="s">
-        <v>664</v>
+        <v>754</v>
       </c>
       <c r="AV1" t="s">
-        <v>680</v>
+        <v>770</v>
       </c>
       <c r="BM1" t="s">
-        <v>765</v>
+        <v>855</v>
       </c>
     </row>
     <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>698</v>
+        <v>788</v>
       </c>
       <c r="B2" t="s">
-        <v>699</v>
+        <v>789</v>
       </c>
       <c r="C2" t="s">
-        <v>700</v>
+        <v>790</v>
       </c>
       <c r="D2" t="s">
-        <v>702</v>
+        <v>792</v>
       </c>
       <c r="E2" t="s">
-        <v>703</v>
+        <v>793</v>
       </c>
       <c r="F2" t="s">
-        <v>704</v>
+        <v>794</v>
       </c>
       <c r="G2" t="s">
-        <v>705</v>
+        <v>795</v>
       </c>
       <c r="H2" t="s">
-        <v>706</v>
+        <v>796</v>
       </c>
       <c r="I2" t="s">
-        <v>707</v>
+        <v>797</v>
       </c>
       <c r="J2" t="s">
-        <v>709</v>
+        <v>799</v>
       </c>
       <c r="K2" t="s">
-        <v>710</v>
+        <v>800</v>
       </c>
       <c r="L2" t="s">
-        <v>711</v>
+        <v>801</v>
       </c>
       <c r="M2" t="s">
-        <v>712</v>
+        <v>802</v>
       </c>
       <c r="N2" t="s">
-        <v>713</v>
+        <v>803</v>
       </c>
       <c r="O2" t="s">
-        <v>714</v>
+        <v>804</v>
       </c>
       <c r="P2" t="s">
-        <v>715</v>
+        <v>805</v>
       </c>
       <c r="Q2" t="s">
-        <v>716</v>
+        <v>806</v>
       </c>
       <c r="R2" t="s">
-        <v>717</v>
+        <v>807</v>
       </c>
       <c r="S2" t="s">
-        <v>718</v>
+        <v>808</v>
       </c>
       <c r="T2" t="s">
-        <v>719</v>
+        <v>809</v>
       </c>
       <c r="U2" t="s">
-        <v>720</v>
+        <v>810</v>
       </c>
       <c r="V2" t="s">
-        <v>721</v>
+        <v>811</v>
       </c>
       <c r="W2" t="s">
-        <v>722</v>
+        <v>812</v>
       </c>
       <c r="X2" t="s">
-        <v>723</v>
+        <v>813</v>
       </c>
       <c r="Y2" t="s">
-        <v>724</v>
+        <v>814</v>
       </c>
       <c r="Z2" t="s">
-        <v>725</v>
+        <v>815</v>
       </c>
       <c r="AA2" t="s">
-        <v>727</v>
+        <v>817</v>
       </c>
       <c r="AB2" t="s">
-        <v>728</v>
+        <v>818</v>
       </c>
       <c r="AC2" t="s">
-        <v>729</v>
+        <v>819</v>
       </c>
       <c r="AD2" t="s">
-        <v>730</v>
+        <v>820</v>
       </c>
       <c r="AE2" t="s">
-        <v>731</v>
+        <v>821</v>
       </c>
       <c r="AF2" t="s">
-        <v>732</v>
+        <v>822</v>
       </c>
       <c r="AG2" t="s">
-        <v>733</v>
+        <v>823</v>
       </c>
       <c r="AH2" t="s">
-        <v>734</v>
+        <v>824</v>
       </c>
       <c r="AI2" t="s">
-        <v>735</v>
+        <v>825</v>
       </c>
       <c r="AJ2" t="s">
-        <v>736</v>
+        <v>826</v>
       </c>
       <c r="AK2" t="s">
-        <v>737</v>
+        <v>827</v>
       </c>
       <c r="AL2" t="s">
-        <v>738</v>
+        <v>828</v>
       </c>
       <c r="AM2" t="s">
-        <v>739</v>
+        <v>829</v>
       </c>
       <c r="AN2" t="s">
-        <v>740</v>
+        <v>830</v>
       </c>
       <c r="AO2" t="s">
-        <v>741</v>
+        <v>831</v>
       </c>
       <c r="AP2" t="s">
-        <v>742</v>
+        <v>832</v>
       </c>
       <c r="AQ2" t="s">
-        <v>743</v>
+        <v>833</v>
       </c>
       <c r="AR2" t="s">
-        <v>744</v>
+        <v>834</v>
       </c>
       <c r="AS2" t="s">
-        <v>745</v>
+        <v>835</v>
       </c>
       <c r="AT2" t="s">
-        <v>746</v>
+        <v>836</v>
       </c>
       <c r="AU2" t="s">
-        <v>747</v>
+        <v>837</v>
       </c>
       <c r="AV2" t="s">
-        <v>748</v>
+        <v>838</v>
       </c>
       <c r="AW2" t="s">
-        <v>749</v>
+        <v>839</v>
       </c>
       <c r="AX2" t="s">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="AY2" t="s">
-        <v>751</v>
+        <v>841</v>
       </c>
       <c r="AZ2" t="s">
-        <v>752</v>
+        <v>842</v>
       </c>
       <c r="BA2" t="s">
-        <v>753</v>
+        <v>843</v>
       </c>
       <c r="BB2" t="s">
-        <v>754</v>
+        <v>844</v>
       </c>
       <c r="BC2" t="s">
-        <v>755</v>
+        <v>845</v>
       </c>
       <c r="BD2" t="s">
-        <v>756</v>
+        <v>846</v>
       </c>
       <c r="BE2" t="s">
-        <v>757</v>
+        <v>847</v>
       </c>
       <c r="BF2" t="s">
-        <v>758</v>
+        <v>848</v>
       </c>
       <c r="BG2" t="s">
-        <v>759</v>
+        <v>849</v>
       </c>
       <c r="BH2" t="s">
-        <v>760</v>
+        <v>850</v>
       </c>
       <c r="BI2" t="s">
-        <v>761</v>
+        <v>851</v>
       </c>
       <c r="BJ2" t="s">
-        <v>762</v>
+        <v>852</v>
       </c>
       <c r="BK2" t="s">
-        <v>763</v>
+        <v>853</v>
       </c>
       <c r="BL2" t="s">
-        <v>764</v>
+        <v>854</v>
       </c>
       <c r="BM2" t="s">
-        <v>766</v>
+        <v>856</v>
       </c>
       <c r="BN2" t="s">
-        <v>767</v>
+        <v>857</v>
       </c>
     </row>
     <row r="3" spans="1:66">
@@ -7197,7 +7877,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>625</v>
+        <v>715</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>

--- a/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
+++ b/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="771">
   <si>
     <t>set</t>
   </si>
@@ -1206,6 +1206,9 @@
     <t>S24</t>
   </si>
   <si>
+    <t>EXPELC</t>
+  </si>
+  <si>
     <t>PWRWAT0</t>
   </si>
   <si>
@@ -1870,6 +1873,12 @@
   </si>
   <si>
     <t>INDOTHLPHELCSHARE</t>
+  </si>
+  <si>
+    <t>INDASHACTCAP</t>
+  </si>
+  <si>
+    <t>PWRCOA003BAL</t>
   </si>
   <si>
     <t>category</t>
@@ -2762,7 +2771,7 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F3">
         <v>12</v>
@@ -2792,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2809,31 +2818,31 @@
         <v>396</v>
       </c>
       <c r="F4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H4" t="s">
+        <v>555</v>
+      </c>
+      <c r="I4" t="s">
         <v>554</v>
       </c>
-      <c r="I4" t="s">
-        <v>553</v>
-      </c>
       <c r="J4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -2850,16 +2859,16 @@
         <v>397</v>
       </c>
       <c r="F5" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="I5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O5" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2876,13 +2885,13 @@
         <v>398</v>
       </c>
       <c r="F6" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="K6" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O6" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -2899,13 +2908,13 @@
         <v>399</v>
       </c>
       <c r="F7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O7" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -2922,13 +2931,13 @@
         <v>400</v>
       </c>
       <c r="F8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="K8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -2945,13 +2954,13 @@
         <v>401</v>
       </c>
       <c r="F9" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="K9" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2968,13 +2977,13 @@
         <v>402</v>
       </c>
       <c r="F10" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O10" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -2991,13 +3000,13 @@
         <v>403</v>
       </c>
       <c r="F11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="K11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -3011,10 +3020,10 @@
         <v>404</v>
       </c>
       <c r="F12" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="O12" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -3028,10 +3037,10 @@
         <v>405</v>
       </c>
       <c r="F13" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O13" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -3045,10 +3054,10 @@
         <v>406</v>
       </c>
       <c r="F14" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O14" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -3062,10 +3071,10 @@
         <v>407</v>
       </c>
       <c r="F15" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O15" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -3079,7 +3088,7 @@
         <v>408</v>
       </c>
       <c r="O16" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="2:15">
@@ -3093,7 +3102,7 @@
         <v>409</v>
       </c>
       <c r="O17" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="18" spans="2:15">
@@ -3107,7 +3116,7 @@
         <v>410</v>
       </c>
       <c r="O18" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" spans="2:15">
@@ -3121,7 +3130,7 @@
         <v>411</v>
       </c>
       <c r="O19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" spans="2:15">
@@ -3135,7 +3144,7 @@
         <v>412</v>
       </c>
       <c r="O20" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="21" spans="2:15">
@@ -3149,7 +3158,7 @@
         <v>413</v>
       </c>
       <c r="O21" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="22" spans="2:15">
@@ -3163,7 +3172,7 @@
         <v>414</v>
       </c>
       <c r="O22" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="23" spans="2:15">
@@ -3177,7 +3186,7 @@
         <v>415</v>
       </c>
       <c r="O23" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="24" spans="2:15">
@@ -3191,7 +3200,7 @@
         <v>416</v>
       </c>
       <c r="O24" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="25" spans="2:15">
@@ -3205,7 +3214,7 @@
         <v>417</v>
       </c>
       <c r="O25" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="26" spans="2:15">
@@ -3219,7 +3228,7 @@
         <v>418</v>
       </c>
       <c r="O26" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="27" spans="2:15">
@@ -3233,7 +3242,7 @@
         <v>419</v>
       </c>
       <c r="O27" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="28" spans="2:15">
@@ -3247,7 +3256,7 @@
         <v>420</v>
       </c>
       <c r="O28" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="29" spans="2:15">
@@ -3261,7 +3270,7 @@
         <v>421</v>
       </c>
       <c r="O29" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="30" spans="2:15">
@@ -3275,7 +3284,7 @@
         <v>422</v>
       </c>
       <c r="O30" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="31" spans="2:15">
@@ -3289,7 +3298,7 @@
         <v>423</v>
       </c>
       <c r="O31" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="32" spans="2:15">
@@ -3303,7 +3312,7 @@
         <v>424</v>
       </c>
       <c r="O32" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="33" spans="2:15">
@@ -3317,7 +3326,7 @@
         <v>425</v>
       </c>
       <c r="O33" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="34" spans="2:15">
@@ -3331,7 +3340,7 @@
         <v>426</v>
       </c>
       <c r="O34" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="35" spans="2:15">
@@ -3345,7 +3354,7 @@
         <v>427</v>
       </c>
       <c r="O35" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="36" spans="2:15">
@@ -3359,7 +3368,7 @@
         <v>428</v>
       </c>
       <c r="O36" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="37" spans="2:15">
@@ -3373,7 +3382,7 @@
         <v>429</v>
       </c>
       <c r="O37" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="38" spans="2:15">
@@ -3387,7 +3396,7 @@
         <v>430</v>
       </c>
       <c r="O38" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="39" spans="2:15">
@@ -3401,7 +3410,7 @@
         <v>431</v>
       </c>
       <c r="O39" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -3412,7 +3421,7 @@
         <v>432</v>
       </c>
       <c r="O40" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" spans="2:15">
@@ -3423,7 +3432,7 @@
         <v>433</v>
       </c>
       <c r="O41" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -3434,7 +3443,7 @@
         <v>434</v>
       </c>
       <c r="O42" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -3445,7 +3454,7 @@
         <v>435</v>
       </c>
       <c r="O43" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -3456,7 +3465,7 @@
         <v>436</v>
       </c>
       <c r="O44" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="45" spans="2:15">
@@ -3467,7 +3476,7 @@
         <v>437</v>
       </c>
       <c r="O45" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -3478,7 +3487,7 @@
         <v>438</v>
       </c>
       <c r="O46" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="47" spans="2:15">
@@ -3489,7 +3498,7 @@
         <v>439</v>
       </c>
       <c r="O47" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="48" spans="2:15">
@@ -3497,10 +3506,10 @@
         <v>75</v>
       </c>
       <c r="E48" t="s">
-        <v>171</v>
+        <v>440</v>
       </c>
       <c r="O48" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="49" spans="3:15">
@@ -3508,10 +3517,10 @@
         <v>76</v>
       </c>
       <c r="E49" t="s">
-        <v>440</v>
+        <v>171</v>
       </c>
       <c r="O49" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="50" spans="3:15">
@@ -3522,7 +3531,7 @@
         <v>441</v>
       </c>
       <c r="O50" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="51" spans="3:15">
@@ -3533,7 +3542,7 @@
         <v>442</v>
       </c>
       <c r="O51" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="52" spans="3:15">
@@ -3544,7 +3553,7 @@
         <v>443</v>
       </c>
       <c r="O52" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="53" spans="3:15">
@@ -3555,7 +3564,7 @@
         <v>444</v>
       </c>
       <c r="O53" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="54" spans="3:15">
@@ -3566,7 +3575,7 @@
         <v>445</v>
       </c>
       <c r="O54" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="55" spans="3:15">
@@ -3577,7 +3586,7 @@
         <v>446</v>
       </c>
       <c r="O55" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="56" spans="3:15">
@@ -3588,7 +3597,7 @@
         <v>447</v>
       </c>
       <c r="O56" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="57" spans="3:15">
@@ -3599,7 +3608,7 @@
         <v>448</v>
       </c>
       <c r="O57" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="58" spans="3:15">
@@ -3610,7 +3619,7 @@
         <v>449</v>
       </c>
       <c r="O58" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="59" spans="3:15">
@@ -3620,6 +3629,9 @@
       <c r="E59" t="s">
         <v>450</v>
       </c>
+      <c r="O59" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="60" spans="3:15">
       <c r="C60" t="s">
@@ -3628,6 +3640,9 @@
       <c r="E60" t="s">
         <v>451</v>
       </c>
+      <c r="O60" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="61" spans="3:15">
       <c r="C61" t="s">
@@ -4026,7 +4041,7 @@
         <v>137</v>
       </c>
       <c r="E110" t="s">
-        <v>242</v>
+        <v>501</v>
       </c>
     </row>
     <row r="111" spans="3:5">
@@ -4034,7 +4049,7 @@
         <v>138</v>
       </c>
       <c r="E111" t="s">
-        <v>501</v>
+        <v>242</v>
       </c>
     </row>
     <row r="112" spans="3:5">
@@ -4234,7 +4249,7 @@
         <v>163</v>
       </c>
       <c r="E136" t="s">
-        <v>88</v>
+        <v>526</v>
       </c>
     </row>
     <row r="137" spans="3:5">
@@ -4242,7 +4257,7 @@
         <v>164</v>
       </c>
       <c r="E137" t="s">
-        <v>526</v>
+        <v>88</v>
       </c>
     </row>
     <row r="138" spans="3:5">
@@ -4258,7 +4273,7 @@
         <v>166</v>
       </c>
       <c r="E139" t="s">
-        <v>362</v>
+        <v>528</v>
       </c>
     </row>
     <row r="140" spans="3:5">
@@ -4266,7 +4281,7 @@
         <v>167</v>
       </c>
       <c r="E140" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="141" spans="3:5">
@@ -4274,7 +4289,7 @@
         <v>168</v>
       </c>
       <c r="E141" t="s">
-        <v>528</v>
+        <v>367</v>
       </c>
     </row>
     <row r="142" spans="3:5">
@@ -4376,6 +4391,9 @@
     <row r="154" spans="3:5">
       <c r="C154" t="s">
         <v>181</v>
+      </c>
+      <c r="E154" t="s">
+        <v>541</v>
       </c>
     </row>
     <row r="155" spans="3:5">
@@ -5420,37 +5438,37 @@
   <sheetData>
     <row r="1" spans="1:69">
       <c r="A1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="O1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="AA1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="AE1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AI1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AM1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="AP1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AS1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="AZ1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="BM1" t="s">
         <v>16</v>
@@ -5458,211 +5476,211 @@
     </row>
     <row r="2" spans="1:69">
       <c r="A2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="D2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="E2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="F2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="G2" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="H2" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="I2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="J2" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="K2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L2" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="N2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="O2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="P2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="Q2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="R2" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="S2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="T2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="U2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="V2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="W2" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="X2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="Y2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="Z2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="AA2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="AB2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AC2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AD2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AE2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="AF2" t="s">
+        <v>659</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>660</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>661</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>663</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>664</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>665</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>666</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>668</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>669</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>670</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>672</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>673</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>674</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>676</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>677</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>678</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>679</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>680</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>681</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>682</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>684</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>685</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>686</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>687</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>688</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>689</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>690</v>
+      </c>
+      <c r="BG2" t="s">
         <v>656</v>
       </c>
-      <c r="AG2" t="s">
-        <v>657</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>658</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>660</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>661</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>662</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>663</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>665</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>666</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>667</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>669</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>670</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>671</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>673</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>674</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>675</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>676</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>677</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>678</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>679</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>681</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>682</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>683</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>684</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>685</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>686</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>687</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>653</v>
-      </c>
       <c r="BH2" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="BI2" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="BJ2" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="BK2" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="BL2" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="BM2" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="BN2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="BO2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="BP2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="BQ2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3" spans="1:69">
@@ -6088,7 +6106,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -6502,228 +6520,228 @@
   <sheetData>
     <row r="1" spans="1:66">
       <c r="A1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="J1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AA1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="AK1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="AV1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="BM1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="F2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="G2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="H2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="I2" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="J2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="K2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="L2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="M2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="N2" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="O2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="P2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="Q2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="R2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="S2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="T2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="U2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="V2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="W2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="X2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="Y2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="Z2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="AA2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="AB2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="AC2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="AD2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="AE2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="AF2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="AG2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="AH2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="AI2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="AJ2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="AK2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="AL2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="AM2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="AN2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="AO2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="AP2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="AQ2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="AR2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="AS2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="AT2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="AU2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="AV2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="AW2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="AX2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="AY2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="AZ2" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="BA2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="BB2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="BC2" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="BD2" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="BE2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="BF2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="BG2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="BH2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="BI2" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="BJ2" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="BK2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="BL2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="BM2" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="BN2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="3" spans="1:66">
@@ -7197,7 +7215,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>

--- a/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
+++ b/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="779">
   <si>
     <t>set</t>
   </si>
@@ -111,6 +111,15 @@
     <t>u</t>
   </si>
   <si>
+    <t>DUMMYLUCF</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>INDPLANTOTHCCS</t>
+  </si>
+  <si>
     <t>DUMREWET</t>
   </si>
   <si>
@@ -1206,6 +1215,12 @@
     <t>S24</t>
   </si>
   <si>
+    <t>DUMLUCF</t>
+  </si>
+  <si>
+    <t>DACCO2</t>
+  </si>
+  <si>
     <t>EXPELC</t>
   </si>
   <si>
@@ -1680,6 +1695,9 @@
     <t>EXTWST</t>
   </si>
   <si>
+    <t>EXTECO</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -1815,9 +1833,6 @@
     <t>DEFORBAL</t>
   </si>
   <si>
-    <t>LNDGRSBAL</t>
-  </si>
-  <si>
     <t>2TRACAREVCAP</t>
   </si>
   <si>
@@ -1842,9 +1857,6 @@
     <t>RECWST</t>
   </si>
   <si>
-    <t>RESTRICTWAT</t>
-  </si>
-  <si>
     <t>TRADSLHTRCURCAP</t>
   </si>
   <si>
@@ -1875,10 +1887,22 @@
     <t>INDOTHLPHELCSHARE</t>
   </si>
   <si>
-    <t>INDASHACTCAP</t>
-  </si>
-  <si>
     <t>PWRCOA003BAL</t>
+  </si>
+  <si>
+    <t>INDMINHPHCAP</t>
+  </si>
+  <si>
+    <t>INDCEMKILNCAP</t>
+  </si>
+  <si>
+    <t>INDASHPLANTCAP</t>
+  </si>
+  <si>
+    <t>INDASHHPHCAP</t>
+  </si>
+  <si>
+    <t>INDOTHPLANTCAP</t>
   </si>
   <si>
     <t>category</t>
@@ -2660,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O360"/>
+  <dimension ref="A1:O363"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2765,16 +2789,16 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2801,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2812,37 +2836,37 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F4" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="G4" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="H4" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="I4" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="J4" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="K4" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="L4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="M4" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="O4" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -2853,22 +2877,22 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E5" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F5" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="I5" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="K5" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="O5" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2879,19 +2903,19 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E6" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F6" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="K6" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="O6" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -2902,19 +2926,19 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E7" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F7" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="K7" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="O7" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -2925,19 +2949,19 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F8" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="K8" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="O8" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -2948,19 +2972,19 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E9" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F9" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="K9" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="O9" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2971,19 +2995,19 @@
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F10" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="K10" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="O10" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -2994,19 +3018,19 @@
         <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E11" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F11" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="K11" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="O11" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -3017,13 +3041,13 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F12" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="O12" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -3034,13 +3058,13 @@
         <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F13" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="O13" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -3051,13 +3075,13 @@
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F14" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="O14" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -3068,13 +3092,13 @@
         <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F15" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="O15" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -3085,10 +3109,13 @@
         <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>408</v>
+        <v>411</v>
+      </c>
+      <c r="F16" t="s">
+        <v>559</v>
       </c>
       <c r="O16" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
     </row>
     <row r="17" spans="2:15">
@@ -3099,10 +3126,10 @@
         <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O17" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:15">
@@ -3113,10 +3140,10 @@
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="O18" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
     </row>
     <row r="19" spans="2:15">
@@ -3127,10 +3154,10 @@
         <v>46</v>
       </c>
       <c r="E19" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="O19" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
     </row>
     <row r="20" spans="2:15">
@@ -3141,10 +3168,10 @@
         <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O20" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="21" spans="2:15">
@@ -3155,10 +3182,10 @@
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="O21" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
     </row>
     <row r="22" spans="2:15">
@@ -3169,10 +3196,10 @@
         <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O22" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" spans="2:15">
@@ -3183,10 +3210,10 @@
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="O23" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="24" spans="2:15">
@@ -3197,10 +3224,10 @@
         <v>51</v>
       </c>
       <c r="E24" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="O24" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="25" spans="2:15">
@@ -3211,10 +3238,10 @@
         <v>52</v>
       </c>
       <c r="E25" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="O25" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="26" spans="2:15">
@@ -3225,10 +3252,10 @@
         <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="O26" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
     </row>
     <row r="27" spans="2:15">
@@ -3239,10 +3266,10 @@
         <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="O27" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
     </row>
     <row r="28" spans="2:15">
@@ -3253,10 +3280,10 @@
         <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O28" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="29" spans="2:15">
@@ -3267,10 +3294,10 @@
         <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="O29" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
     </row>
     <row r="30" spans="2:15">
@@ -3281,10 +3308,10 @@
         <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="O30" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="31" spans="2:15">
@@ -3295,10 +3322,10 @@
         <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="O31" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
     </row>
     <row r="32" spans="2:15">
@@ -3309,10 +3336,10 @@
         <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O32" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="33" spans="2:15">
@@ -3323,10 +3350,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O33" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
     <row r="34" spans="2:15">
@@ -3337,10 +3364,10 @@
         <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O34" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35" spans="2:15">
@@ -3351,10 +3378,10 @@
         <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="O35" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
     </row>
     <row r="36" spans="2:15">
@@ -3365,10 +3392,10 @@
         <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O36" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="37" spans="2:15">
@@ -3379,10 +3406,10 @@
         <v>64</v>
       </c>
       <c r="E37" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="O37" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
     </row>
     <row r="38" spans="2:15">
@@ -3393,10 +3420,10 @@
         <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O38" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="39" spans="2:15">
@@ -3407,10 +3434,10 @@
         <v>66</v>
       </c>
       <c r="E39" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="O39" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -3418,10 +3445,10 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O40" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="41" spans="2:15">
@@ -3429,10 +3456,10 @@
         <v>68</v>
       </c>
       <c r="E41" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="O41" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -3440,10 +3467,10 @@
         <v>69</v>
       </c>
       <c r="E42" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O42" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -3451,10 +3478,10 @@
         <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="O43" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -3462,10 +3489,10 @@
         <v>71</v>
       </c>
       <c r="E44" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="O44" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
     </row>
     <row r="45" spans="2:15">
@@ -3473,10 +3500,10 @@
         <v>72</v>
       </c>
       <c r="E45" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="O45" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -3484,10 +3511,10 @@
         <v>73</v>
       </c>
       <c r="E46" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O46" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="47" spans="2:15">
@@ -3495,10 +3522,10 @@
         <v>74</v>
       </c>
       <c r="E47" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O47" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="48" spans="2:15">
@@ -3506,10 +3533,10 @@
         <v>75</v>
       </c>
       <c r="E48" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="O48" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="49" spans="3:15">
@@ -3517,10 +3544,10 @@
         <v>76</v>
       </c>
       <c r="E49" t="s">
-        <v>171</v>
+        <v>444</v>
       </c>
       <c r="O49" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="50" spans="3:15">
@@ -3528,10 +3555,10 @@
         <v>77</v>
       </c>
       <c r="E50" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="O50" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
     </row>
     <row r="51" spans="3:15">
@@ -3539,10 +3566,10 @@
         <v>78</v>
       </c>
       <c r="E51" t="s">
-        <v>442</v>
+        <v>174</v>
       </c>
       <c r="O51" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
     </row>
     <row r="52" spans="3:15">
@@ -3550,10 +3577,10 @@
         <v>79</v>
       </c>
       <c r="E52" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O52" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
     </row>
     <row r="53" spans="3:15">
@@ -3561,10 +3588,10 @@
         <v>80</v>
       </c>
       <c r="E53" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O53" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
     </row>
     <row r="54" spans="3:15">
@@ -3572,10 +3599,10 @@
         <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O54" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
     </row>
     <row r="55" spans="3:15">
@@ -3583,10 +3610,10 @@
         <v>82</v>
       </c>
       <c r="E55" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="O55" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
     </row>
     <row r="56" spans="3:15">
@@ -3594,10 +3621,10 @@
         <v>83</v>
       </c>
       <c r="E56" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O56" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
     </row>
     <row r="57" spans="3:15">
@@ -3605,10 +3632,10 @@
         <v>84</v>
       </c>
       <c r="E57" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="O57" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
     </row>
     <row r="58" spans="3:15">
@@ -3616,10 +3643,10 @@
         <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="O58" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
     </row>
     <row r="59" spans="3:15">
@@ -3627,10 +3654,10 @@
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O59" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="60" spans="3:15">
@@ -3638,10 +3665,10 @@
         <v>87</v>
       </c>
       <c r="E60" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="O60" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="61" spans="3:15">
@@ -3649,7 +3676,10 @@
         <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>452</v>
+        <v>455</v>
+      </c>
+      <c r="O61" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="62" spans="3:15">
@@ -3657,7 +3687,10 @@
         <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>453</v>
+        <v>456</v>
+      </c>
+      <c r="O62" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="63" spans="3:15">
@@ -3665,7 +3698,10 @@
         <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>454</v>
+        <v>457</v>
+      </c>
+      <c r="O63" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="3:15">
@@ -3673,135 +3709,144 @@
         <v>91</v>
       </c>
       <c r="E64" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5">
+        <v>458</v>
+      </c>
+      <c r="O64" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="65" spans="3:15">
       <c r="C65" t="s">
         <v>92</v>
       </c>
       <c r="E65" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="66" spans="3:5">
+        <v>459</v>
+      </c>
+      <c r="O65" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="66" spans="3:15">
       <c r="C66" t="s">
         <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="67" spans="3:5">
+        <v>460</v>
+      </c>
+      <c r="O66" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="67" spans="3:15">
       <c r="C67" t="s">
         <v>94</v>
       </c>
       <c r="E67" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="68" spans="3:15">
       <c r="C68" t="s">
         <v>95</v>
       </c>
       <c r="E68" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="69" spans="3:5">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="69" spans="3:15">
       <c r="C69" t="s">
         <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="70" spans="3:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="70" spans="3:15">
       <c r="C70" t="s">
         <v>97</v>
       </c>
       <c r="E70" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="71" spans="3:5">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="71" spans="3:15">
       <c r="C71" t="s">
         <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="72" spans="3:15">
       <c r="C72" t="s">
         <v>99</v>
       </c>
       <c r="E72" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="73" spans="3:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="73" spans="3:15">
       <c r="C73" t="s">
         <v>100</v>
       </c>
       <c r="E73" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="74" spans="3:5">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="74" spans="3:15">
       <c r="C74" t="s">
         <v>101</v>
       </c>
       <c r="E74" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="75" spans="3:5">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="75" spans="3:15">
       <c r="C75" t="s">
         <v>102</v>
       </c>
       <c r="E75" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="76" spans="3:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="76" spans="3:15">
       <c r="C76" t="s">
         <v>103</v>
       </c>
       <c r="E76" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="77" spans="3:5">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="77" spans="3:15">
       <c r="C77" t="s">
         <v>104</v>
       </c>
       <c r="E77" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="78" spans="3:5">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78" spans="3:15">
       <c r="C78" t="s">
         <v>105</v>
       </c>
       <c r="E78" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="79" spans="3:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="79" spans="3:15">
       <c r="C79" t="s">
         <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="80" spans="3:5">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="80" spans="3:15">
       <c r="C80" t="s">
         <v>107</v>
       </c>
       <c r="E80" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81" spans="3:5">
@@ -3809,7 +3854,7 @@
         <v>108</v>
       </c>
       <c r="E81" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" spans="3:5">
@@ -3817,7 +3862,7 @@
         <v>109</v>
       </c>
       <c r="E82" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="83" spans="3:5">
@@ -3825,7 +3870,7 @@
         <v>110</v>
       </c>
       <c r="E83" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84" spans="3:5">
@@ -3833,7 +3878,7 @@
         <v>111</v>
       </c>
       <c r="E84" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" spans="3:5">
@@ -3841,7 +3886,7 @@
         <v>112</v>
       </c>
       <c r="E85" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="86" spans="3:5">
@@ -3849,7 +3894,7 @@
         <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="3:5">
@@ -3857,7 +3902,7 @@
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="3:5">
@@ -3865,7 +3910,7 @@
         <v>115</v>
       </c>
       <c r="E88" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="89" spans="3:5">
@@ -3873,7 +3918,7 @@
         <v>116</v>
       </c>
       <c r="E89" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="90" spans="3:5">
@@ -3881,7 +3926,7 @@
         <v>117</v>
       </c>
       <c r="E90" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91" spans="3:5">
@@ -3889,7 +3934,7 @@
         <v>118</v>
       </c>
       <c r="E91" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="92" spans="3:5">
@@ -3897,7 +3942,7 @@
         <v>119</v>
       </c>
       <c r="E92" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="93" spans="3:5">
@@ -3905,7 +3950,7 @@
         <v>120</v>
       </c>
       <c r="E93" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="94" spans="3:5">
@@ -3913,7 +3958,7 @@
         <v>121</v>
       </c>
       <c r="E94" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="95" spans="3:5">
@@ -3921,7 +3966,7 @@
         <v>122</v>
       </c>
       <c r="E95" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="3:5">
@@ -3929,7 +3974,7 @@
         <v>123</v>
       </c>
       <c r="E96" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="97" spans="3:5">
@@ -3937,7 +3982,7 @@
         <v>124</v>
       </c>
       <c r="E97" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="98" spans="3:5">
@@ -3945,7 +3990,7 @@
         <v>125</v>
       </c>
       <c r="E98" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="99" spans="3:5">
@@ -3953,7 +3998,7 @@
         <v>126</v>
       </c>
       <c r="E99" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" spans="3:5">
@@ -3961,7 +4006,7 @@
         <v>127</v>
       </c>
       <c r="E100" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" spans="3:5">
@@ -3969,7 +4014,7 @@
         <v>128</v>
       </c>
       <c r="E101" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="102" spans="3:5">
@@ -3977,7 +4022,7 @@
         <v>129</v>
       </c>
       <c r="E102" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" spans="3:5">
@@ -3985,7 +4030,7 @@
         <v>130</v>
       </c>
       <c r="E103" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104" spans="3:5">
@@ -3993,7 +4038,7 @@
         <v>131</v>
       </c>
       <c r="E104" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="105" spans="3:5">
@@ -4001,7 +4046,7 @@
         <v>132</v>
       </c>
       <c r="E105" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106" spans="3:5">
@@ -4009,7 +4054,7 @@
         <v>133</v>
       </c>
       <c r="E106" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" spans="3:5">
@@ -4017,7 +4062,7 @@
         <v>134</v>
       </c>
       <c r="E107" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="108" spans="3:5">
@@ -4025,7 +4070,7 @@
         <v>135</v>
       </c>
       <c r="E108" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="109" spans="3:5">
@@ -4033,7 +4078,7 @@
         <v>136</v>
       </c>
       <c r="E109" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="110" spans="3:5">
@@ -4041,7 +4086,7 @@
         <v>137</v>
       </c>
       <c r="E110" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="111" spans="3:5">
@@ -4049,7 +4094,7 @@
         <v>138</v>
       </c>
       <c r="E111" t="s">
-        <v>242</v>
+        <v>505</v>
       </c>
     </row>
     <row r="112" spans="3:5">
@@ -4057,7 +4102,7 @@
         <v>139</v>
       </c>
       <c r="E112" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="113" spans="3:5">
@@ -4065,7 +4110,7 @@
         <v>140</v>
       </c>
       <c r="E113" t="s">
-        <v>503</v>
+        <v>245</v>
       </c>
     </row>
     <row r="114" spans="3:5">
@@ -4073,7 +4118,7 @@
         <v>141</v>
       </c>
       <c r="E114" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="115" spans="3:5">
@@ -4081,7 +4126,7 @@
         <v>142</v>
       </c>
       <c r="E115" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="116" spans="3:5">
@@ -4089,7 +4134,7 @@
         <v>143</v>
       </c>
       <c r="E116" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="117" spans="3:5">
@@ -4097,7 +4142,7 @@
         <v>144</v>
       </c>
       <c r="E117" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="118" spans="3:5">
@@ -4105,7 +4150,7 @@
         <v>145</v>
       </c>
       <c r="E118" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="119" spans="3:5">
@@ -4113,7 +4158,7 @@
         <v>146</v>
       </c>
       <c r="E119" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="120" spans="3:5">
@@ -4121,7 +4166,7 @@
         <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="121" spans="3:5">
@@ -4129,7 +4174,7 @@
         <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="122" spans="3:5">
@@ -4137,7 +4182,7 @@
         <v>149</v>
       </c>
       <c r="E122" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="123" spans="3:5">
@@ -4145,7 +4190,7 @@
         <v>150</v>
       </c>
       <c r="E123" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="124" spans="3:5">
@@ -4153,7 +4198,7 @@
         <v>151</v>
       </c>
       <c r="E124" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="125" spans="3:5">
@@ -4161,7 +4206,7 @@
         <v>152</v>
       </c>
       <c r="E125" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="126" spans="3:5">
@@ -4169,7 +4214,7 @@
         <v>153</v>
       </c>
       <c r="E126" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="127" spans="3:5">
@@ -4177,7 +4222,7 @@
         <v>154</v>
       </c>
       <c r="E127" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="128" spans="3:5">
@@ -4185,7 +4230,7 @@
         <v>155</v>
       </c>
       <c r="E128" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="129" spans="3:5">
@@ -4193,7 +4238,7 @@
         <v>156</v>
       </c>
       <c r="E129" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="130" spans="3:5">
@@ -4201,7 +4246,7 @@
         <v>157</v>
       </c>
       <c r="E130" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="131" spans="3:5">
@@ -4209,7 +4254,7 @@
         <v>158</v>
       </c>
       <c r="E131" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="132" spans="3:5">
@@ -4217,7 +4262,7 @@
         <v>159</v>
       </c>
       <c r="E132" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="133" spans="3:5">
@@ -4225,7 +4270,7 @@
         <v>160</v>
       </c>
       <c r="E133" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="134" spans="3:5">
@@ -4233,7 +4278,7 @@
         <v>161</v>
       </c>
       <c r="E134" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="135" spans="3:5">
@@ -4241,7 +4286,7 @@
         <v>162</v>
       </c>
       <c r="E135" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="136" spans="3:5">
@@ -4249,7 +4294,7 @@
         <v>163</v>
       </c>
       <c r="E136" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
     </row>
     <row r="137" spans="3:5">
@@ -4257,7 +4302,7 @@
         <v>164</v>
       </c>
       <c r="E137" t="s">
-        <v>88</v>
+        <v>530</v>
       </c>
     </row>
     <row r="138" spans="3:5">
@@ -4265,7 +4310,7 @@
         <v>165</v>
       </c>
       <c r="E138" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="139" spans="3:5">
@@ -4273,7 +4318,7 @@
         <v>166</v>
       </c>
       <c r="E139" t="s">
-        <v>528</v>
+        <v>91</v>
       </c>
     </row>
     <row r="140" spans="3:5">
@@ -4281,7 +4326,7 @@
         <v>167</v>
       </c>
       <c r="E140" t="s">
-        <v>362</v>
+        <v>532</v>
       </c>
     </row>
     <row r="141" spans="3:5">
@@ -4289,7 +4334,7 @@
         <v>168</v>
       </c>
       <c r="E141" t="s">
-        <v>367</v>
+        <v>533</v>
       </c>
     </row>
     <row r="142" spans="3:5">
@@ -4297,7 +4342,7 @@
         <v>169</v>
       </c>
       <c r="E142" t="s">
-        <v>529</v>
+        <v>365</v>
       </c>
     </row>
     <row r="143" spans="3:5">
@@ -4305,7 +4350,7 @@
         <v>170</v>
       </c>
       <c r="E143" t="s">
-        <v>530</v>
+        <v>370</v>
       </c>
     </row>
     <row r="144" spans="3:5">
@@ -4313,7 +4358,7 @@
         <v>171</v>
       </c>
       <c r="E144" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="145" spans="3:5">
@@ -4321,7 +4366,7 @@
         <v>172</v>
       </c>
       <c r="E145" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="146" spans="3:5">
@@ -4329,7 +4374,7 @@
         <v>173</v>
       </c>
       <c r="E146" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="147" spans="3:5">
@@ -4337,7 +4382,7 @@
         <v>174</v>
       </c>
       <c r="E147" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="148" spans="3:5">
@@ -4345,7 +4390,7 @@
         <v>175</v>
       </c>
       <c r="E148" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="149" spans="3:5">
@@ -4353,7 +4398,7 @@
         <v>176</v>
       </c>
       <c r="E149" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" spans="3:5">
@@ -4361,7 +4406,7 @@
         <v>177</v>
       </c>
       <c r="E150" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="151" spans="3:5">
@@ -4369,7 +4414,7 @@
         <v>178</v>
       </c>
       <c r="E151" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="152" spans="3:5">
@@ -4377,7 +4422,7 @@
         <v>179</v>
       </c>
       <c r="E152" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="153" spans="3:5">
@@ -4385,7 +4430,7 @@
         <v>180</v>
       </c>
       <c r="E153" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="154" spans="3:5">
@@ -4393,18 +4438,24 @@
         <v>181</v>
       </c>
       <c r="E154" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="155" spans="3:5">
       <c r="C155" t="s">
         <v>182</v>
       </c>
+      <c r="E155" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="156" spans="3:5">
       <c r="C156" t="s">
         <v>183</v>
       </c>
+      <c r="E156" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="157" spans="3:5">
       <c r="C157" t="s">
@@ -5424,6 +5475,21 @@
     <row r="360" spans="3:3">
       <c r="C360" t="s">
         <v>387</v>
+      </c>
+    </row>
+    <row r="361" spans="3:3">
+      <c r="C361" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="362" spans="3:3">
+      <c r="C362" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="363" spans="3:3">
+      <c r="C363" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -5438,37 +5504,37 @@
   <sheetData>
     <row r="1" spans="1:69">
       <c r="A1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B1" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
       <c r="L1" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="O1" t="s">
-        <v>639</v>
+        <v>647</v>
       </c>
       <c r="AA1" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="AE1" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="AI1" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="AM1" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="AP1" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="AS1" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="AZ1" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="BM1" t="s">
         <v>16</v>
@@ -5476,211 +5542,211 @@
     </row>
     <row r="2" spans="1:69">
       <c r="A2" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="B2" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C2" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D2" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="E2" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="F2" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="G2" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="H2" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="I2" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="J2" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="K2" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="L2" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="M2" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="N2" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="O2" t="s">
-        <v>640</v>
+        <v>648</v>
       </c>
       <c r="P2" t="s">
-        <v>641</v>
+        <v>649</v>
       </c>
       <c r="Q2" t="s">
-        <v>642</v>
+        <v>650</v>
       </c>
       <c r="R2" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="S2" t="s">
-        <v>644</v>
+        <v>652</v>
       </c>
       <c r="T2" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="U2" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="V2" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="W2" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="X2" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="Y2" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="Z2" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="AA2" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="AB2" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="AC2" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="AD2" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="AE2" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="AF2" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="AG2" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="AH2" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="AI2" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="AJ2" t="s">
+        <v>672</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>673</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>674</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>676</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>677</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>678</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>680</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>681</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>682</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>684</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>685</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>686</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>687</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>688</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>689</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>690</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>692</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>693</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>694</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>695</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>696</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>697</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>698</v>
+      </c>
+      <c r="BG2" t="s">
         <v>664</v>
       </c>
-      <c r="AK2" t="s">
-        <v>665</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>666</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>668</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>669</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>670</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>672</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>673</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>674</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>676</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>677</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>678</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>679</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>680</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>681</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>682</v>
-      </c>
-      <c r="AZ2" t="s">
-        <v>684</v>
-      </c>
-      <c r="BA2" t="s">
-        <v>685</v>
-      </c>
-      <c r="BB2" t="s">
-        <v>686</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>687</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>688</v>
-      </c>
-      <c r="BE2" t="s">
-        <v>689</v>
-      </c>
-      <c r="BF2" t="s">
-        <v>690</v>
-      </c>
-      <c r="BG2" t="s">
-        <v>656</v>
-      </c>
       <c r="BH2" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="BI2" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="BJ2" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="BK2" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="BL2" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
       <c r="BM2" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="BN2" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="BO2" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="BP2" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="BQ2" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
     </row>
     <row r="3" spans="1:69">
@@ -6106,7 +6172,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -6520,228 +6586,228 @@
   <sheetData>
     <row r="1" spans="1:66">
       <c r="A1" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="B1" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="D1" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="J1" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
       <c r="AA1" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="AK1" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="AV1" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="BM1" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
     </row>
     <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="B2" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="C2" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
       <c r="D2" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="E2" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="F2" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="G2" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="H2" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="I2" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="J2" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="K2" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="L2" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="M2" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="N2" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="O2" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="P2" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="Q2" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="R2" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="S2" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="T2" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="U2" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="V2" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="W2" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="X2" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="Y2" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="Z2" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="AA2" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="AB2" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="AC2" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="AD2" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="AE2" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="AF2" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="AG2" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="AH2" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="AI2" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="AJ2" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="AK2" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="AL2" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="AM2" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="AN2" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="AO2" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="AP2" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="AQ2" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="AR2" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="AS2" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="AT2" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="AU2" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="AV2" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="AW2" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="AX2" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="AY2" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="AZ2" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="BA2" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="BB2" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="BC2" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="BD2" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="BE2" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="BF2" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="BG2" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="BH2" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="BI2" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="BJ2" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="BK2" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="BL2" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="BM2" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="BN2" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
     </row>
     <row r="3" spans="1:66">
@@ -7215,7 +7281,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>

--- a/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
+++ b/src/workflow/1_Experiment/0_From_Confection/B1_Model_Structure.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="779">
   <si>
     <t>set</t>
   </si>
@@ -111,6 +111,15 @@
     <t>u</t>
   </si>
   <si>
+    <t>DUMMYLUCF</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>INDPLANTOTHCCS</t>
+  </si>
+  <si>
     <t>DUMREWET</t>
   </si>
   <si>
@@ -1206,6 +1215,15 @@
     <t>S24</t>
   </si>
   <si>
+    <t>DUMLUCF</t>
+  </si>
+  <si>
+    <t>DACCO2</t>
+  </si>
+  <si>
+    <t>EXPELC</t>
+  </si>
+  <si>
     <t>PWRWAT0</t>
   </si>
   <si>
@@ -1677,6 +1695,9 @@
     <t>EXTWST</t>
   </si>
   <si>
+    <t>EXTECO</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -1812,9 +1833,6 @@
     <t>DEFORBAL</t>
   </si>
   <si>
-    <t>LNDGRSBAL</t>
-  </si>
-  <si>
     <t>2TRACAREVCAP</t>
   </si>
   <si>
@@ -1839,9 +1857,6 @@
     <t>RECWST</t>
   </si>
   <si>
-    <t>RESTRICTWAT</t>
-  </si>
-  <si>
     <t>TRADSLHTRCURCAP</t>
   </si>
   <si>
@@ -1870,6 +1885,24 @@
   </si>
   <si>
     <t>INDOTHLPHELCSHARE</t>
+  </si>
+  <si>
+    <t>PWRCOA003BAL</t>
+  </si>
+  <si>
+    <t>INDMINHPHCAP</t>
+  </si>
+  <si>
+    <t>INDCEMKILNCAP</t>
+  </si>
+  <si>
+    <t>INDASHPLANTCAP</t>
+  </si>
+  <si>
+    <t>INDASHHPHCAP</t>
+  </si>
+  <si>
+    <t>INDOTHPLANTCAP</t>
   </si>
   <si>
     <t>category</t>
@@ -2651,7 +2684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O360"/>
+  <dimension ref="A1:O363"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -2756,16 +2789,16 @@
         <v>36</v>
       </c>
       <c r="C3">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -2792,7 +2825,7 @@
         <v>0</v>
       </c>
       <c r="O3">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -2803,37 +2836,37 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="E4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F4" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="G4" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="H4" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="I4" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="J4" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="K4" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="L4" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="M4" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="O4" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -2844,22 +2877,22 @@
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E5" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F5" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I5" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="K5" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="O5" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -2870,19 +2903,19 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E6" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="F6" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="K6" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="O6" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -2893,19 +2926,19 @@
         <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="E7" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F7" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="K7" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="O7" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -2916,19 +2949,19 @@
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E8" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="F8" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="K8" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="O8" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -2939,19 +2972,19 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E9" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F9" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="K9" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="O9" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -2962,19 +2995,19 @@
         <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F10" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="K10" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="O10" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -2985,19 +3018,19 @@
         <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E11" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F11" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="K11" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="O11" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -3008,13 +3041,13 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F12" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="O12" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -3025,13 +3058,13 @@
         <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F13" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="O13" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -3042,13 +3075,13 @@
         <v>41</v>
       </c>
       <c r="E14" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F14" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="O14" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -3059,13 +3092,13 @@
         <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F15" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="O15" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -3076,10 +3109,13 @@
         <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>408</v>
+        <v>411</v>
+      </c>
+      <c r="F16" t="s">
+        <v>559</v>
       </c>
       <c r="O16" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
     </row>
     <row r="17" spans="2:15">
@@ -3090,10 +3126,10 @@
         <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O17" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
     </row>
     <row r="18" spans="2:15">
@@ -3104,10 +3140,10 @@
         <v>45</v>
       </c>
       <c r="E18" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="O18" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
     </row>
     <row r="19" spans="2:15">
@@ -3118,10 +3154,10 @@
         <v>46</v>
       </c>
       <c r="E19" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="O19" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
     </row>
     <row r="20" spans="2:15">
@@ -3132,10 +3168,10 @@
         <v>47</v>
       </c>
       <c r="E20" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="O20" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
     </row>
     <row r="21" spans="2:15">
@@ -3146,10 +3182,10 @@
         <v>48</v>
       </c>
       <c r="E21" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="O21" t="s">
-        <v>580</v>
+        <v>587</v>
       </c>
     </row>
     <row r="22" spans="2:15">
@@ -3160,10 +3196,10 @@
         <v>49</v>
       </c>
       <c r="E22" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O22" t="s">
-        <v>581</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" spans="2:15">
@@ -3174,10 +3210,10 @@
         <v>50</v>
       </c>
       <c r="E23" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="O23" t="s">
-        <v>582</v>
+        <v>589</v>
       </c>
     </row>
     <row r="24" spans="2:15">
@@ -3188,10 +3224,10 @@
         <v>51</v>
       </c>
       <c r="E24" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="O24" t="s">
-        <v>583</v>
+        <v>590</v>
       </c>
     </row>
     <row r="25" spans="2:15">
@@ -3202,10 +3238,10 @@
         <v>52</v>
       </c>
       <c r="E25" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="O25" t="s">
-        <v>584</v>
+        <v>591</v>
       </c>
     </row>
     <row r="26" spans="2:15">
@@ -3216,10 +3252,10 @@
         <v>53</v>
       </c>
       <c r="E26" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="O26" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
     </row>
     <row r="27" spans="2:15">
@@ -3230,10 +3266,10 @@
         <v>54</v>
       </c>
       <c r="E27" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="O27" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
     </row>
     <row r="28" spans="2:15">
@@ -3244,10 +3280,10 @@
         <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O28" t="s">
-        <v>587</v>
+        <v>594</v>
       </c>
     </row>
     <row r="29" spans="2:15">
@@ -3258,10 +3294,10 @@
         <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="O29" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
     </row>
     <row r="30" spans="2:15">
@@ -3272,10 +3308,10 @@
         <v>57</v>
       </c>
       <c r="E30" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="O30" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
     </row>
     <row r="31" spans="2:15">
@@ -3286,10 +3322,10 @@
         <v>58</v>
       </c>
       <c r="E31" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="O31" t="s">
-        <v>590</v>
+        <v>597</v>
       </c>
     </row>
     <row r="32" spans="2:15">
@@ -3300,10 +3336,10 @@
         <v>59</v>
       </c>
       <c r="E32" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="O32" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
     </row>
     <row r="33" spans="2:15">
@@ -3314,10 +3350,10 @@
         <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O33" t="s">
-        <v>592</v>
+        <v>599</v>
       </c>
     </row>
     <row r="34" spans="2:15">
@@ -3328,10 +3364,10 @@
         <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O34" t="s">
-        <v>593</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35" spans="2:15">
@@ -3342,10 +3378,10 @@
         <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="O35" t="s">
-        <v>594</v>
+        <v>601</v>
       </c>
     </row>
     <row r="36" spans="2:15">
@@ -3356,10 +3392,10 @@
         <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O36" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
     </row>
     <row r="37" spans="2:15">
@@ -3370,10 +3406,10 @@
         <v>64</v>
       </c>
       <c r="E37" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="O37" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
     </row>
     <row r="38" spans="2:15">
@@ -3384,10 +3420,10 @@
         <v>65</v>
       </c>
       <c r="E38" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="O38" t="s">
-        <v>597</v>
+        <v>604</v>
       </c>
     </row>
     <row r="39" spans="2:15">
@@ -3398,10 +3434,10 @@
         <v>66</v>
       </c>
       <c r="E39" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="O39" t="s">
-        <v>598</v>
+        <v>605</v>
       </c>
     </row>
     <row r="40" spans="2:15">
@@ -3409,10 +3445,10 @@
         <v>67</v>
       </c>
       <c r="E40" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="O40" t="s">
-        <v>599</v>
+        <v>606</v>
       </c>
     </row>
     <row r="41" spans="2:15">
@@ -3420,10 +3456,10 @@
         <v>68</v>
       </c>
       <c r="E41" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="O41" t="s">
-        <v>600</v>
+        <v>607</v>
       </c>
     </row>
     <row r="42" spans="2:15">
@@ -3431,10 +3467,10 @@
         <v>69</v>
       </c>
       <c r="E42" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="O42" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
     </row>
     <row r="43" spans="2:15">
@@ -3442,10 +3478,10 @@
         <v>70</v>
       </c>
       <c r="E43" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="O43" t="s">
-        <v>602</v>
+        <v>609</v>
       </c>
     </row>
     <row r="44" spans="2:15">
@@ -3453,10 +3489,10 @@
         <v>71</v>
       </c>
       <c r="E44" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="O44" t="s">
-        <v>603</v>
+        <v>610</v>
       </c>
     </row>
     <row r="45" spans="2:15">
@@ -3464,10 +3500,10 @@
         <v>72</v>
       </c>
       <c r="E45" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="O45" t="s">
-        <v>604</v>
+        <v>611</v>
       </c>
     </row>
     <row r="46" spans="2:15">
@@ -3475,10 +3511,10 @@
         <v>73</v>
       </c>
       <c r="E46" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="O46" t="s">
-        <v>605</v>
+        <v>612</v>
       </c>
     </row>
     <row r="47" spans="2:15">
@@ -3486,10 +3522,10 @@
         <v>74</v>
       </c>
       <c r="E47" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O47" t="s">
-        <v>606</v>
+        <v>613</v>
       </c>
     </row>
     <row r="48" spans="2:15">
@@ -3497,10 +3533,10 @@
         <v>75</v>
       </c>
       <c r="E48" t="s">
-        <v>171</v>
+        <v>443</v>
       </c>
       <c r="O48" t="s">
-        <v>607</v>
+        <v>614</v>
       </c>
     </row>
     <row r="49" spans="3:15">
@@ -3508,10 +3544,10 @@
         <v>76</v>
       </c>
       <c r="E49" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="O49" t="s">
-        <v>608</v>
+        <v>615</v>
       </c>
     </row>
     <row r="50" spans="3:15">
@@ -3519,10 +3555,10 @@
         <v>77</v>
       </c>
       <c r="E50" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="O50" t="s">
-        <v>609</v>
+        <v>616</v>
       </c>
     </row>
     <row r="51" spans="3:15">
@@ -3530,10 +3566,10 @@
         <v>78</v>
       </c>
       <c r="E51" t="s">
-        <v>442</v>
+        <v>174</v>
       </c>
       <c r="O51" t="s">
-        <v>610</v>
+        <v>617</v>
       </c>
     </row>
     <row r="52" spans="3:15">
@@ -3541,10 +3577,10 @@
         <v>79</v>
       </c>
       <c r="E52" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O52" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
     </row>
     <row r="53" spans="3:15">
@@ -3552,10 +3588,10 @@
         <v>80</v>
       </c>
       <c r="E53" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="O53" t="s">
-        <v>612</v>
+        <v>619</v>
       </c>
     </row>
     <row r="54" spans="3:15">
@@ -3563,10 +3599,10 @@
         <v>81</v>
       </c>
       <c r="E54" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O54" t="s">
-        <v>613</v>
+        <v>620</v>
       </c>
     </row>
     <row r="55" spans="3:15">
@@ -3574,10 +3610,10 @@
         <v>82</v>
       </c>
       <c r="E55" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="O55" t="s">
-        <v>614</v>
+        <v>621</v>
       </c>
     </row>
     <row r="56" spans="3:15">
@@ -3585,10 +3621,10 @@
         <v>83</v>
       </c>
       <c r="E56" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O56" t="s">
-        <v>615</v>
+        <v>622</v>
       </c>
     </row>
     <row r="57" spans="3:15">
@@ -3596,10 +3632,10 @@
         <v>84</v>
       </c>
       <c r="E57" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="O57" t="s">
-        <v>616</v>
+        <v>623</v>
       </c>
     </row>
     <row r="58" spans="3:15">
@@ -3607,10 +3643,10 @@
         <v>85</v>
       </c>
       <c r="E58" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="O58" t="s">
-        <v>617</v>
+        <v>624</v>
       </c>
     </row>
     <row r="59" spans="3:15">
@@ -3618,7 +3654,10 @@
         <v>86</v>
       </c>
       <c r="E59" t="s">
-        <v>450</v>
+        <v>453</v>
+      </c>
+      <c r="O59" t="s">
+        <v>625</v>
       </c>
     </row>
     <row r="60" spans="3:15">
@@ -3626,7 +3665,10 @@
         <v>87</v>
       </c>
       <c r="E60" t="s">
-        <v>451</v>
+        <v>454</v>
+      </c>
+      <c r="O60" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="61" spans="3:15">
@@ -3634,7 +3676,10 @@
         <v>88</v>
       </c>
       <c r="E61" t="s">
-        <v>452</v>
+        <v>455</v>
+      </c>
+      <c r="O61" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="62" spans="3:15">
@@ -3642,7 +3687,10 @@
         <v>89</v>
       </c>
       <c r="E62" t="s">
-        <v>453</v>
+        <v>456</v>
+      </c>
+      <c r="O62" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="63" spans="3:15">
@@ -3650,7 +3698,10 @@
         <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>454</v>
+        <v>457</v>
+      </c>
+      <c r="O63" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="64" spans="3:15">
@@ -3658,135 +3709,144 @@
         <v>91</v>
       </c>
       <c r="E64" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5">
+        <v>458</v>
+      </c>
+      <c r="O64" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="65" spans="3:15">
       <c r="C65" t="s">
         <v>92</v>
       </c>
       <c r="E65" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="66" spans="3:5">
+        <v>459</v>
+      </c>
+      <c r="O65" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="66" spans="3:15">
       <c r="C66" t="s">
         <v>93</v>
       </c>
       <c r="E66" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="67" spans="3:5">
+        <v>460</v>
+      </c>
+      <c r="O66" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="67" spans="3:15">
       <c r="C67" t="s">
         <v>94</v>
       </c>
       <c r="E67" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="68" spans="3:15">
       <c r="C68" t="s">
         <v>95</v>
       </c>
       <c r="E68" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="69" spans="3:5">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="69" spans="3:15">
       <c r="C69" t="s">
         <v>96</v>
       </c>
       <c r="E69" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="70" spans="3:5">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="70" spans="3:15">
       <c r="C70" t="s">
         <v>97</v>
       </c>
       <c r="E70" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="71" spans="3:5">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="71" spans="3:15">
       <c r="C71" t="s">
         <v>98</v>
       </c>
       <c r="E71" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="72" spans="3:15">
       <c r="C72" t="s">
         <v>99</v>
       </c>
       <c r="E72" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="73" spans="3:5">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="73" spans="3:15">
       <c r="C73" t="s">
         <v>100</v>
       </c>
       <c r="E73" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="74" spans="3:5">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="74" spans="3:15">
       <c r="C74" t="s">
         <v>101</v>
       </c>
       <c r="E74" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="75" spans="3:5">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="75" spans="3:15">
       <c r="C75" t="s">
         <v>102</v>
       </c>
       <c r="E75" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="76" spans="3:5">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="76" spans="3:15">
       <c r="C76" t="s">
         <v>103</v>
       </c>
       <c r="E76" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="77" spans="3:5">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="77" spans="3:15">
       <c r="C77" t="s">
         <v>104</v>
       </c>
       <c r="E77" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="78" spans="3:5">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="78" spans="3:15">
       <c r="C78" t="s">
         <v>105</v>
       </c>
       <c r="E78" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="79" spans="3:5">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="79" spans="3:15">
       <c r="C79" t="s">
         <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="80" spans="3:5">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="80" spans="3:15">
       <c r="C80" t="s">
         <v>107</v>
       </c>
       <c r="E80" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="81" spans="3:5">
@@ -3794,7 +3854,7 @@
         <v>108</v>
       </c>
       <c r="E81" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="82" spans="3:5">
@@ -3802,7 +3862,7 @@
         <v>109</v>
       </c>
       <c r="E82" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="83" spans="3:5">
@@ -3810,7 +3870,7 @@
         <v>110</v>
       </c>
       <c r="E83" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84" spans="3:5">
@@ -3818,7 +3878,7 @@
         <v>111</v>
       </c>
       <c r="E84" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" spans="3:5">
@@ -3826,7 +3886,7 @@
         <v>112</v>
       </c>
       <c r="E85" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="86" spans="3:5">
@@ -3834,7 +3894,7 @@
         <v>113</v>
       </c>
       <c r="E86" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87" spans="3:5">
@@ -3842,7 +3902,7 @@
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="3:5">
@@ -3850,7 +3910,7 @@
         <v>115</v>
       </c>
       <c r="E88" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="89" spans="3:5">
@@ -3858,7 +3918,7 @@
         <v>116</v>
       </c>
       <c r="E89" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="90" spans="3:5">
@@ -3866,7 +3926,7 @@
         <v>117</v>
       </c>
       <c r="E90" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91" spans="3:5">
@@ -3874,7 +3934,7 @@
         <v>118</v>
       </c>
       <c r="E91" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="92" spans="3:5">
@@ -3882,7 +3942,7 @@
         <v>119</v>
       </c>
       <c r="E92" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="93" spans="3:5">
@@ -3890,7 +3950,7 @@
         <v>120</v>
       </c>
       <c r="E93" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="94" spans="3:5">
@@ -3898,7 +3958,7 @@
         <v>121</v>
       </c>
       <c r="E94" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="95" spans="3:5">
@@ -3906,7 +3966,7 @@
         <v>122</v>
       </c>
       <c r="E95" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="96" spans="3:5">
@@ -3914,7 +3974,7 @@
         <v>123</v>
       </c>
       <c r="E96" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="97" spans="3:5">
@@ -3922,7 +3982,7 @@
         <v>124</v>
       </c>
       <c r="E97" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="98" spans="3:5">
@@ -3930,7 +3990,7 @@
         <v>125</v>
       </c>
       <c r="E98" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="99" spans="3:5">
@@ -3938,7 +3998,7 @@
         <v>126</v>
       </c>
       <c r="E99" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="100" spans="3:5">
@@ -3946,7 +4006,7 @@
         <v>127</v>
       </c>
       <c r="E100" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="101" spans="3:5">
@@ -3954,7 +4014,7 @@
         <v>128</v>
       </c>
       <c r="E101" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="102" spans="3:5">
@@ -3962,7 +4022,7 @@
         <v>129</v>
       </c>
       <c r="E102" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" spans="3:5">
@@ -3970,7 +4030,7 @@
         <v>130</v>
       </c>
       <c r="E103" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104" spans="3:5">
@@ -3978,7 +4038,7 @@
         <v>131</v>
       </c>
       <c r="E104" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="105" spans="3:5">
@@ -3986,7 +4046,7 @@
         <v>132</v>
       </c>
       <c r="E105" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="106" spans="3:5">
@@ -3994,7 +4054,7 @@
         <v>133</v>
       </c>
       <c r="E106" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="107" spans="3:5">
@@ -4002,7 +4062,7 @@
         <v>134</v>
       </c>
       <c r="E107" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="108" spans="3:5">
@@ -4010,7 +4070,7 @@
         <v>135</v>
       </c>
       <c r="E108" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="109" spans="3:5">
@@ -4018,7 +4078,7 @@
         <v>136</v>
       </c>
       <c r="E109" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="110" spans="3:5">
@@ -4026,7 +4086,7 @@
         <v>137</v>
       </c>
       <c r="E110" t="s">
-        <v>242</v>
+        <v>504</v>
       </c>
     </row>
     <row r="111" spans="3:5">
@@ -4034,7 +4094,7 @@
         <v>138</v>
       </c>
       <c r="E111" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="112" spans="3:5">
@@ -4042,7 +4102,7 @@
         <v>139</v>
       </c>
       <c r="E112" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="113" spans="3:5">
@@ -4050,7 +4110,7 @@
         <v>140</v>
       </c>
       <c r="E113" t="s">
-        <v>503</v>
+        <v>245</v>
       </c>
     </row>
     <row r="114" spans="3:5">
@@ -4058,7 +4118,7 @@
         <v>141</v>
       </c>
       <c r="E114" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="115" spans="3:5">
@@ -4066,7 +4126,7 @@
         <v>142</v>
       </c>
       <c r="E115" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="116" spans="3:5">
@@ -4074,7 +4134,7 @@
         <v>143</v>
       </c>
       <c r="E116" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="117" spans="3:5">
@@ -4082,7 +4142,7 @@
         <v>144</v>
       </c>
       <c r="E117" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="118" spans="3:5">
@@ -4090,7 +4150,7 @@
         <v>145</v>
       </c>
       <c r="E118" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="119" spans="3:5">
@@ -4098,7 +4158,7 @@
         <v>146</v>
       </c>
       <c r="E119" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="120" spans="3:5">
@@ -4106,7 +4166,7 @@
         <v>147</v>
       </c>
       <c r="E120" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="121" spans="3:5">
@@ -4114,7 +4174,7 @@
         <v>148</v>
       </c>
       <c r="E121" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="122" spans="3:5">
@@ -4122,7 +4182,7 @@
         <v>149</v>
       </c>
       <c r="E122" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="123" spans="3:5">
@@ -4130,7 +4190,7 @@
         <v>150</v>
       </c>
       <c r="E123" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="124" spans="3:5">
@@ -4138,7 +4198,7 @@
         <v>151</v>
       </c>
       <c r="E124" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="125" spans="3:5">
@@ -4146,7 +4206,7 @@
         <v>152</v>
       </c>
       <c r="E125" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="126" spans="3:5">
@@ -4154,7 +4214,7 @@
         <v>153</v>
       </c>
       <c r="E126" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="127" spans="3:5">
@@ -4162,7 +4222,7 @@
         <v>154</v>
       </c>
       <c r="E127" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="128" spans="3:5">
@@ -4170,7 +4230,7 @@
         <v>155</v>
       </c>
       <c r="E128" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="129" spans="3:5">
@@ -4178,7 +4238,7 @@
         <v>156</v>
       </c>
       <c r="E129" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="130" spans="3:5">
@@ -4186,7 +4246,7 @@
         <v>157</v>
       </c>
       <c r="E130" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="131" spans="3:5">
@@ -4194,7 +4254,7 @@
         <v>158</v>
       </c>
       <c r="E131" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="132" spans="3:5">
@@ -4202,7 +4262,7 @@
         <v>159</v>
       </c>
       <c r="E132" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="133" spans="3:5">
@@ -4210,7 +4270,7 @@
         <v>160</v>
       </c>
       <c r="E133" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="134" spans="3:5">
@@ -4218,7 +4278,7 @@
         <v>161</v>
       </c>
       <c r="E134" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
     </row>
     <row r="135" spans="3:5">
@@ -4226,7 +4286,7 @@
         <v>162</v>
       </c>
       <c r="E135" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="136" spans="3:5">
@@ -4234,7 +4294,7 @@
         <v>163</v>
       </c>
       <c r="E136" t="s">
-        <v>88</v>
+        <v>529</v>
       </c>
     </row>
     <row r="137" spans="3:5">
@@ -4242,7 +4302,7 @@
         <v>164</v>
       </c>
       <c r="E137" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
     </row>
     <row r="138" spans="3:5">
@@ -4250,7 +4310,7 @@
         <v>165</v>
       </c>
       <c r="E138" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
     </row>
     <row r="139" spans="3:5">
@@ -4258,7 +4318,7 @@
         <v>166</v>
       </c>
       <c r="E139" t="s">
-        <v>362</v>
+        <v>91</v>
       </c>
     </row>
     <row r="140" spans="3:5">
@@ -4266,7 +4326,7 @@
         <v>167</v>
       </c>
       <c r="E140" t="s">
-        <v>367</v>
+        <v>532</v>
       </c>
     </row>
     <row r="141" spans="3:5">
@@ -4274,7 +4334,7 @@
         <v>168</v>
       </c>
       <c r="E141" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="142" spans="3:5">
@@ -4282,7 +4342,7 @@
         <v>169</v>
       </c>
       <c r="E142" t="s">
-        <v>529</v>
+        <v>365</v>
       </c>
     </row>
     <row r="143" spans="3:5">
@@ -4290,7 +4350,7 @@
         <v>170</v>
       </c>
       <c r="E143" t="s">
-        <v>530</v>
+        <v>370</v>
       </c>
     </row>
     <row r="144" spans="3:5">
@@ -4298,7 +4358,7 @@
         <v>171</v>
       </c>
       <c r="E144" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="145" spans="3:5">
@@ -4306,7 +4366,7 @@
         <v>172</v>
       </c>
       <c r="E145" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="146" spans="3:5">
@@ -4314,7 +4374,7 @@
         <v>173</v>
       </c>
       <c r="E146" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="147" spans="3:5">
@@ -4322,7 +4382,7 @@
         <v>174</v>
       </c>
       <c r="E147" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="148" spans="3:5">
@@ -4330,7 +4390,7 @@
         <v>175</v>
       </c>
       <c r="E148" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="149" spans="3:5">
@@ -4338,7 +4398,7 @@
         <v>176</v>
       </c>
       <c r="E149" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" spans="3:5">
@@ -4346,7 +4406,7 @@
         <v>177</v>
       </c>
       <c r="E150" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
     </row>
     <row r="151" spans="3:5">
@@ -4354,7 +4414,7 @@
         <v>178</v>
       </c>
       <c r="E151" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="152" spans="3:5">
@@ -4362,7 +4422,7 @@
         <v>179</v>
       </c>
       <c r="E152" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="153" spans="3:5">
@@ -4370,23 +4430,32 @@
         <v>180</v>
       </c>
       <c r="E153" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="154" spans="3:5">
       <c r="C154" t="s">
         <v>181</v>
       </c>
+      <c r="E154" t="s">
+        <v>544</v>
+      </c>
     </row>
     <row r="155" spans="3:5">
       <c r="C155" t="s">
         <v>182</v>
       </c>
+      <c r="E155" t="s">
+        <v>545</v>
+      </c>
     </row>
     <row r="156" spans="3:5">
       <c r="C156" t="s">
         <v>183</v>
       </c>
+      <c r="E156" t="s">
+        <v>546</v>
+      </c>
     </row>
     <row r="157" spans="3:5">
       <c r="C157" t="s">
@@ -5406,6 +5475,21 @@
     <row r="360" spans="3:3">
       <c r="C360" t="s">
         <v>387</v>
+      </c>
+    </row>
+    <row r="361" spans="3:3">
+      <c r="C361" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="362" spans="3:3">
+      <c r="C362" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="363" spans="3:3">
+      <c r="C363" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -5420,37 +5504,37 @@
   <sheetData>
     <row r="1" spans="1:69">
       <c r="A1" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="B1" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="L1" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="O1" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="AA1" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="AE1" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="AI1" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="AM1" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="AP1" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="AS1" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="AZ1" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="BM1" t="s">
         <v>16</v>
@@ -5458,211 +5542,211 @@
     </row>
     <row r="2" spans="1:69">
       <c r="A2" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="B2" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="C2" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="D2" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="E2" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="F2" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="G2" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="H2" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="I2" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="J2" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="K2" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="L2" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="M2" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="N2" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="O2" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="P2" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="Q2" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="R2" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="S2" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="T2" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="U2" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="V2" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="W2" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="X2" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="Y2" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="Z2" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="AA2" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="AB2" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="AC2" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="AD2" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="AE2" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="AF2" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="AG2" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="AH2" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="AI2" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="AJ2" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="AK2" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="AL2" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="AM2" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="AN2" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="AO2" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="AP2" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="AQ2" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="AR2" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="AS2" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="AT2" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="AU2" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="AV2" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="AW2" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="AX2" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="AY2" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="AZ2" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="BA2" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="BB2" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="BC2" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="BD2" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="BE2" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="BF2" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="BG2" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="BH2" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="BI2" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="BJ2" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="BK2" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="BL2" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="BM2" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="BN2" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="BO2" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="BP2" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="BQ2" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
     </row>
     <row r="3" spans="1:69">
@@ -6088,7 +6172,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="G5" t="s">
         <v>24</v>
@@ -6502,228 +6586,228 @@
   <sheetData>
     <row r="1" spans="1:66">
       <c r="A1" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="B1" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="D1" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="J1" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="AA1" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="AK1" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="AV1" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="BM1" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
     </row>
     <row r="2" spans="1:66">
       <c r="A2" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="B2" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="C2" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="D2" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="E2" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="F2" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="G2" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="H2" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="I2" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="J2" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="K2" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="L2" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="M2" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="N2" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="O2" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="P2" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="Q2" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="R2" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="S2" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="T2" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="U2" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="V2" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="W2" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="X2" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="Y2" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="Z2" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="AA2" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="AB2" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="AC2" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="AD2" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
       <c r="AE2" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="AF2" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="AG2" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="AH2" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="AI2" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="AJ2" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="AK2" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="AL2" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="AM2" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="AN2" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="AO2" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
       <c r="AP2" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="AQ2" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="AR2" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="AS2" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="AT2" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="AU2" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="AV2" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="AW2" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="AX2" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="AY2" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="AZ2" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="BA2" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="BB2" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="BC2" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="BD2" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="BE2" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="BF2" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="BG2" t="s">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="BH2" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="BI2" t="s">
-        <v>761</v>
+        <v>772</v>
       </c>
       <c r="BJ2" t="s">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="BK2" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="BL2" t="s">
-        <v>764</v>
+        <v>775</v>
       </c>
       <c r="BM2" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="BN2" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
     </row>
     <row r="3" spans="1:66">
@@ -7197,7 +7281,7 @@
         <v>20</v>
       </c>
       <c r="Z5" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="AA5" t="s">
         <v>18</v>
